--- a/SPC26S1 - 00 Master v2.xlsx
+++ b/SPC26S1 - 00 Master v2.xlsx
@@ -279,7 +279,7 @@
     <t>Row order - timely filing deadline</t>
   </si>
   <si>
-    <t>Sorted the same way as the monthly workbooks: by Days Until Deadline, most urgent first, so the two views line up. A negative number means the filing window has already closed; a blank means no limit is on file. The counts below are as at 19 September 2026, and the row order is a snapshot - sort ascending on Days Until Deadline to bring it up to date.</t>
+    <t>Sorted the same way as the monthly workbooks: by Days Until Deadline, most urgent first, so the two views line up. A negative number means the filing window has already closed; a blank means no limit is on file. The counts below update automatically, and the row order is a snapshot - sort ascending on Days Until Deadline to bring it up to date.</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 22</t>
@@ -11753,8 +11753,9 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
+      <c r="A3" s="2" t="str">
+        <f>"Every one of the "&amp;COUNTA('All Claims'!$D$2:$D$2000)&amp;" claims for 2026 S1, all specialties and all six months in one place, on the 'All Claims' tab."</f>
+        <v>Every one of the 476 claims for 2026 S1, all specialties and all six months in one place, on the 'All Claims' tab.</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -11771,28 +11772,33 @@
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
+      <c r="A7" s="2" t="str">
+        <f>"    1 - Due in 5 days or less: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;=0",'All Claims'!$L$2:$L$2000,"&lt;=5")</f>
+        <v>    1 - Due in 5 days or less: 1</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
+      <c r="A8" s="2" t="str">
+        <f>"    2 - Due in 6-30 days: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;5",'All Claims'!$L$2:$L$2000,"&lt;=30")</f>
+        <v>    2 - Due in 6-30 days: 9</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
+      <c r="A9" s="2" t="str">
+        <f>"    3 - Due in 31+ days: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;30")</f>
+        <v>    3 - Due in 31+ days: 149</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
+      <c r="A10" s="2" t="str">
+        <f>"    4 - Past deadline: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&lt;0")</f>
+        <v>    4 - Past deadline: 274</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
+      <c r="A11" s="2" t="str">
+        <f>"    5 - No limit on file: "&amp;COUNTIFS('All Claims'!$D$2:$D$2000,"&lt;&gt;",'All Claims'!$L$2:$L$2000,"")</f>
+        <v>    5 - No limit on file: 43</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">

--- a/SPC26S1 - 00 Master v2.xlsx
+++ b/SPC26S1 - 00 Master v2.xlsx
@@ -3504,7 +3504,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3687,9 +3687,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFF9933"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3711,6 +3715,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11738,7 +11749,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -11949,14 +11960,14 @@
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Under Review - orange</t>
+          <t xml:space="preserve">    Under Review - bright orange, bold (follow up on these)</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Denied - red</t>
+          <t xml:space="preserve">    Denied, not worked yet (Latest Date Worked empty) - red</t>
         </is>
       </c>
     </row>
@@ -11976,6 +11987,13 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied, already worked (Latest Date Worked filled in) - light pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Any other status is left unshaded.</t>
         </is>
@@ -12019,6 +12037,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
     <cfRule type="expression" dxfId="22" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="23" priority="9">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69059,7 +69082,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="21">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="21" priority="22">
       <formula>TRIM($A2)="Rejected"</formula>

--- a/SPC26S1 - 00 Master v2.xlsx
+++ b/SPC26S1 - 00 Master v2.xlsx
@@ -279,7 +279,7 @@
     <t>Row order - timely filing deadline</t>
   </si>
   <si>
-    <t>Sorted by Days Until Deadline, most urgent first, except that Finalized claims with a Latest Date Worked are moved to the bottom (still in deadline order among themselves). A negative number means the filing window has already closed; a blank means no limit is on file. The counts below update automatically, and the row order is a snapshot - to bring it up to date, sort ascending on Days Until Deadline and then move the Finalized rows with a Latest Date Worked back to the bottom.</t>
+    <t>Sorted by Days Until Deadline, most urgent first, except that Finalized claims with a Latest Date Worked are moved to the bottom (still in deadline order among themselves). A negative number means the filing window has already closed; a blank means no limit is on file. The counts below update automatically (Finalized claims with a Latest Date Worked have their deadline cells left empty and are not counted), and the row order is a snapshot - to bring it up to date, sort ascending on Days Until Deadline and then move the Finalized rows with a Latest Date Worked back to the bottom.</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 22</t>
@@ -11785,31 +11785,31 @@
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
         <f>"    1 - Due in 5 days or less: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;=0",'All Claims'!$L$2:$L$2000,"&lt;=5")</f>
-        <v>    1 - Due in 5 days or less: 1</v>
+        <v>    1 - Due in 5 days or less: 0</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
         <f>"    2 - Due in 6-30 days: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;5",'All Claims'!$L$2:$L$2000,"&lt;=30")</f>
-        <v>    2 - Due in 6-30 days: 9</v>
+        <v>    2 - Due in 6-30 days: 5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
         <f>"    3 - Due in 31+ days: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&gt;30")</f>
-        <v>    3 - Due in 31+ days: 149</v>
+        <v>    3 - Due in 31+ days: 123</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
         <f>"    4 - Past deadline: "&amp;COUNTIFS('All Claims'!$L$2:$L$2000,"&lt;0")</f>
-        <v>    4 - Past deadline: 274</v>
+        <v>    4 - Past deadline: 210</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f>"    5 - No limit on file: "&amp;COUNTIFS('All Claims'!$D$2:$D$2000,"&lt;&gt;",'All Claims'!$L$2:$L$2000,"")</f>
-        <v>    5 - No limit on file: 43</v>
+        <f>"    5 - No limit on file: "&amp;SUMPRODUCT(('All Claims'!$D$2:$D$2000&lt;&gt;"")*('All Claims'!$L$2:$L$2000="")*(1-(TRIM('All Claims'!$A$2:$A$2000)="Finalized")*('All Claims'!$K$2:$K$2000&lt;&gt;"")))</f>
+        <v>    5 - No limit on file: 42</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -12258,14 +12258,15 @@
         <v>-207</v>
       </c>
       <c r="M2" s="11" t="str">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N2" s="11" t="str">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O2" s="9">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,3,16))</f>
         <v>46097</v>
       </c>
       <c r="P2" s="8" t="s">
@@ -12376,14 +12377,15 @@
         <v>-187</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-187</v>
       </c>
       <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+60-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+60-TODAY()))</f>
         <v>-155</v>
       </c>
       <c r="O3" s="9">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,4,5))</f>
         <v>46117</v>
       </c>
       <c r="P3" s="8" t="s">
@@ -12502,14 +12504,15 @@
         <v>-187</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-187</v>
       </c>
       <c r="N4" s="11">
-        <f ca="1">IF($C4="","",$C4+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+540-TODAY()))</f>
         <v>357</v>
       </c>
       <c r="O4" s="9">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,4,5))</f>
         <v>46117</v>
       </c>
       <c r="P4" s="8" t="s">
@@ -12628,14 +12631,15 @@
         <v>-187</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($F5="","",$F5+90-TODAY()))</f>
         <v>-187</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+540-TODAY()))</f>
         <v>378</v>
       </c>
       <c r="O5" s="9">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,4,5))</f>
         <v>46117</v>
       </c>
       <c r="P5" s="8" t="s">
@@ -12754,14 +12758,15 @@
         <v>-186</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="N6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>203</v>
       </c>
       <c r="O6" s="9">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,4,6))</f>
         <v>46118</v>
       </c>
       <c r="P6" s="8" t="s">
@@ -12872,14 +12877,15 @@
         <v>-185</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+90-TODAY()))</f>
         <v>-185</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>124</v>
       </c>
       <c r="O7" s="9">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,4,7))</f>
         <v>46119</v>
       </c>
       <c r="P7" s="8" t="s">
@@ -12990,14 +12996,15 @@
         <v>-184</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+90-TODAY()))</f>
         <v>-184</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($C8="","",$C8+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+540-TODAY()))</f>
         <v>435</v>
       </c>
       <c r="O8" s="9">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,4,8))</f>
         <v>46120</v>
       </c>
       <c r="P8" s="8" t="s">
@@ -13108,14 +13115,15 @@
         <v>-184</v>
       </c>
       <c r="M9" s="11" t="str">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N9" s="11" t="str">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O9" s="9">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,4,8))</f>
         <v>46120</v>
       </c>
       <c r="P9" s="8" t="s">
@@ -13228,14 +13236,15 @@
         <v>-183</v>
       </c>
       <c r="M10" s="11">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+180-TODAY()))</f>
         <v>17</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O10" s="9">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,4,9))</f>
         <v>46121</v>
       </c>
       <c r="P10" s="8" t="s">
@@ -13346,14 +13355,15 @@
         <v>-183</v>
       </c>
       <c r="M11" s="11">
-        <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($F11="","",$F11+90-TODAY()))</f>
         <v>-183</v>
       </c>
       <c r="N11" s="11">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+180-TODAY()))</f>
         <v>-12</v>
       </c>
       <c r="O11" s="9">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,4,9))</f>
         <v>46121</v>
       </c>
       <c r="P11" s="8" t="s">
@@ -13464,14 +13474,15 @@
         <v>-183</v>
       </c>
       <c r="M12" s="11">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+180-TODAY()))</f>
         <v>32</v>
       </c>
       <c r="N12" s="11">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="O12" s="9">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,4,9))</f>
         <v>46121</v>
       </c>
       <c r="P12" s="8" t="s">
@@ -13584,14 +13595,15 @@
         <v>-179</v>
       </c>
       <c r="M13" s="11">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+180-TODAY()))</f>
         <v>-79</v>
       </c>
       <c r="N13" s="11">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>106</v>
       </c>
       <c r="O13" s="9">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,4,13))</f>
         <v>46125</v>
       </c>
       <c r="P13" s="8" t="s">
@@ -13704,14 +13716,15 @@
         <v>-179</v>
       </c>
       <c r="M14" s="11">
-        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($F14="","",$F14+90-TODAY()))</f>
         <v>-179</v>
       </c>
       <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
         <v>-55</v>
       </c>
       <c r="O14" s="9">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,4,13))</f>
         <v>46125</v>
       </c>
       <c r="P14" s="8" t="s">
@@ -13822,14 +13835,15 @@
         <v>-178</v>
       </c>
       <c r="M15" s="11">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>194</v>
       </c>
       <c r="N15" s="11">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>194</v>
       </c>
       <c r="O15" s="9">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,4,14))</f>
         <v>46126</v>
       </c>
       <c r="P15" s="8" t="s">
@@ -13940,14 +13954,15 @@
         <v>-178</v>
       </c>
       <c r="M16" s="11">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($F16="","",$F16+90-TODAY()))</f>
         <v>-178</v>
       </c>
       <c r="N16" s="11">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="O16" s="9">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,4,14))</f>
         <v>46126</v>
       </c>
       <c r="P16" s="8" t="s">
@@ -14064,14 +14079,15 @@
         <v>-178</v>
       </c>
       <c r="M17" s="11">
-        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($F17="","",$F17+90-TODAY()))</f>
         <v>-178</v>
       </c>
       <c r="N17" s="11" t="str">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O17" s="9">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,4,14))</f>
         <v>46126</v>
       </c>
       <c r="P17" s="8" t="s">
@@ -14182,14 +14198,15 @@
         <v>-177</v>
       </c>
       <c r="M18" s="11">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
         <v>39</v>
       </c>
       <c r="N18" s="11">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>224</v>
       </c>
       <c r="O18" s="9">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,4,15))</f>
         <v>46127</v>
       </c>
       <c r="P18" s="8" t="s">
@@ -14302,14 +14319,15 @@
         <v>-171</v>
       </c>
       <c r="M19" s="11">
-        <f ca="1">IF($F19="","",$F19+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($F19="","",$F19+90-TODAY()))</f>
         <v>-171</v>
       </c>
       <c r="N19" s="11">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v>125</v>
       </c>
       <c r="O19" s="9">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,4,21))</f>
         <v>46133</v>
       </c>
       <c r="P19" s="8" t="s">
@@ -14420,14 +14438,15 @@
         <v>-171</v>
       </c>
       <c r="M20" s="11">
-        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($F20="","",$F20+90-TODAY()))</f>
         <v>-171</v>
       </c>
       <c r="N20" s="11">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="O20" s="9">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,4,21))</f>
         <v>46133</v>
       </c>
       <c r="P20" s="8" t="s">
@@ -14540,14 +14559,15 @@
         <v>-170</v>
       </c>
       <c r="M21" s="11">
-        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($F21="","",$F21+90-TODAY()))</f>
         <v>-170</v>
       </c>
       <c r="N21" s="11">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+365-TODAY()))</f>
         <v>155</v>
       </c>
       <c r="O21" s="9">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2026,4,22))</f>
         <v>46134</v>
       </c>
       <c r="P21" s="8" t="s">
@@ -14660,14 +14680,15 @@
         <v>-169</v>
       </c>
       <c r="M22" s="11">
-        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($F22="","",$F22+90-TODAY()))</f>
         <v>-169</v>
       </c>
       <c r="N22" s="11">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+365-TODAY()))</f>
         <v>224</v>
       </c>
       <c r="O22" s="9">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,4,23))</f>
         <v>46135</v>
       </c>
       <c r="P22" s="8" t="s">
@@ -14782,14 +14803,15 @@
         <v>-169</v>
       </c>
       <c r="M23" s="11">
-        <f ca="1">IF($F23="","",$F23+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($F23="","",$F23+90-TODAY()))</f>
         <v>-169</v>
       </c>
       <c r="N23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
         <v>113</v>
       </c>
       <c r="O23" s="9">
+        <f>IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",DATE(2026,4,23))</f>
         <v>46135</v>
       </c>
       <c r="P23" s="8" t="s">
@@ -14900,14 +14922,15 @@
         <v>-168</v>
       </c>
       <c r="M24" s="11">
-        <f ca="1">IF($C24="","",$C24+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+90-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="N24" s="11">
-        <f ca="1">IF($C24="","",$C24+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+90-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="O24" s="9">
+        <f>IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",DATE(2026,4,24))</f>
         <v>46136</v>
       </c>
       <c r="P24" s="8" t="s">
@@ -15026,14 +15049,15 @@
         <v>-166</v>
       </c>
       <c r="M25" s="11">
-        <f ca="1">IF($F25="","",$F25+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($F25="","",$F25+90-TODAY()))</f>
         <v>-166</v>
       </c>
       <c r="N25" s="11">
-        <f ca="1">IF($C25="","",$C25+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+540-TODAY()))</f>
         <v>347</v>
       </c>
       <c r="O25" s="9">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,4,26))</f>
         <v>46138</v>
       </c>
       <c r="P25" s="8" t="s">
@@ -15152,14 +15176,15 @@
         <v>-165</v>
       </c>
       <c r="M26" s="11">
-        <f ca="1">IF($F26="","",$F26+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($F26="","",$F26+90-TODAY()))</f>
         <v>-165</v>
       </c>
       <c r="N26" s="11">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
         <v>189</v>
       </c>
       <c r="O26" s="9">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,4,27))</f>
         <v>46139</v>
       </c>
       <c r="P26" s="8" t="s">
@@ -15270,14 +15295,15 @@
         <v>-165</v>
       </c>
       <c r="M27" s="11">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
         <v>348</v>
       </c>
       <c r="N27" s="11">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
         <v>348</v>
       </c>
       <c r="O27" s="9">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2026,4,27))</f>
         <v>46139</v>
       </c>
       <c r="P27" s="8" t="s">
@@ -15390,14 +15416,15 @@
         <v>-163</v>
       </c>
       <c r="M28" s="11">
-        <f ca="1">IF($F28="","",$F28+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($F28="","",$F28+90-TODAY()))</f>
         <v>-163</v>
       </c>
       <c r="N28" s="11">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
         <v>127</v>
       </c>
       <c r="O28" s="9">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2026,4,29))</f>
         <v>46141</v>
       </c>
       <c r="P28" s="8" t="s">
@@ -15508,14 +15535,15 @@
         <v>-163</v>
       </c>
       <c r="M29" s="11">
-        <f ca="1">IF($C29="","",$C29+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+180-TODAY()))</f>
         <v>32</v>
       </c>
       <c r="N29" s="11">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="O29" s="9">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2026,4,29))</f>
         <v>46141</v>
       </c>
       <c r="P29" s="8" t="s">
@@ -15630,14 +15658,15 @@
         <v>-158</v>
       </c>
       <c r="M30" s="11">
-        <f ca="1">IF($F30="","",$F30+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($F30="","",$F30+90-TODAY()))</f>
         <v>-158</v>
       </c>
       <c r="N30" s="11">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
         <v>159</v>
       </c>
       <c r="O30" s="9">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2026,5,4))</f>
         <v>46146</v>
       </c>
       <c r="P30" s="8" t="s">
@@ -15748,14 +15777,15 @@
         <v>-157</v>
       </c>
       <c r="M31" s="11">
-        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+180-TODAY()))</f>
         <v>3</v>
       </c>
       <c r="N31" s="11">
-        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+180-TODAY()))</f>
         <v>3</v>
       </c>
       <c r="O31" s="9">
+        <f>IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",DATE(2026,5,5))</f>
         <v>46147</v>
       </c>
       <c r="P31" s="8" t="s">
@@ -15874,14 +15904,15 @@
         <v>-155</v>
       </c>
       <c r="M32" s="11">
-        <f ca="1">IF($F32="","",$F32+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($F32="","",$F32+90-TODAY()))</f>
         <v>-155</v>
       </c>
       <c r="N32" s="11">
-        <f ca="1">IF($C32="","",$C32+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+540-TODAY()))</f>
         <v>383</v>
       </c>
       <c r="O32" s="9">
+        <f>IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",DATE(2026,5,7))</f>
         <v>46149</v>
       </c>
       <c r="P32" s="8" t="s">
@@ -15992,14 +16023,15 @@
         <v>-152</v>
       </c>
       <c r="M33" s="11">
-        <f ca="1">IF($F33="","",$F33+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($F33="","",$F33+90-TODAY()))</f>
         <v>-152</v>
       </c>
       <c r="N33" s="11">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+365-TODAY()))</f>
         <v>209</v>
       </c>
       <c r="O33" s="9">
+        <f>IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",DATE(2026,5,10))</f>
         <v>46152</v>
       </c>
       <c r="P33" s="8" t="s">
@@ -16110,14 +16142,15 @@
         <v>-149</v>
       </c>
       <c r="M34" s="11">
-        <f ca="1">IF($F34="","",$F34+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($F34="","",$F34+90-TODAY()))</f>
         <v>-149</v>
       </c>
       <c r="N34" s="11">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
         <v>180</v>
       </c>
       <c r="O34" s="9">
+        <f>IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",DATE(2026,5,13))</f>
         <v>46155</v>
       </c>
       <c r="P34" s="8" t="s">
@@ -16230,14 +16263,15 @@
         <v>-148</v>
       </c>
       <c r="M35" s="11">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($C35="","",$C35+365-TODAY()))</f>
         <v>159</v>
       </c>
       <c r="N35" s="11">
-        <f ca="1">IF($C35="","",$C35+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($C35="","",$C35+90-TODAY()))</f>
         <v>-116</v>
       </c>
       <c r="O35" s="9">
+        <f>IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",DATE(2026,5,14))</f>
         <v>46156</v>
       </c>
       <c r="P35" s="8" t="s">
@@ -16348,14 +16382,15 @@
         <v>-148</v>
       </c>
       <c r="M36" s="11">
-        <f ca="1">IF($C36="","",$C36+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",IF($C36="","",$C36+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N36" s="11">
-        <f ca="1">IF($C36="","",$C36+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",IF($C36="","",$C36+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O36" s="9">
+        <f>IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",DATE(2026,5,14))</f>
         <v>46156</v>
       </c>
       <c r="P36" s="8" t="s">
@@ -16466,14 +16501,15 @@
         <v>-145</v>
       </c>
       <c r="M37" s="11">
-        <f ca="1">IF($F37="","",$F37+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",IF($F37="","",$F37+90-TODAY()))</f>
         <v>-145</v>
       </c>
       <c r="N37" s="11">
-        <f ca="1">IF($C37="","",$C37+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",IF($C37="","",$C37+365-TODAY()))</f>
         <v>215</v>
       </c>
       <c r="O37" s="9">
+        <f>IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",DATE(2026,5,17))</f>
         <v>46159</v>
       </c>
       <c r="P37" s="8" t="s">
@@ -16592,14 +16628,15 @@
         <v>-145</v>
       </c>
       <c r="M38" s="11">
-        <f ca="1">IF($F38="","",$F38+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",IF($F38="","",$F38+90-TODAY()))</f>
         <v>-145</v>
       </c>
       <c r="N38" s="11">
-        <f ca="1">IF($C38="","",$C38+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",IF($C38="","",$C38+365-TODAY()))</f>
         <v>288</v>
       </c>
       <c r="O38" s="9">
+        <f>IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",DATE(2026,5,17))</f>
         <v>46159</v>
       </c>
       <c r="P38" s="8" t="s">
@@ -16712,14 +16749,15 @@
         <v>-144</v>
       </c>
       <c r="M39" s="11">
-        <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",IF($C39="","",$C39+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N39" s="11">
-        <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",IF($C39="","",$C39+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O39" s="9">
+        <f>IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",DATE(2026,5,18))</f>
         <v>46160</v>
       </c>
       <c r="P39" s="8" t="s">
@@ -16832,14 +16870,15 @@
         <v>-143</v>
       </c>
       <c r="M40" s="11">
-        <f ca="1">IF($F40="","",$F40+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",IF($F40="","",$F40+90-TODAY()))</f>
         <v>-143</v>
       </c>
       <c r="N40" s="11">
-        <f ca="1">IF($C40="","",$C40+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",IF($C40="","",$C40+365-TODAY()))</f>
         <v>162</v>
       </c>
       <c r="O40" s="9">
+        <f>IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",DATE(2026,5,19))</f>
         <v>46161</v>
       </c>
       <c r="P40" s="8" t="s">
@@ -16950,14 +16989,15 @@
         <v>-142</v>
       </c>
       <c r="M41" s="11">
-        <f ca="1">IF($C41="","",$C41+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",IF($C41="","",$C41+180-TODAY()))</f>
         <v>-18</v>
       </c>
       <c r="N41" s="11">
-        <f ca="1">IF($C41="","",$C41+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",IF($C41="","",$C41+365-TODAY()))</f>
         <v>167</v>
       </c>
       <c r="O41" s="9">
+        <f>IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",DATE(2026,5,20))</f>
         <v>46162</v>
       </c>
       <c r="P41" s="8" t="s">
@@ -17072,14 +17112,15 @@
         <v>-141</v>
       </c>
       <c r="M42" s="11">
-        <f ca="1">IF($C42="","",$C42+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",IF($C42="","",$C42+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N42" s="11">
-        <f ca="1">IF($C42="","",$C42+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",IF($C42="","",$C42+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O42" s="9">
+        <f>IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",DATE(2026,5,21))</f>
         <v>46163</v>
       </c>
       <c r="P42" s="8" t="s">
@@ -17190,14 +17231,15 @@
         <v>-141</v>
       </c>
       <c r="M43" s="11">
-        <f ca="1">IF($C43="","",$C43+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",IF($C43="","",$C43+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N43" s="11">
-        <f ca="1">IF($C43="","",$C43+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",IF($C43="","",$C43+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O43" s="9">
+        <f>IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",DATE(2026,5,21))</f>
         <v>46163</v>
       </c>
       <c r="P43" s="8" t="s">
@@ -17308,14 +17350,15 @@
         <v>-135</v>
       </c>
       <c r="M44" s="11">
-        <f ca="1">IF($F44="","",$F44+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A44)="Finalized",$K44&lt;&gt;""),"",IF($F44="","",$F44+90-TODAY()))</f>
         <v>-135</v>
       </c>
       <c r="N44" s="11">
-        <f ca="1">IF($C44="","",$C44+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A44)="Finalized",$K44&lt;&gt;""),"",IF($C44="","",$C44+365-TODAY()))</f>
         <v>273</v>
       </c>
       <c r="O44" s="9">
+        <f>IF(AND(TRIM($A44)="Finalized",$K44&lt;&gt;""),"",DATE(2026,5,27))</f>
         <v>46169</v>
       </c>
       <c r="P44" s="8" t="s">
@@ -17430,14 +17473,15 @@
         <v>-134</v>
       </c>
       <c r="M45" s="11">
-        <f ca="1">IF($C45="","",$C45+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A45)="Finalized",$K45&lt;&gt;""),"",IF($C45="","",$C45+365-TODAY()))</f>
         <v>250</v>
       </c>
       <c r="N45" s="11">
-        <f ca="1">IF($C45="","",$C45+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A45)="Finalized",$K45&lt;&gt;""),"",IF($C45="","",$C45+365-TODAY()))</f>
         <v>250</v>
       </c>
       <c r="O45" s="9">
+        <f>IF(AND(TRIM($A45)="Finalized",$K45&lt;&gt;""),"",DATE(2026,5,28))</f>
         <v>46170</v>
       </c>
       <c r="P45" s="8" t="s">
@@ -17550,14 +17594,15 @@
         <v>-131</v>
       </c>
       <c r="M46" s="11">
-        <f ca="1">IF($C46="","",$C46+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A46)="Finalized",$K46&lt;&gt;""),"",IF($C46="","",$C46+180-TODAY()))</f>
         <v>93</v>
       </c>
       <c r="N46" s="11">
-        <f ca="1">IF($C46="","",$C46+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A46)="Finalized",$K46&lt;&gt;""),"",IF($C46="","",$C46+365-TODAY()))</f>
         <v>278</v>
       </c>
       <c r="O46" s="9">
+        <f>IF(AND(TRIM($A46)="Finalized",$K46&lt;&gt;""),"",DATE(2026,5,31))</f>
         <v>46173</v>
       </c>
       <c r="P46" s="8" t="s">
@@ -17678,14 +17723,15 @@
         <v>-130</v>
       </c>
       <c r="M47" s="11">
-        <f ca="1">IF($F47="","",$F47+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A47)="Finalized",$K47&lt;&gt;""),"",IF($F47="","",$F47+90-TODAY()))</f>
         <v>-130</v>
       </c>
       <c r="N47" s="11">
-        <f ca="1">IF($C47="","",$C47+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A47)="Finalized",$K47&lt;&gt;""),"",IF($C47="","",$C47+180-TODAY()))</f>
         <v>-11</v>
       </c>
       <c r="O47" s="9">
+        <f>IF(AND(TRIM($A47)="Finalized",$K47&lt;&gt;""),"",DATE(2026,6,1))</f>
         <v>46174</v>
       </c>
       <c r="P47" s="8" t="s">
@@ -17802,14 +17848,15 @@
         <v>-129</v>
       </c>
       <c r="M48" s="11">
-        <f ca="1">IF($F48="","",$F48+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A48)="Finalized",$K48&lt;&gt;""),"",IF($F48="","",$F48+90-TODAY()))</f>
         <v>-129</v>
       </c>
       <c r="N48" s="11">
-        <f ca="1">IF($C48="","",$C48+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A48)="Finalized",$K48&lt;&gt;""),"",IF($C48="","",$C48+365-TODAY()))</f>
         <v>195</v>
       </c>
       <c r="O48" s="9">
+        <f>IF(AND(TRIM($A48)="Finalized",$K48&lt;&gt;""),"",DATE(2026,6,2))</f>
         <v>46175</v>
       </c>
       <c r="P48" s="8" t="s">
@@ -17920,14 +17967,15 @@
         <v>-129</v>
       </c>
       <c r="M49" s="11">
-        <f ca="1">IF($F49="","",$F49+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A49)="Finalized",$K49&lt;&gt;""),"",IF($F49="","",$F49+90-TODAY()))</f>
         <v>-129</v>
       </c>
       <c r="N49" s="11">
-        <f ca="1">IF($C49="","",$C49+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A49)="Finalized",$K49&lt;&gt;""),"",IF($C49="","",$C49+180-TODAY()))</f>
         <v>80</v>
       </c>
       <c r="O49" s="9">
+        <f>IF(AND(TRIM($A49)="Finalized",$K49&lt;&gt;""),"",DATE(2026,6,2))</f>
         <v>46175</v>
       </c>
       <c r="P49" s="8" t="s">
@@ -18044,14 +18092,15 @@
         <v>-128</v>
       </c>
       <c r="M50" s="11">
-        <f ca="1">IF($C50="","",$C50+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A50)="Finalized",$K50&lt;&gt;""),"",IF($C50="","",$C50+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="N50" s="11">
-        <f ca="1">IF($C50="","",$C50+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A50)="Finalized",$K50&lt;&gt;""),"",IF($C50="","",$C50+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O50" s="9">
+        <f>IF(AND(TRIM($A50)="Finalized",$K50&lt;&gt;""),"",DATE(2026,6,3))</f>
         <v>46176</v>
       </c>
       <c r="P50" s="8" t="s">
@@ -18162,14 +18211,15 @@
         <v>-127</v>
       </c>
       <c r="M51" s="11">
-        <f ca="1">IF($C51="","",$C51+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A51)="Finalized",$K51&lt;&gt;""),"",IF($C51="","",$C51+365-TODAY()))</f>
         <v>182</v>
       </c>
       <c r="N51" s="11">
-        <f ca="1">IF($C51="","",$C51+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A51)="Finalized",$K51&lt;&gt;""),"",IF($C51="","",$C51+365-TODAY()))</f>
         <v>182</v>
       </c>
       <c r="O51" s="9">
+        <f>IF(AND(TRIM($A51)="Finalized",$K51&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P51" s="8" t="s">
@@ -18280,14 +18330,15 @@
         <v>-127</v>
       </c>
       <c r="M52" s="11">
-        <f ca="1">IF($C52="","",$C52+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A52)="Finalized",$K52&lt;&gt;""),"",IF($C52="","",$C52+180-TODAY()))</f>
         <v>72</v>
       </c>
       <c r="N52" s="11">
-        <f ca="1">IF($C52="","",$C52+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A52)="Finalized",$K52&lt;&gt;""),"",IF($C52="","",$C52+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="O52" s="9">
+        <f>IF(AND(TRIM($A52)="Finalized",$K52&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P52" s="8" t="s">
@@ -18400,14 +18451,15 @@
         <v>-127</v>
       </c>
       <c r="M53" s="11">
-        <f ca="1">IF($F53="","",$F53+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A53)="Finalized",$K53&lt;&gt;""),"",IF($F53="","",$F53+90-TODAY()))</f>
         <v>-127</v>
       </c>
       <c r="N53" s="11">
-        <f ca="1">IF($C53="","",$C53+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A53)="Finalized",$K53&lt;&gt;""),"",IF($C53="","",$C53+540-TODAY()))</f>
         <v>333</v>
       </c>
       <c r="O53" s="9">
+        <f>IF(AND(TRIM($A53)="Finalized",$K53&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P53" s="8" t="s">
@@ -18518,14 +18570,15 @@
         <v>-127</v>
       </c>
       <c r="M54" s="11">
-        <f ca="1">IF($F54="","",$F54+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A54)="Finalized",$K54&lt;&gt;""),"",IF($F54="","",$F54+365-TODAY()))</f>
         <v>118</v>
       </c>
       <c r="N54" s="11">
-        <f ca="1">IF($F54="","",$F54+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A54)="Finalized",$K54&lt;&gt;""),"",IF($F54="","",$F54+365-TODAY()))</f>
         <v>118</v>
       </c>
       <c r="O54" s="9">
+        <f>IF(AND(TRIM($A54)="Finalized",$K54&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P54" s="8" t="s">
@@ -18638,14 +18691,15 @@
         <v>-127</v>
       </c>
       <c r="M55" s="11">
-        <f ca="1">IF($F55="","",$F55+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A55)="Finalized",$K55&lt;&gt;""),"",IF($F55="","",$F55+90-TODAY()))</f>
         <v>-127</v>
       </c>
       <c r="N55" s="11">
-        <f ca="1">IF($C55="","",$C55+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A55)="Finalized",$K55&lt;&gt;""),"",IF($C55="","",$C55+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="O55" s="9">
+        <f>IF(AND(TRIM($A55)="Finalized",$K55&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P55" s="8" t="s">
@@ -18758,14 +18812,15 @@
         <v>-122</v>
       </c>
       <c r="M56" s="11">
-        <f ca="1">IF($C56="","",$C56+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A56)="Finalized",$K56&lt;&gt;""),"",IF($C56="","",$C56+365-TODAY()))</f>
         <v>182</v>
       </c>
       <c r="N56" s="11">
-        <f ca="1">IF($C56="","",$C56+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A56)="Finalized",$K56&lt;&gt;""),"",IF($C56="","",$C56+365-TODAY()))</f>
         <v>182</v>
       </c>
       <c r="O56" s="9">
+        <f>IF(AND(TRIM($A56)="Finalized",$K56&lt;&gt;""),"",DATE(2026,6,9))</f>
         <v>46182</v>
       </c>
       <c r="P56" s="8" t="s">
@@ -18876,14 +18931,15 @@
         <v>-121</v>
       </c>
       <c r="M57" s="11">
-        <f ca="1">IF($F57="","",$F57+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A57)="Finalized",$K57&lt;&gt;""),"",IF($F57="","",$F57+90-TODAY()))</f>
         <v>-121</v>
       </c>
       <c r="N57" s="11">
-        <f ca="1">IF($C57="","",$C57+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A57)="Finalized",$K57&lt;&gt;""),"",IF($C57="","",$C57+540-TODAY()))</f>
         <v>344</v>
       </c>
       <c r="O57" s="9">
+        <f>IF(AND(TRIM($A57)="Finalized",$K57&lt;&gt;""),"",DATE(2026,6,10))</f>
         <v>46183</v>
       </c>
       <c r="P57" s="8" t="s">
@@ -18998,14 +19054,15 @@
         <v>-121</v>
       </c>
       <c r="M58" s="11">
-        <f ca="1">IF($F58="","",$F58+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A58)="Finalized",$K58&lt;&gt;""),"",IF($F58="","",$F58+90-TODAY()))</f>
         <v>-121</v>
       </c>
       <c r="N58" s="11">
-        <f ca="1">IF($C58="","",$C58+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A58)="Finalized",$K58&lt;&gt;""),"",IF($C58="","",$C58+540-TODAY()))</f>
         <v>456</v>
       </c>
       <c r="O58" s="9">
+        <f>IF(AND(TRIM($A58)="Finalized",$K58&lt;&gt;""),"",DATE(2026,6,10))</f>
         <v>46183</v>
       </c>
       <c r="P58" s="8" t="s">
@@ -19118,14 +19175,15 @@
         <v>-121</v>
       </c>
       <c r="M59" s="11">
-        <f ca="1">IF($C59="","",$C59+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A59)="Finalized",$K59&lt;&gt;""),"",IF($C59="","",$C59+180-TODAY()))</f>
         <v>3</v>
       </c>
       <c r="N59" s="11">
-        <f ca="1">IF($C59="","",$C59+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A59)="Finalized",$K59&lt;&gt;""),"",IF($C59="","",$C59+365-TODAY()))</f>
         <v>188</v>
       </c>
       <c r="O59" s="9">
+        <f>IF(AND(TRIM($A59)="Finalized",$K59&lt;&gt;""),"",DATE(2026,6,10))</f>
         <v>46183</v>
       </c>
       <c r="P59" s="8" t="s">
@@ -19238,14 +19296,15 @@
         <v>-117</v>
       </c>
       <c r="M60" s="11">
-        <f ca="1">IF($F60="","",$F60+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A60)="Finalized",$K60&lt;&gt;""),"",IF($F60="","",$F60+90-TODAY()))</f>
         <v>-117</v>
       </c>
       <c r="N60" s="11">
-        <f ca="1">IF($C60="","",$C60+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A60)="Finalized",$K60&lt;&gt;""),"",IF($C60="","",$C60+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="O60" s="9">
+        <f>IF(AND(TRIM($A60)="Finalized",$K60&lt;&gt;""),"",DATE(2026,6,14))</f>
         <v>46187</v>
       </c>
       <c r="P60" s="8" t="s">
@@ -19358,14 +19417,15 @@
         <v>-116</v>
       </c>
       <c r="M61" s="11">
-        <f ca="1">IF($C61="","",$C61+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A61)="Finalized",$K61&lt;&gt;""),"",IF($C61="","",$C61+180-TODAY()))</f>
         <v>11</v>
       </c>
       <c r="N61" s="11">
-        <f ca="1">IF($C61="","",$C61+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A61)="Finalized",$K61&lt;&gt;""),"",IF($C61="","",$C61+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="O61" s="9">
+        <f>IF(AND(TRIM($A61)="Finalized",$K61&lt;&gt;""),"",DATE(2026,6,15))</f>
         <v>46188</v>
       </c>
       <c r="P61" s="8" t="s">
@@ -19478,14 +19538,15 @@
         <v>-116</v>
       </c>
       <c r="M62" s="11">
-        <f ca="1">IF($C62="","",$C62+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A62)="Finalized",$K62&lt;&gt;""),"",IF($C62="","",$C62+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="N62" s="11">
-        <f ca="1">IF($C62="","",$C62+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A62)="Finalized",$K62&lt;&gt;""),"",IF($C62="","",$C62+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="O62" s="9">
+        <f>IF(AND(TRIM($A62)="Finalized",$K62&lt;&gt;""),"",DATE(2026,6,15))</f>
         <v>46188</v>
       </c>
       <c r="P62" s="8" t="s">
@@ -19600,14 +19661,15 @@
         <v>-115</v>
       </c>
       <c r="M63" s="11">
-        <f ca="1">IF($C63="","",$C63+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A63)="Finalized",$K63&lt;&gt;""),"",IF($C63="","",$C63+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="N63" s="11">
-        <f ca="1">IF($C63="","",$C63+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A63)="Finalized",$K63&lt;&gt;""),"",IF($C63="","",$C63+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="O63" s="9">
+        <f>IF(AND(TRIM($A63)="Finalized",$K63&lt;&gt;""),"",DATE(2026,6,16))</f>
         <v>46189</v>
       </c>
       <c r="P63" s="8" t="s">
@@ -19720,14 +19782,15 @@
         <v>-115</v>
       </c>
       <c r="M64" s="11">
-        <f ca="1">IF($C64="","",$C64+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A64)="Finalized",$K64&lt;&gt;""),"",IF($C64="","",$C64+180-TODAY()))</f>
         <v>37</v>
       </c>
       <c r="N64" s="11">
-        <f ca="1">IF($C64="","",$C64+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A64)="Finalized",$K64&lt;&gt;""),"",IF($C64="","",$C64+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="O64" s="9">
+        <f>IF(AND(TRIM($A64)="Finalized",$K64&lt;&gt;""),"",DATE(2026,6,16))</f>
         <v>46189</v>
       </c>
       <c r="P64" s="8" t="s">
@@ -19838,14 +19901,15 @@
         <v>-115</v>
       </c>
       <c r="M65" s="11">
-        <f ca="1">IF($F65="","",$F65+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A65)="Finalized",$K65&lt;&gt;""),"",IF($F65="","",$F65+90-TODAY()))</f>
         <v>-115</v>
       </c>
       <c r="N65" s="11">
-        <f ca="1">IF($C65="","",$C65+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A65)="Finalized",$K65&lt;&gt;""),"",IF($C65="","",$C65+180-TODAY()))</f>
         <v>-10</v>
       </c>
       <c r="O65" s="9">
+        <f>IF(AND(TRIM($A65)="Finalized",$K65&lt;&gt;""),"",DATE(2026,6,16))</f>
         <v>46189</v>
       </c>
       <c r="P65" s="8" t="s">
@@ -19958,14 +20022,15 @@
         <v>-115</v>
       </c>
       <c r="M66" s="11">
-        <f ca="1">IF($F66="","",$F66+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A66)="Finalized",$K66&lt;&gt;""),"",IF($F66="","",$F66+90-TODAY()))</f>
         <v>-115</v>
       </c>
       <c r="N66" s="11">
-        <f ca="1">IF($C66="","",$C66+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A66)="Finalized",$K66&lt;&gt;""),"",IF($C66="","",$C66+540-TODAY()))</f>
         <v>456</v>
       </c>
       <c r="O66" s="9">
+        <f>IF(AND(TRIM($A66)="Finalized",$K66&lt;&gt;""),"",DATE(2026,6,16))</f>
         <v>46189</v>
       </c>
       <c r="P66" s="8" t="s">
@@ -20082,14 +20147,15 @@
         <v>-113</v>
       </c>
       <c r="M67" s="11">
-        <f ca="1">IF($C67="","",$C67+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A67)="Finalized",$K67&lt;&gt;""),"",IF($C67="","",$C67+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="N67" s="11">
-        <f ca="1">IF($C67="","",$C67+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A67)="Finalized",$K67&lt;&gt;""),"",IF($C67="","",$C67+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="O67" s="9">
+        <f>IF(AND(TRIM($A67)="Finalized",$K67&lt;&gt;""),"",DATE(2026,6,18))</f>
         <v>46191</v>
       </c>
       <c r="P67" s="8" t="s">
@@ -20200,14 +20266,15 @@
         <v>-113</v>
       </c>
       <c r="M68" s="11">
-        <f ca="1">IF($F68="","",$F68+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A68)="Finalized",$K68&lt;&gt;""),"",IF($F68="","",$F68+90-TODAY()))</f>
         <v>-113</v>
       </c>
       <c r="N68" s="11">
-        <f ca="1">IF($C68="","",$C68+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A68)="Finalized",$K68&lt;&gt;""),"",IF($C68="","",$C68+365-TODAY()))</f>
         <v>185</v>
       </c>
       <c r="O68" s="9">
+        <f>IF(AND(TRIM($A68)="Finalized",$K68&lt;&gt;""),"",DATE(2026,6,18))</f>
         <v>46191</v>
       </c>
       <c r="P68" s="8" t="s">
@@ -20318,14 +20385,15 @@
         <v>-109</v>
       </c>
       <c r="M69" s="11">
-        <f ca="1">IF($C69="","",$C69+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A69)="Finalized",$K69&lt;&gt;""),"",IF($C69="","",$C69+365-TODAY()))</f>
         <v>187</v>
       </c>
       <c r="N69" s="11">
-        <f ca="1">IF($C69="","",$C69+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A69)="Finalized",$K69&lt;&gt;""),"",IF($C69="","",$C69+365-TODAY()))</f>
         <v>187</v>
       </c>
       <c r="O69" s="9">
+        <f>IF(AND(TRIM($A69)="Finalized",$K69&lt;&gt;""),"",DATE(2026,6,22))</f>
         <v>46195</v>
       </c>
       <c r="P69" s="8" t="s">
@@ -20440,14 +20508,15 @@
         <v>-107</v>
       </c>
       <c r="M70" s="11">
-        <f ca="1">IF($C70="","",$C70+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A70)="Finalized",$K70&lt;&gt;""),"",IF($C70="","",$C70+180-TODAY()))</f>
         <v>92</v>
       </c>
       <c r="N70" s="11">
-        <f ca="1">IF($C70="","",$C70+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A70)="Finalized",$K70&lt;&gt;""),"",IF($C70="","",$C70+365-TODAY()))</f>
         <v>277</v>
       </c>
       <c r="O70" s="9">
+        <f>IF(AND(TRIM($A70)="Finalized",$K70&lt;&gt;""),"",DATE(2026,6,24))</f>
         <v>46197</v>
       </c>
       <c r="P70" s="8" t="s">
@@ -20566,14 +20635,15 @@
         <v>-106</v>
       </c>
       <c r="M71" s="11">
-        <f ca="1">IF($C71="","",$C71+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A71)="Finalized",$K71&lt;&gt;""),"",IF($C71="","",$C71+180-TODAY()))</f>
         <v>73</v>
       </c>
       <c r="N71" s="11">
-        <f ca="1">IF($C71="","",$C71+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A71)="Finalized",$K71&lt;&gt;""),"",IF($C71="","",$C71+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O71" s="9">
+        <f>IF(AND(TRIM($A71)="Finalized",$K71&lt;&gt;""),"",DATE(2026,6,25))</f>
         <v>46198</v>
       </c>
       <c r="P71" s="8" t="s">
@@ -20686,14 +20756,15 @@
         <v>-106</v>
       </c>
       <c r="M72" s="11">
-        <f ca="1">IF($C72="","",$C72+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A72)="Finalized",$K72&lt;&gt;""),"",IF($C72="","",$C72+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="N72" s="11">
-        <f ca="1">IF($C72="","",$C72+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A72)="Finalized",$K72&lt;&gt;""),"",IF($C72="","",$C72+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O72" s="9">
+        <f>IF(AND(TRIM($A72)="Finalized",$K72&lt;&gt;""),"",DATE(2026,6,25))</f>
         <v>46198</v>
       </c>
       <c r="P72" s="8" t="s">
@@ -20804,14 +20875,15 @@
         <v>-101</v>
       </c>
       <c r="M73" s="11">
-        <f ca="1">IF($F73="","",$F73+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A73)="Finalized",$K73&lt;&gt;""),"",IF($F73="","",$F73+90-TODAY()))</f>
         <v>-101</v>
       </c>
       <c r="N73" s="11">
-        <f ca="1">IF($C73="","",$C73+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A73)="Finalized",$K73&lt;&gt;""),"",IF($C73="","",$C73+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="O73" s="9">
+        <f>IF(AND(TRIM($A73)="Finalized",$K73&lt;&gt;""),"",DATE(2026,6,30))</f>
         <v>46203</v>
       </c>
       <c r="P73" s="8" t="s">
@@ -20922,14 +20994,15 @@
         <v>-101</v>
       </c>
       <c r="M74" s="11">
-        <f ca="1">IF($C74="","",$C74+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A74)="Finalized",$K74&lt;&gt;""),"",IF($C74="","",$C74+180-TODAY()))</f>
         <v>94</v>
       </c>
       <c r="N74" s="11">
-        <f ca="1">IF($C74="","",$C74+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A74)="Finalized",$K74&lt;&gt;""),"",IF($C74="","",$C74+365-TODAY()))</f>
         <v>279</v>
       </c>
       <c r="O74" s="9">
+        <f>IF(AND(TRIM($A74)="Finalized",$K74&lt;&gt;""),"",DATE(2026,6,30))</f>
         <v>46203</v>
       </c>
       <c r="P74" s="8" t="s">
@@ -21044,14 +21117,15 @@
         <v>-100</v>
       </c>
       <c r="M75" s="11">
-        <f ca="1">IF($C75="","",$C75+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A75)="Finalized",$K75&lt;&gt;""),"",IF($C75="","",$C75+180-TODAY()))</f>
         <v>92</v>
       </c>
       <c r="N75" s="11">
-        <f ca="1">IF($C75="","",$C75+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A75)="Finalized",$K75&lt;&gt;""),"",IF($C75="","",$C75+365-TODAY()))</f>
         <v>277</v>
       </c>
       <c r="O75" s="9">
+        <f>IF(AND(TRIM($A75)="Finalized",$K75&lt;&gt;""),"",DATE(2026,7,1))</f>
         <v>46204</v>
       </c>
       <c r="P75" s="8" t="s">
@@ -21166,14 +21240,15 @@
         <v>-99</v>
       </c>
       <c r="M76" s="11">
-        <f ca="1">IF($C76="","",$C76+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A76)="Finalized",$K76&lt;&gt;""),"",IF($C76="","",$C76+180-TODAY()))</f>
         <v>-11</v>
       </c>
       <c r="N76" s="11">
-        <f ca="1">IF($C76="","",$C76+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A76)="Finalized",$K76&lt;&gt;""),"",IF($C76="","",$C76+180-TODAY()))</f>
         <v>-11</v>
       </c>
       <c r="O76" s="9">
+        <f>IF(AND(TRIM($A76)="Finalized",$K76&lt;&gt;""),"",DATE(2026,7,2))</f>
         <v>46205</v>
       </c>
       <c r="P76" s="8" t="s">
@@ -21286,14 +21361,15 @@
         <v>-96</v>
       </c>
       <c r="M77" s="11">
-        <f ca="1">IF($F77="","",$F77+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A77)="Finalized",$K77&lt;&gt;""),"",IF($F77="","",$F77+90-TODAY()))</f>
         <v>-96</v>
       </c>
       <c r="N77" s="11">
-        <f ca="1">IF($C77="","",$C77+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A77)="Finalized",$K77&lt;&gt;""),"",IF($C77="","",$C77+180-TODAY()))</f>
         <v>73</v>
       </c>
       <c r="O77" s="9">
+        <f>IF(AND(TRIM($A77)="Finalized",$K77&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P77" s="8" t="s">
@@ -21406,14 +21482,15 @@
         <v>-96</v>
       </c>
       <c r="M78" s="11">
-        <f ca="1">IF($F78="","",$F78+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A78)="Finalized",$K78&lt;&gt;""),"",IF($F78="","",$F78+90-TODAY()))</f>
         <v>-96</v>
       </c>
       <c r="N78" s="11">
-        <f ca="1">IF($C78="","",$C78+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A78)="Finalized",$K78&lt;&gt;""),"",IF($C78="","",$C78+540-TODAY()))</f>
         <v>401</v>
       </c>
       <c r="O78" s="9">
+        <f>IF(AND(TRIM($A78)="Finalized",$K78&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P78" s="8" t="s">
@@ -21534,14 +21611,15 @@
         <v>-96</v>
       </c>
       <c r="M79" s="11">
-        <f ca="1">IF($C79="","",$C79+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A79)="Finalized",$K79&lt;&gt;""),"",IF($C79="","",$C79+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="N79" s="11">
-        <f ca="1">IF($C79="","",$C79+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A79)="Finalized",$K79&lt;&gt;""),"",IF($C79="","",$C79+90-TODAY()))</f>
         <v>-52</v>
       </c>
       <c r="O79" s="9">
+        <f>IF(AND(TRIM($A79)="Finalized",$K79&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P79" s="8" t="s">
@@ -21654,14 +21732,15 @@
         <v>-95</v>
       </c>
       <c r="M80" s="11">
-        <f ca="1">IF($F80="","",$F80+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A80)="Finalized",$K80&lt;&gt;""),"",IF($F80="","",$F80+90-TODAY()))</f>
         <v>-95</v>
       </c>
       <c r="N80" s="11">
-        <f ca="1">IF($C80="","",$C80+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A80)="Finalized",$K80&lt;&gt;""),"",IF($C80="","",$C80+365-TODAY()))</f>
         <v>225</v>
       </c>
       <c r="O80" s="9">
+        <f>IF(AND(TRIM($A80)="Finalized",$K80&lt;&gt;""),"",DATE(2026,7,6))</f>
         <v>46209</v>
       </c>
       <c r="P80" s="8" t="s">
@@ -21772,14 +21851,15 @@
         <v>-93</v>
       </c>
       <c r="M81" s="11">
-        <f ca="1">IF($C81="","",$C81+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A81)="Finalized",$K81&lt;&gt;""),"",IF($C81="","",$C81+180-TODAY()))</f>
         <v>60</v>
       </c>
       <c r="N81" s="11">
-        <f ca="1">IF($C81="","",$C81+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A81)="Finalized",$K81&lt;&gt;""),"",IF($C81="","",$C81+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="O81" s="9">
+        <f>IF(AND(TRIM($A81)="Finalized",$K81&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P81" s="8" t="s">
@@ -21892,14 +21972,15 @@
         <v>-93</v>
       </c>
       <c r="M82" s="11">
-        <f ca="1">IF($C82="","",$C82+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A82)="Finalized",$K82&lt;&gt;""),"",IF($C82="","",$C82+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="N82" s="11">
-        <f ca="1">IF($C82="","",$C82+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A82)="Finalized",$K82&lt;&gt;""),"",IF($C82="","",$C82+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="O82" s="9">
+        <f>IF(AND(TRIM($A82)="Finalized",$K82&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P82" s="8" t="s">
@@ -22010,14 +22091,15 @@
         <v>-93</v>
       </c>
       <c r="M83" s="11">
-        <f ca="1">IF($C83="","",$C83+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A83)="Finalized",$K83&lt;&gt;""),"",IF($C83="","",$C83+180-TODAY()))</f>
         <v>17</v>
       </c>
       <c r="N83" s="11">
-        <f ca="1">IF($C83="","",$C83+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A83)="Finalized",$K83&lt;&gt;""),"",IF($C83="","",$C83+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O83" s="9">
+        <f>IF(AND(TRIM($A83)="Finalized",$K83&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P83" s="8" t="s">
@@ -22132,14 +22214,15 @@
         <v>-92</v>
       </c>
       <c r="M84" s="11">
-        <f ca="1">IF($C84="","",$C84+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A84)="Finalized",$K84&lt;&gt;""),"",IF($C84="","",$C84+180-TODAY()))</f>
         <v>17</v>
       </c>
       <c r="N84" s="11">
-        <f ca="1">IF($C84="","",$C84+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A84)="Finalized",$K84&lt;&gt;""),"",IF($C84="","",$C84+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O84" s="9">
+        <f>IF(AND(TRIM($A84)="Finalized",$K84&lt;&gt;""),"",DATE(2026,7,9))</f>
         <v>46212</v>
       </c>
       <c r="P84" s="8" t="s">
@@ -22252,14 +22335,15 @@
         <v>-91</v>
       </c>
       <c r="M85" s="11">
-        <f ca="1">IF($C85="","",$C85+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A85)="Finalized",$K85&lt;&gt;""),"",IF($C85="","",$C85+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="N85" s="11">
-        <f ca="1">IF($C85="","",$C85+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A85)="Finalized",$K85&lt;&gt;""),"",IF($C85="","",$C85+90-TODAY()))</f>
         <v>-52</v>
       </c>
       <c r="O85" s="9">
+        <f>IF(AND(TRIM($A85)="Finalized",$K85&lt;&gt;""),"",DATE(2026,7,10))</f>
         <v>46213</v>
       </c>
       <c r="P85" s="8" t="s">
@@ -22372,14 +22456,15 @@
         <v>-89</v>
       </c>
       <c r="M86" s="11">
-        <f ca="1">IF($F86="","",$F86+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A86)="Finalized",$K86&lt;&gt;""),"",IF($F86="","",$F86+90-TODAY()))</f>
         <v>-89</v>
       </c>
       <c r="N86" s="11">
-        <f ca="1">IF($C86="","",$C86+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A86)="Finalized",$K86&lt;&gt;""),"",IF($C86="","",$C86+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O86" s="9">
+        <f>IF(AND(TRIM($A86)="Finalized",$K86&lt;&gt;""),"",DATE(2026,7,12))</f>
         <v>46215</v>
       </c>
       <c r="P86" s="8" t="s">
@@ -22494,14 +22579,15 @@
         <v>-89</v>
       </c>
       <c r="M87" s="11">
-        <f ca="1">IF($F87="","",$F87+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A87)="Finalized",$K87&lt;&gt;""),"",IF($F87="","",$F87+90-TODAY()))</f>
         <v>-89</v>
       </c>
       <c r="N87" s="11">
-        <f ca="1">IF($C87="","",$C87+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A87)="Finalized",$K87&lt;&gt;""),"",IF($C87="","",$C87+180-TODAY()))</f>
         <v>38</v>
       </c>
       <c r="O87" s="9">
+        <f>IF(AND(TRIM($A87)="Finalized",$K87&lt;&gt;""),"",DATE(2026,7,12))</f>
         <v>46215</v>
       </c>
       <c r="P87" s="8" t="s">
@@ -22620,14 +22706,15 @@
         <v>-87</v>
       </c>
       <c r="M88" s="11">
-        <f ca="1">IF($C88="","",$C88+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A88)="Finalized",$K88&lt;&gt;""),"",IF($C88="","",$C88+365-TODAY()))</f>
         <v>323</v>
       </c>
       <c r="N88" s="11">
-        <f ca="1">IF($C88="","",$C88+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A88)="Finalized",$K88&lt;&gt;""),"",IF($C88="","",$C88+365-TODAY()))</f>
         <v>323</v>
       </c>
       <c r="O88" s="9">
+        <f>IF(AND(TRIM($A88)="Finalized",$K88&lt;&gt;""),"",DATE(2026,7,14))</f>
         <v>46217</v>
       </c>
       <c r="P88" s="8" t="s">
@@ -22736,14 +22823,15 @@
         <v>-87</v>
       </c>
       <c r="M89" s="11">
-        <f ca="1">IF($C89="","",$C89+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A89)="Finalized",$K89&lt;&gt;""),"",IF($C89="","",$C89+180-TODAY()))</f>
         <v>128</v>
       </c>
       <c r="N89" s="11">
-        <f ca="1">IF($C89="","",$C89+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A89)="Finalized",$K89&lt;&gt;""),"",IF($C89="","",$C89+365-TODAY()))</f>
         <v>313</v>
       </c>
       <c r="O89" s="9">
+        <f>IF(AND(TRIM($A89)="Finalized",$K89&lt;&gt;""),"",DATE(2026,7,14))</f>
         <v>46217</v>
       </c>
       <c r="P89" s="8" t="s">
@@ -22858,14 +22946,15 @@
         <v>-86</v>
       </c>
       <c r="M90" s="11">
-        <f ca="1">IF($C90="","",$C90+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A90)="Finalized",$K90&lt;&gt;""),"",IF($C90="","",$C90+180-TODAY()))</f>
         <v>32</v>
       </c>
       <c r="N90" s="11">
-        <f ca="1">IF($C90="","",$C90+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A90)="Finalized",$K90&lt;&gt;""),"",IF($C90="","",$C90+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="O90" s="9">
+        <f>IF(AND(TRIM($A90)="Finalized",$K90&lt;&gt;""),"",DATE(2026,7,15))</f>
         <v>46218</v>
       </c>
       <c r="P90" s="8" t="s">
@@ -22978,14 +23067,15 @@
         <v>-86</v>
       </c>
       <c r="M91" s="11">
-        <f ca="1">IF($C91="","",$C91+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A91)="Finalized",$K91&lt;&gt;""),"",IF($C91="","",$C91+180-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="N91" s="11">
-        <f ca="1">IF($C91="","",$C91+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A91)="Finalized",$K91&lt;&gt;""),"",IF($C91="","",$C91+365-TODAY()))</f>
         <v>204</v>
       </c>
       <c r="O91" s="9">
+        <f>IF(AND(TRIM($A91)="Finalized",$K91&lt;&gt;""),"",DATE(2026,7,15))</f>
         <v>46218</v>
       </c>
       <c r="P91" s="8" t="s">
@@ -23100,14 +23190,15 @@
         <v>-84</v>
       </c>
       <c r="M92" s="11">
-        <f ca="1">IF($C92="","",$C92+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A92)="Finalized",$K92&lt;&gt;""),"",IF($C92="","",$C92+180-TODAY()))</f>
         <v>60</v>
       </c>
       <c r="N92" s="11">
-        <f ca="1">IF($C92="","",$C92+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A92)="Finalized",$K92&lt;&gt;""),"",IF($C92="","",$C92+180-TODAY()))</f>
         <v>60</v>
       </c>
       <c r="O92" s="9">
+        <f>IF(AND(TRIM($A92)="Finalized",$K92&lt;&gt;""),"",DATE(2026,7,17))</f>
         <v>46220</v>
       </c>
       <c r="P92" s="8" t="s">
@@ -23218,14 +23309,15 @@
         <v>-83</v>
       </c>
       <c r="M93" s="11">
-        <f ca="1">IF($C93="","",$C93+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A93)="Finalized",$K93&lt;&gt;""),"",IF($C93="","",$C93+365-TODAY()))</f>
         <v>278</v>
       </c>
       <c r="N93" s="11">
-        <f ca="1">IF($C93="","",$C93+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A93)="Finalized",$K93&lt;&gt;""),"",IF($C93="","",$C93+365-TODAY()))</f>
         <v>278</v>
       </c>
       <c r="O93" s="9">
+        <f>IF(AND(TRIM($A93)="Finalized",$K93&lt;&gt;""),"",DATE(2026,7,18))</f>
         <v>46221</v>
       </c>
       <c r="P93" s="8" t="s">
@@ -23336,14 +23428,15 @@
         <v>-83</v>
       </c>
       <c r="M94" s="11">
-        <f ca="1">IF($C94="","",$C94+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A94)="Finalized",$K94&lt;&gt;""),"",IF($C94="","",$C94+180-TODAY()))</f>
         <v>39</v>
       </c>
       <c r="N94" s="11">
-        <f ca="1">IF($C94="","",$C94+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A94)="Finalized",$K94&lt;&gt;""),"",IF($C94="","",$C94+180-TODAY()))</f>
         <v>39</v>
       </c>
       <c r="O94" s="9">
+        <f>IF(AND(TRIM($A94)="Finalized",$K94&lt;&gt;""),"",DATE(2026,7,18))</f>
         <v>46221</v>
       </c>
       <c r="P94" s="8" t="s">
@@ -23454,14 +23547,15 @@
         <v>-82</v>
       </c>
       <c r="M95" s="11">
-        <f ca="1">IF($F95="","",$F95+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A95)="Finalized",$K95&lt;&gt;""),"",IF($F95="","",$F95+90-TODAY()))</f>
         <v>-82</v>
       </c>
       <c r="N95" s="11">
-        <f ca="1">IF($C95="","",$C95+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A95)="Finalized",$K95&lt;&gt;""),"",IF($C95="","",$C95+365-TODAY()))</f>
         <v>218</v>
       </c>
       <c r="O95" s="9">
+        <f>IF(AND(TRIM($A95)="Finalized",$K95&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P95" s="8" t="s">
@@ -23572,14 +23666,15 @@
         <v>-82</v>
       </c>
       <c r="M96" s="11">
-        <f ca="1">IF($F96="","",$F96+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A96)="Finalized",$K96&lt;&gt;""),"",IF($F96="","",$F96+90-TODAY()))</f>
         <v>-82</v>
       </c>
       <c r="N96" s="11">
-        <f ca="1">IF($C96="","",$C96+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A96)="Finalized",$K96&lt;&gt;""),"",IF($C96="","",$C96+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="O96" s="9">
+        <f>IF(AND(TRIM($A96)="Finalized",$K96&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P96" s="8" t="s">
@@ -23702,14 +23797,15 @@
         <v>-82</v>
       </c>
       <c r="M97" s="11">
-        <f ca="1">IF($C97="","",$C97+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A97)="Finalized",$K97&lt;&gt;""),"",IF($C97="","",$C97+180-TODAY()))</f>
         <v>17</v>
       </c>
       <c r="N97" s="11">
-        <f ca="1">IF($C97="","",$C97+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A97)="Finalized",$K97&lt;&gt;""),"",IF($C97="","",$C97+365-TODAY()))</f>
         <v>202</v>
       </c>
       <c r="O97" s="9">
+        <f>IF(AND(TRIM($A97)="Finalized",$K97&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P97" s="8" t="s">
@@ -23824,14 +23920,15 @@
         <v>-80</v>
       </c>
       <c r="M98" s="11">
-        <f ca="1">IF($C98="","",$C98+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A98)="Finalized",$K98&lt;&gt;""),"",IF($C98="","",$C98+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="N98" s="11">
-        <f ca="1">IF($C98="","",$C98+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A98)="Finalized",$K98&lt;&gt;""),"",IF($C98="","",$C98+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="O98" s="9">
+        <f>IF(AND(TRIM($A98)="Finalized",$K98&lt;&gt;""),"",DATE(2026,7,21))</f>
         <v>46224</v>
       </c>
       <c r="P98" s="8" t="s">
@@ -23944,14 +24041,15 @@
         <v>-79</v>
       </c>
       <c r="M99" s="11">
-        <f ca="1">IF($F99="","",$F99+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A99)="Finalized",$K99&lt;&gt;""),"",IF($F99="","",$F99+90-TODAY()))</f>
         <v>-79</v>
       </c>
       <c r="N99" s="11">
-        <f ca="1">IF($C99="","",$C99+60-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A99)="Finalized",$K99&lt;&gt;""),"",IF($C99="","",$C99+60-TODAY()))</f>
         <v>-42</v>
       </c>
       <c r="O99" s="9">
+        <f>IF(AND(TRIM($A99)="Finalized",$K99&lt;&gt;""),"",DATE(2026,7,22))</f>
         <v>46225</v>
       </c>
       <c r="P99" s="8" t="s">
@@ -24066,14 +24164,15 @@
         <v>-79</v>
       </c>
       <c r="M100" s="11">
-        <f ca="1">IF($C100="","",$C100+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A100)="Finalized",$K100&lt;&gt;""),"",IF($C100="","",$C100+365-TODAY()))</f>
         <v>131</v>
       </c>
       <c r="N100" s="11">
-        <f ca="1">IF($C100="","",$C100+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A100)="Finalized",$K100&lt;&gt;""),"",IF($C100="","",$C100+365-TODAY()))</f>
         <v>131</v>
       </c>
       <c r="O100" s="9">
+        <f>IF(AND(TRIM($A100)="Finalized",$K100&lt;&gt;""),"",DATE(2026,7,22))</f>
         <v>46225</v>
       </c>
       <c r="P100" s="8" t="s">
@@ -24184,14 +24283,15 @@
         <v>-79</v>
       </c>
       <c r="M101" s="11">
-        <f ca="1">IF($C101="","",$C101+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A101)="Finalized",$K101&lt;&gt;""),"",IF($C101="","",$C101+180-TODAY()))</f>
         <v>53</v>
       </c>
       <c r="N101" s="11">
-        <f ca="1">IF($C101="","",$C101+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A101)="Finalized",$K101&lt;&gt;""),"",IF($C101="","",$C101+365-TODAY()))</f>
         <v>238</v>
       </c>
       <c r="O101" s="9">
+        <f>IF(AND(TRIM($A101)="Finalized",$K101&lt;&gt;""),"",DATE(2026,7,22))</f>
         <v>46225</v>
       </c>
       <c r="P101" s="8" t="s">
@@ -24302,14 +24402,15 @@
         <v>-78</v>
       </c>
       <c r="M102" s="11">
-        <f ca="1">IF($C102="","",$C102+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A102)="Finalized",$K102&lt;&gt;""),"",IF($C102="","",$C102+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="N102" s="11">
-        <f ca="1">IF($C102="","",$C102+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A102)="Finalized",$K102&lt;&gt;""),"",IF($C102="","",$C102+365-TODAY()))</f>
         <v>228</v>
       </c>
       <c r="O102" s="9">
+        <f>IF(AND(TRIM($A102)="Finalized",$K102&lt;&gt;""),"",DATE(2026,7,23))</f>
         <v>46226</v>
       </c>
       <c r="P102" s="8" t="s">
@@ -24420,14 +24521,15 @@
         <v>-75</v>
       </c>
       <c r="M103" s="11">
-        <f ca="1">IF($C103="","",$C103+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A103)="Finalized",$K103&lt;&gt;""),"",IF($C103="","",$C103+180-TODAY()))</f>
         <v>32</v>
       </c>
       <c r="N103" s="11">
-        <f ca="1">IF($C103="","",$C103+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A103)="Finalized",$K103&lt;&gt;""),"",IF($C103="","",$C103+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="O103" s="9">
+        <f>IF(AND(TRIM($A103)="Finalized",$K103&lt;&gt;""),"",DATE(2026,7,26))</f>
         <v>46229</v>
       </c>
       <c r="P103" s="8" t="s">
@@ -24542,14 +24644,15 @@
         <v>-74</v>
       </c>
       <c r="M104" s="11">
-        <f ca="1">IF($F104="","",$F104+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A104)="Finalized",$K104&lt;&gt;""),"",IF($F104="","",$F104+90-TODAY()))</f>
         <v>-74</v>
       </c>
       <c r="N104" s="11">
-        <f ca="1">IF($C104="","",$C104+60-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A104)="Finalized",$K104&lt;&gt;""),"",IF($C104="","",$C104+60-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="O104" s="9">
+        <f>IF(AND(TRIM($A104)="Finalized",$K104&lt;&gt;""),"",DATE(2026,7,27))</f>
         <v>46230</v>
       </c>
       <c r="P104" s="8" t="s">
@@ -24664,14 +24767,15 @@
         <v>-74</v>
       </c>
       <c r="M105" s="11">
-        <f ca="1">IF($F105="","",$F105+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A105)="Finalized",$K105&lt;&gt;""),"",IF($F105="","",$F105+365-TODAY()))</f>
         <v>111</v>
       </c>
       <c r="N105" s="11">
-        <f ca="1">IF($F105="","",$F105+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A105)="Finalized",$K105&lt;&gt;""),"",IF($F105="","",$F105+365-TODAY()))</f>
         <v>111</v>
       </c>
       <c r="O105" s="9">
+        <f>IF(AND(TRIM($A105)="Finalized",$K105&lt;&gt;""),"",DATE(2026,7,27))</f>
         <v>46230</v>
       </c>
       <c r="P105" s="8" t="s">
@@ -24782,14 +24886,15 @@
         <v>-73</v>
       </c>
       <c r="M106" s="11">
-        <f ca="1">IF($C106="","",$C106+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A106)="Finalized",$K106&lt;&gt;""),"",IF($C106="","",$C106+180-TODAY()))</f>
         <v>143</v>
       </c>
       <c r="N106" s="11">
-        <f ca="1">IF($C106="","",$C106+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A106)="Finalized",$K106&lt;&gt;""),"",IF($C106="","",$C106+365-TODAY()))</f>
         <v>328</v>
       </c>
       <c r="O106" s="9">
+        <f>IF(AND(TRIM($A106)="Finalized",$K106&lt;&gt;""),"",DATE(2026,7,28))</f>
         <v>46231</v>
       </c>
       <c r="P106" s="8" t="s">
@@ -24906,14 +25011,15 @@
         <v>-72</v>
       </c>
       <c r="M107" s="11">
-        <f ca="1">IF($C107="","",$C107+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A107)="Finalized",$K107&lt;&gt;""),"",IF($C107="","",$C107+365-TODAY()))</f>
         <v>189</v>
       </c>
       <c r="N107" s="11">
-        <f ca="1">IF($C107="","",$C107+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A107)="Finalized",$K107&lt;&gt;""),"",IF($C107="","",$C107+90-TODAY()))</f>
         <v>-86</v>
       </c>
       <c r="O107" s="9">
+        <f>IF(AND(TRIM($A107)="Finalized",$K107&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P107" s="8" t="s">
@@ -25024,14 +25130,15 @@
         <v>-72</v>
       </c>
       <c r="M108" s="11">
-        <f ca="1">IF($C108="","",$C108+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A108)="Finalized",$K108&lt;&gt;""),"",IF($C108="","",$C108+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="N108" s="11">
-        <f ca="1">IF($C108="","",$C108+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A108)="Finalized",$K108&lt;&gt;""),"",IF($C108="","",$C108+365-TODAY()))</f>
         <v>221</v>
       </c>
       <c r="O108" s="9">
+        <f>IF(AND(TRIM($A108)="Finalized",$K108&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P108" s="8" t="s">
@@ -25146,14 +25253,15 @@
         <v>-72</v>
       </c>
       <c r="M109" s="11">
-        <f ca="1">IF($C109="","",$C109+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A109)="Finalized",$K109&lt;&gt;""),"",IF($C109="","",$C109+365-TODAY()))</f>
         <v>213</v>
       </c>
       <c r="N109" s="11">
-        <f ca="1">IF($C109="","",$C109+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A109)="Finalized",$K109&lt;&gt;""),"",IF($C109="","",$C109+365-TODAY()))</f>
         <v>213</v>
       </c>
       <c r="O109" s="9">
+        <f>IF(AND(TRIM($A109)="Finalized",$K109&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P109" s="8" t="s">
@@ -25266,14 +25374,15 @@
         <v>-72</v>
       </c>
       <c r="M110" s="11">
-        <f ca="1">IF($C110="","",$C110+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A110)="Finalized",$K110&lt;&gt;""),"",IF($C110="","",$C110+180-TODAY()))</f>
         <v>38</v>
       </c>
       <c r="N110" s="11">
-        <f ca="1">IF($C110="","",$C110+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A110)="Finalized",$K110&lt;&gt;""),"",IF($C110="","",$C110+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="O110" s="9">
+        <f>IF(AND(TRIM($A110)="Finalized",$K110&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P110" s="8" t="s">
@@ -25388,14 +25497,15 @@
         <v>-72</v>
       </c>
       <c r="M111" s="11">
-        <f ca="1">IF($F111="","",$F111+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A111)="Finalized",$K111&lt;&gt;""),"",IF($F111="","",$F111+90-TODAY()))</f>
         <v>-72</v>
       </c>
       <c r="N111" s="11">
-        <f ca="1">IF($C111="","",$C111+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A111)="Finalized",$K111&lt;&gt;""),"",IF($C111="","",$C111+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="O111" s="9">
+        <f>IF(AND(TRIM($A111)="Finalized",$K111&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P111" s="8" t="s">
@@ -25512,14 +25622,15 @@
         <v>-71</v>
       </c>
       <c r="M112" s="11" t="str">
-        <f ca="1">IF($C112="","",$C112+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A112)="Finalized",$K112&lt;&gt;""),"",IF($C112="","",$C112+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N112" s="11" t="str">
-        <f ca="1">IF($C112="","",$C112+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A112)="Finalized",$K112&lt;&gt;""),"",IF($C112="","",$C112+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O112" s="9">
+        <f>IF(AND(TRIM($A112)="Finalized",$K112&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P112" s="8" t="s">
@@ -25628,14 +25739,15 @@
         <v>-71</v>
       </c>
       <c r="M113" s="11">
-        <f ca="1">IF($C113="","",$C113+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A113)="Finalized",$K113&lt;&gt;""),"",IF($C113="","",$C113+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="N113" s="11">
-        <f ca="1">IF($C113="","",$C113+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A113)="Finalized",$K113&lt;&gt;""),"",IF($C113="","",$C113+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="O113" s="9">
+        <f>IF(AND(TRIM($A113)="Finalized",$K113&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P113" s="8" t="s">
@@ -25755,10 +25867,11 @@
       </c>
       <c r="M114" s="11"/>
       <c r="N114" s="11">
-        <f ca="1">IF($C114="","",$C114+65-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A114)="Finalized",$K114&lt;&gt;""),"",IF($C114="","",$C114+65-TODAY()))</f>
         <v>-86</v>
       </c>
       <c r="O114" s="9">
+        <f>IF(AND(TRIM($A114)="Finalized",$K114&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P114" s="8" t="s">
@@ -25871,14 +25984,15 @@
         <v>-71</v>
       </c>
       <c r="M115" s="11" t="str">
-        <f ca="1">IF($C115="","",$C115+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A115)="Finalized",$K115&lt;&gt;""),"",IF($C115="","",$C115+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N115" s="11" t="str">
-        <f ca="1">IF($C115="","",$C115+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A115)="Finalized",$K115&lt;&gt;""),"",IF($C115="","",$C115+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O115" s="9">
+        <f>IF(AND(TRIM($A115)="Finalized",$K115&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P115" s="8" t="s">
@@ -25991,14 +26105,15 @@
         <v>-70</v>
       </c>
       <c r="M116" s="11">
-        <f ca="1">IF($C116="","",$C116+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A116)="Finalized",$K116&lt;&gt;""),"",IF($C116="","",$C116+365-TODAY()))</f>
         <v>284</v>
       </c>
       <c r="N116" s="11">
-        <f ca="1">IF($C116="","",$C116+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A116)="Finalized",$K116&lt;&gt;""),"",IF($C116="","",$C116+90-TODAY()))</f>
         <v>9</v>
       </c>
       <c r="O116" s="9">
+        <f>IF(AND(TRIM($A116)="Finalized",$K116&lt;&gt;""),"",DATE(2026,7,31))</f>
         <v>46234</v>
       </c>
       <c r="P116" s="8" t="s">
@@ -26119,14 +26234,15 @@
         <v>-70</v>
       </c>
       <c r="M117" s="11">
-        <f ca="1">IF($F117="","",$F117+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A117)="Finalized",$K117&lt;&gt;""),"",IF($F117="","",$F117+365-TODAY()))</f>
         <v>175</v>
       </c>
       <c r="N117" s="11">
-        <f ca="1">IF($C117="","",$C117+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A117)="Finalized",$K117&lt;&gt;""),"",IF($C117="","",$C117+180-TODAY()))</f>
         <v>30</v>
       </c>
       <c r="O117" s="9">
+        <f>IF(AND(TRIM($A117)="Finalized",$K117&lt;&gt;""),"",DATE(2026,7,31))</f>
         <v>46234</v>
       </c>
       <c r="P117" s="8" t="s">
@@ -26241,14 +26357,15 @@
         <v>-69</v>
       </c>
       <c r="M118" s="11">
-        <f ca="1">IF($C118="","",$C118+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A118)="Finalized",$K118&lt;&gt;""),"",IF($C118="","",$C118+180-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="N118" s="11">
-        <f ca="1">IF($C118="","",$C118+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A118)="Finalized",$K118&lt;&gt;""),"",IF($C118="","",$C118+180-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O118" s="9">
+        <f>IF(AND(TRIM($A118)="Finalized",$K118&lt;&gt;""),"",DATE(2026,8,1))</f>
         <v>46235</v>
       </c>
       <c r="P118" s="8" t="s">
@@ -26359,14 +26476,15 @@
         <v>-68</v>
       </c>
       <c r="M119" s="11">
-        <f ca="1">IF($F119="","",$F119+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A119)="Finalized",$K119&lt;&gt;""),"",IF($F119="","",$F119+90-TODAY()))</f>
         <v>-68</v>
       </c>
       <c r="N119" s="11">
-        <f ca="1">IF($C119="","",$C119+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A119)="Finalized",$K119&lt;&gt;""),"",IF($C119="","",$C119+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="O119" s="9">
+        <f>IF(AND(TRIM($A119)="Finalized",$K119&lt;&gt;""),"",DATE(2026,8,2))</f>
         <v>46236</v>
       </c>
       <c r="P119" s="8" t="s">
@@ -26481,14 +26599,15 @@
         <v>-68</v>
       </c>
       <c r="M120" s="11">
-        <f ca="1">IF($C120="","",$C120+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A120)="Finalized",$K120&lt;&gt;""),"",IF($C120="","",$C120+180-TODAY()))</f>
         <v>46</v>
       </c>
       <c r="N120" s="11">
-        <f ca="1">IF($C120="","",$C120+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A120)="Finalized",$K120&lt;&gt;""),"",IF($C120="","",$C120+365-TODAY()))</f>
         <v>231</v>
       </c>
       <c r="O120" s="9">
+        <f>IF(AND(TRIM($A120)="Finalized",$K120&lt;&gt;""),"",DATE(2026,8,2))</f>
         <v>46236</v>
       </c>
       <c r="P120" s="8" t="s">
@@ -26599,14 +26718,15 @@
         <v>-66</v>
       </c>
       <c r="M121" s="11">
-        <f ca="1">IF($F121="","",$F121+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A121)="Finalized",$K121&lt;&gt;""),"",IF($F121="","",$F121+90-TODAY()))</f>
         <v>-66</v>
       </c>
       <c r="N121" s="11">
-        <f ca="1">IF($C121="","",$C121+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A121)="Finalized",$K121&lt;&gt;""),"",IF($C121="","",$C121+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O121" s="9">
+        <f>IF(AND(TRIM($A121)="Finalized",$K121&lt;&gt;""),"",DATE(2026,8,4))</f>
         <v>46238</v>
       </c>
       <c r="P121" s="8" t="s">
@@ -26719,14 +26839,15 @@
         <v>-65</v>
       </c>
       <c r="M122" s="11" t="str">
-        <f ca="1">IF($C122="","",$C122+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A122)="Finalized",$K122&lt;&gt;""),"",IF($C122="","",$C122+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N122" s="11" t="str">
-        <f ca="1">IF($C122="","",$C122+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A122)="Finalized",$K122&lt;&gt;""),"",IF($C122="","",$C122+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O122" s="9">
+        <f>IF(AND(TRIM($A122)="Finalized",$K122&lt;&gt;""),"",DATE(2026,8,5))</f>
         <v>46239</v>
       </c>
       <c r="P122" s="8" t="s">
@@ -26835,14 +26956,15 @@
         <v>-65</v>
       </c>
       <c r="M123" s="11">
-        <f ca="1">IF($C123="","",$C123+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A123)="Finalized",$K123&lt;&gt;""),"",IF($C123="","",$C123+365-TODAY()))</f>
         <v>297</v>
       </c>
       <c r="N123" s="11">
-        <f ca="1">IF($C123="","",$C123+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A123)="Finalized",$K123&lt;&gt;""),"",IF($C123="","",$C123+365-TODAY()))</f>
         <v>297</v>
       </c>
       <c r="O123" s="9">
+        <f>IF(AND(TRIM($A123)="Finalized",$K123&lt;&gt;""),"",DATE(2026,8,5))</f>
         <v>46239</v>
       </c>
       <c r="P123" s="8" t="s">
@@ -26957,14 +27079,15 @@
         <v>-64</v>
       </c>
       <c r="M124" s="11">
-        <f ca="1">IF($F124="","",$F124+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A124)="Finalized",$K124&lt;&gt;""),"",IF($F124="","",$F124+90-TODAY()))</f>
         <v>-64</v>
       </c>
       <c r="N124" s="11">
-        <f ca="1">IF($C124="","",$C124+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A124)="Finalized",$K124&lt;&gt;""),"",IF($C124="","",$C124+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="O124" s="9">
+        <f>IF(AND(TRIM($A124)="Finalized",$K124&lt;&gt;""),"",DATE(2026,8,6))</f>
         <v>46240</v>
       </c>
       <c r="P124" s="8" t="s">
@@ -27079,14 +27202,15 @@
         <v>-64</v>
       </c>
       <c r="M125" s="11">
-        <f ca="1">IF($C125="","",$C125+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A125)="Finalized",$K125&lt;&gt;""),"",IF($C125="","",$C125+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="N125" s="11">
-        <f ca="1">IF($C125="","",$C125+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A125)="Finalized",$K125&lt;&gt;""),"",IF($C125="","",$C125+90-TODAY()))</f>
         <v>-53</v>
       </c>
       <c r="O125" s="9">
+        <f>IF(AND(TRIM($A125)="Finalized",$K125&lt;&gt;""),"",DATE(2026,8,6))</f>
         <v>46240</v>
       </c>
       <c r="P125" s="8" t="s">
@@ -27195,14 +27319,15 @@
         <v>-61</v>
       </c>
       <c r="M126" s="11">
-        <f ca="1">IF($F126="","",$F126+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A126)="Finalized",$K126&lt;&gt;""),"",IF($F126="","",$F126+90-TODAY()))</f>
         <v>-61</v>
       </c>
       <c r="N126" s="11">
-        <f ca="1">IF($C126="","",$C126+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A126)="Finalized",$K126&lt;&gt;""),"",IF($C126="","",$C126+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="O126" s="9">
+        <f>IF(AND(TRIM($A126)="Finalized",$K126&lt;&gt;""),"",DATE(2026,8,9))</f>
         <v>46243</v>
       </c>
       <c r="P126" s="8" t="s">
@@ -27319,14 +27444,15 @@
         <v>-61</v>
       </c>
       <c r="M127" s="11">
-        <f ca="1">IF($F127="","",$F127+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A127)="Finalized",$K127&lt;&gt;""),"",IF($F127="","",$F127+90-TODAY()))</f>
         <v>-61</v>
       </c>
       <c r="N127" s="11">
-        <f ca="1">IF($C127="","",$C127+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A127)="Finalized",$K127&lt;&gt;""),"",IF($C127="","",$C127+540-TODAY()))</f>
         <v>432</v>
       </c>
       <c r="O127" s="9">
+        <f>IF(AND(TRIM($A127)="Finalized",$K127&lt;&gt;""),"",DATE(2026,8,9))</f>
         <v>46243</v>
       </c>
       <c r="P127" s="8" t="s">
@@ -27447,14 +27573,15 @@
         <v>-60</v>
       </c>
       <c r="M128" s="11">
-        <f ca="1">IF($F128="","",$F128+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A128)="Finalized",$K128&lt;&gt;""),"",IF($F128="","",$F128+90-TODAY()))</f>
         <v>-60</v>
       </c>
       <c r="N128" s="11">
-        <f ca="1">IF($C128="","",$C128+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A128)="Finalized",$K128&lt;&gt;""),"",IF($C128="","",$C128+180-TODAY()))</f>
         <v>124</v>
       </c>
       <c r="O128" s="9">
+        <f>IF(AND(TRIM($A128)="Finalized",$K128&lt;&gt;""),"",DATE(2026,8,10))</f>
         <v>46244</v>
       </c>
       <c r="P128" s="8" t="s">
@@ -27567,14 +27694,15 @@
         <v>-59</v>
       </c>
       <c r="M129" s="11">
-        <f ca="1">IF($C129="","",$C129+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A129)="Finalized",$K129&lt;&gt;""),"",IF($C129="","",$C129+365-TODAY()))</f>
         <v>323</v>
       </c>
       <c r="N129" s="11">
-        <f ca="1">IF($C129="","",$C129+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A129)="Finalized",$K129&lt;&gt;""),"",IF($C129="","",$C129+365-TODAY()))</f>
         <v>323</v>
       </c>
       <c r="O129" s="9">
+        <f>IF(AND(TRIM($A129)="Finalized",$K129&lt;&gt;""),"",DATE(2026,8,11))</f>
         <v>46245</v>
       </c>
       <c r="P129" s="8" t="s">
@@ -27691,14 +27819,15 @@
         <v>-59</v>
       </c>
       <c r="M130" s="11">
-        <f ca="1">IF($C130="","",$C130+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A130)="Finalized",$K130&lt;&gt;""),"",IF($C130="","",$C130+180-TODAY()))</f>
         <v>46</v>
       </c>
       <c r="N130" s="11">
-        <f ca="1">IF($C130="","",$C130+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A130)="Finalized",$K130&lt;&gt;""),"",IF($C130="","",$C130+365-TODAY()))</f>
         <v>231</v>
       </c>
       <c r="O130" s="9">
+        <f>IF(AND(TRIM($A130)="Finalized",$K130&lt;&gt;""),"",DATE(2026,8,11))</f>
         <v>46245</v>
       </c>
       <c r="P130" s="8" t="s">
@@ -27813,14 +27942,15 @@
         <v>-58</v>
       </c>
       <c r="M131" s="11" t="str">
-        <f ca="1">IF($C131="","",$C131+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A131)="Finalized",$K131&lt;&gt;""),"",IF($C131="","",$C131+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N131" s="11" t="str">
-        <f ca="1">IF($C131="","",$C131+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A131)="Finalized",$K131&lt;&gt;""),"",IF($C131="","",$C131+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O131" s="9">
+        <f>IF(AND(TRIM($A131)="Finalized",$K131&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P131" s="8" t="s">
@@ -27929,14 +28059,15 @@
         <v>-58</v>
       </c>
       <c r="M132" s="11" t="str">
-        <f ca="1">IF($C132="","",$C132+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A132)="Finalized",$K132&lt;&gt;""),"",IF($C132="","",$C132+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N132" s="11" t="str">
-        <f ca="1">IF($C132="","",$C132+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A132)="Finalized",$K132&lt;&gt;""),"",IF($C132="","",$C132+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O132" s="9">
+        <f>IF(AND(TRIM($A132)="Finalized",$K132&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P132" s="8" t="s">
@@ -28045,14 +28176,15 @@
         <v>-58</v>
       </c>
       <c r="M133" s="11">
-        <f ca="1">IF($F133="","",$F133+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A133)="Finalized",$K133&lt;&gt;""),"",IF($F133="","",$F133+90-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="N133" s="11">
-        <f ca="1">IF($C133="","",$C133+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A133)="Finalized",$K133&lt;&gt;""),"",IF($C133="","",$C133+180-TODAY()))</f>
         <v>46</v>
       </c>
       <c r="O133" s="9">
+        <f>IF(AND(TRIM($A133)="Finalized",$K133&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P133" s="8" t="s">
@@ -28163,14 +28295,15 @@
         <v>-57</v>
       </c>
       <c r="M134" s="11" t="str">
-        <f ca="1">IF($C134="","",$C134+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A134)="Finalized",$K134&lt;&gt;""),"",IF($C134="","",$C134+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N134" s="11" t="str">
-        <f ca="1">IF($C134="","",$C134+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A134)="Finalized",$K134&lt;&gt;""),"",IF($C134="","",$C134+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O134" s="9">
+        <f>IF(AND(TRIM($A134)="Finalized",$K134&lt;&gt;""),"",DATE(2026,8,13))</f>
         <v>46247</v>
       </c>
       <c r="P134" s="8" t="s">
@@ -28287,14 +28420,15 @@
         <v>-56</v>
       </c>
       <c r="M135" s="11" t="str">
-        <f ca="1">IF($C135="","",$C135+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A135)="Finalized",$K135&lt;&gt;""),"",IF($C135="","",$C135+90-TODAY()))</f>
         <v/>
       </c>
       <c r="N135" s="11" t="str">
-        <f ca="1">IF($C135="","",$C135+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A135)="Finalized",$K135&lt;&gt;""),"",IF($C135="","",$C135+90-TODAY()))</f>
         <v/>
       </c>
       <c r="O135" s="9">
+        <f>IF(AND(TRIM($A135)="Finalized",$K135&lt;&gt;""),"",DATE(2026,8,14))</f>
         <v>46248</v>
       </c>
       <c r="P135" s="8" t="s">
@@ -28403,14 +28537,15 @@
         <v>-54</v>
       </c>
       <c r="M136" s="11">
-        <f ca="1">IF($C136="","",$C136+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A136)="Finalized",$K136&lt;&gt;""),"",IF($C136="","",$C136+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N136" s="11">
-        <f ca="1">IF($C136="","",$C136+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A136)="Finalized",$K136&lt;&gt;""),"",IF($C136="","",$C136+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="O136" s="9">
+        <f>IF(AND(TRIM($A136)="Finalized",$K136&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P136" s="8" t="s">
@@ -28523,14 +28658,15 @@
         <v>-54</v>
       </c>
       <c r="M137" s="11">
-        <f ca="1">IF($F137="","",$F137+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A137)="Finalized",$K137&lt;&gt;""),"",IF($F137="","",$F137+90-TODAY()))</f>
         <v>-54</v>
       </c>
       <c r="N137" s="11">
-        <f ca="1">IF($C137="","",$C137+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A137)="Finalized",$K137&lt;&gt;""),"",IF($C137="","",$C137+540-TODAY()))</f>
         <v>421</v>
       </c>
       <c r="O137" s="9">
+        <f>IF(AND(TRIM($A137)="Finalized",$K137&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P137" s="8" t="s">
@@ -28645,14 +28781,15 @@
         <v>-54</v>
       </c>
       <c r="M138" s="11">
-        <f ca="1">IF($C138="","",$C138+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A138)="Finalized",$K138&lt;&gt;""),"",IF($C138="","",$C138+180-TODAY()))</f>
         <v>128</v>
       </c>
       <c r="N138" s="11">
-        <f ca="1">IF($C138="","",$C138+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A138)="Finalized",$K138&lt;&gt;""),"",IF($C138="","",$C138+365-TODAY()))</f>
         <v>313</v>
       </c>
       <c r="O138" s="9">
+        <f>IF(AND(TRIM($A138)="Finalized",$K138&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P138" s="8" t="s">
@@ -28765,14 +28902,15 @@
         <v>-52</v>
       </c>
       <c r="M139" s="11">
-        <f ca="1">IF($C139="","",$C139+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A139)="Finalized",$K139&lt;&gt;""),"",IF($C139="","",$C139+180-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="N139" s="11">
-        <f ca="1">IF($C139="","",$C139+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A139)="Finalized",$K139&lt;&gt;""),"",IF($C139="","",$C139+365-TODAY()))</f>
         <v>250</v>
       </c>
       <c r="O139" s="9">
+        <f>IF(AND(TRIM($A139)="Finalized",$K139&lt;&gt;""),"",DATE(2026,8,18))</f>
         <v>46252</v>
       </c>
       <c r="P139" s="8" t="s">
@@ -28885,14 +29023,15 @@
         <v>-52</v>
       </c>
       <c r="M140" s="11">
-        <f ca="1">IF($C140="","",$C140+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A140)="Finalized",$K140&lt;&gt;""),"",IF($C140="","",$C140+180-TODAY()))</f>
         <v>59</v>
       </c>
       <c r="N140" s="11">
-        <f ca="1">IF($C140="","",$C140+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A140)="Finalized",$K140&lt;&gt;""),"",IF($C140="","",$C140+365-TODAY()))</f>
         <v>244</v>
       </c>
       <c r="O140" s="9">
+        <f>IF(AND(TRIM($A140)="Finalized",$K140&lt;&gt;""),"",DATE(2026,8,18))</f>
         <v>46252</v>
       </c>
       <c r="P140" s="8" t="s">
@@ -29005,14 +29144,15 @@
         <v>-51</v>
       </c>
       <c r="M141" s="11">
-        <f ca="1">IF($C141="","",$C141+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A141)="Finalized",$K141&lt;&gt;""),"",IF($C141="","",$C141+180-TODAY()))</f>
         <v>118</v>
       </c>
       <c r="N141" s="11">
-        <f ca="1">IF($C141="","",$C141+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A141)="Finalized",$K141&lt;&gt;""),"",IF($C141="","",$C141+365-TODAY()))</f>
         <v>303</v>
       </c>
       <c r="O141" s="9">
+        <f>IF(AND(TRIM($A141)="Finalized",$K141&lt;&gt;""),"",DATE(2026,8,19))</f>
         <v>46253</v>
       </c>
       <c r="P141" s="8" t="s">
@@ -29129,14 +29269,15 @@
         <v>-51</v>
       </c>
       <c r="M142" s="11">
-        <f ca="1">IF($C142="","",$C142+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A142)="Finalized",$K142&lt;&gt;""),"",IF($C142="","",$C142+180-TODAY()))</f>
         <v>135</v>
       </c>
       <c r="N142" s="11">
-        <f ca="1">IF($C142="","",$C142+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A142)="Finalized",$K142&lt;&gt;""),"",IF($C142="","",$C142+365-TODAY()))</f>
         <v>320</v>
       </c>
       <c r="O142" s="9">
+        <f>IF(AND(TRIM($A142)="Finalized",$K142&lt;&gt;""),"",DATE(2026,8,19))</f>
         <v>46253</v>
       </c>
       <c r="P142" s="8" t="s">
@@ -29245,14 +29386,15 @@
         <v>-50</v>
       </c>
       <c r="M143" s="11" t="str">
-        <f ca="1">IF($C143="","",$C143+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A143)="Finalized",$K143&lt;&gt;""),"",IF($C143="","",$C143+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N143" s="11" t="str">
-        <f ca="1">IF($C143="","",$C143+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A143)="Finalized",$K143&lt;&gt;""),"",IF($C143="","",$C143+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O143" s="9">
+        <f>IF(AND(TRIM($A143)="Finalized",$K143&lt;&gt;""),"",DATE(2026,8,20))</f>
         <v>46254</v>
       </c>
       <c r="P143" s="8" t="s">
@@ -29361,14 +29503,15 @@
         <v>-50</v>
       </c>
       <c r="M144" s="11">
-        <f ca="1">IF($C144="","",$C144+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A144)="Finalized",$K144&lt;&gt;""),"",IF($C144="","",$C144+180-TODAY()))</f>
         <v>59</v>
       </c>
       <c r="N144" s="11">
-        <f ca="1">IF($C144="","",$C144+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A144)="Finalized",$K144&lt;&gt;""),"",IF($C144="","",$C144+365-TODAY()))</f>
         <v>244</v>
       </c>
       <c r="O144" s="9">
+        <f>IF(AND(TRIM($A144)="Finalized",$K144&lt;&gt;""),"",DATE(2026,8,20))</f>
         <v>46254</v>
       </c>
       <c r="P144" s="8" t="s">
@@ -29481,14 +29624,15 @@
         <v>-46</v>
       </c>
       <c r="M145" s="11">
-        <f ca="1">IF($F145="","",$F145+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A145)="Finalized",$K145&lt;&gt;""),"",IF($F145="","",$F145+90-TODAY()))</f>
         <v>-46</v>
       </c>
       <c r="N145" s="11">
-        <f ca="1">IF($C145="","",$C145+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A145)="Finalized",$K145&lt;&gt;""),"",IF($C145="","",$C145+180-TODAY()))</f>
         <v>57</v>
       </c>
       <c r="O145" s="9">
+        <f>IF(AND(TRIM($A145)="Finalized",$K145&lt;&gt;""),"",DATE(2026,8,24))</f>
         <v>46258</v>
       </c>
       <c r="P145" s="8" t="s">
@@ -29603,14 +29747,15 @@
         <v>-45</v>
       </c>
       <c r="M146" s="11">
-        <f ca="1">IF($C146="","",$C146+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A146)="Finalized",$K146&lt;&gt;""),"",IF($C146="","",$C146+180-TODAY()))</f>
         <v>95</v>
       </c>
       <c r="N146" s="11">
-        <f ca="1">IF($C146="","",$C146+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A146)="Finalized",$K146&lt;&gt;""),"",IF($C146="","",$C146+365-TODAY()))</f>
         <v>280</v>
       </c>
       <c r="O146" s="9">
+        <f>IF(AND(TRIM($A146)="Finalized",$K146&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P146" s="8" t="s">
@@ -29727,14 +29872,15 @@
         <v>-45</v>
       </c>
       <c r="M147" s="11">
-        <f ca="1">IF($F147="","",$F147+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A147)="Finalized",$K147&lt;&gt;""),"",IF($F147="","",$F147+90-TODAY()))</f>
         <v>-45</v>
       </c>
       <c r="N147" s="11">
-        <f ca="1">IF($C147="","",$C147+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A147)="Finalized",$K147&lt;&gt;""),"",IF($C147="","",$C147+180-TODAY()))</f>
         <v>53</v>
       </c>
       <c r="O147" s="9">
+        <f>IF(AND(TRIM($A147)="Finalized",$K147&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P147" s="8" t="s">
@@ -29851,14 +29997,15 @@
         <v>-45</v>
       </c>
       <c r="M148" s="11">
-        <f ca="1">IF($C148="","",$C148+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A148)="Finalized",$K148&lt;&gt;""),"",IF($C148="","",$C148+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N148" s="11">
-        <f ca="1">IF($C148="","",$C148+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A148)="Finalized",$K148&lt;&gt;""),"",IF($C148="","",$C148+90-TODAY()))</f>
         <v>-3</v>
       </c>
       <c r="O148" s="9">
+        <f>IF(AND(TRIM($A148)="Finalized",$K148&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P148" s="8" t="s">
@@ -29973,14 +30120,15 @@
         <v>-44</v>
       </c>
       <c r="M149" s="11">
-        <f ca="1">IF($C149="","",$C149+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A149)="Finalized",$K149&lt;&gt;""),"",IF($C149="","",$C149+180-TODAY()))</f>
         <v>40</v>
       </c>
       <c r="N149" s="11">
-        <f ca="1">IF($C149="","",$C149+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A149)="Finalized",$K149&lt;&gt;""),"",IF($C149="","",$C149+180-TODAY()))</f>
         <v>40</v>
       </c>
       <c r="O149" s="9">
+        <f>IF(AND(TRIM($A149)="Finalized",$K149&lt;&gt;""),"",DATE(2026,8,26))</f>
         <v>46260</v>
       </c>
       <c r="P149" s="8" t="s">
@@ -30095,14 +30243,15 @@
         <v>-43</v>
       </c>
       <c r="M150" s="11">
-        <f ca="1">IF($C150="","",$C150+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A150)="Finalized",$K150&lt;&gt;""),"",IF($C150="","",$C150+365-TODAY()))</f>
         <v>252</v>
       </c>
       <c r="N150" s="11">
-        <f ca="1">IF($C150="","",$C150+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A150)="Finalized",$K150&lt;&gt;""),"",IF($C150="","",$C150+365-TODAY()))</f>
         <v>252</v>
       </c>
       <c r="O150" s="9">
+        <f>IF(AND(TRIM($A150)="Finalized",$K150&lt;&gt;""),"",DATE(2026,8,27))</f>
         <v>46261</v>
       </c>
       <c r="P150" s="8" t="s">
@@ -30213,14 +30362,15 @@
         <v>-43</v>
       </c>
       <c r="M151" s="11">
-        <f ca="1">IF($C151="","",$C151+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A151)="Finalized",$K151&lt;&gt;""),"",IF($C151="","",$C151+180-TODAY()))</f>
         <v>61</v>
       </c>
       <c r="N151" s="11">
-        <f ca="1">IF($C151="","",$C151+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A151)="Finalized",$K151&lt;&gt;""),"",IF($C151="","",$C151+180-TODAY()))</f>
         <v>61</v>
       </c>
       <c r="O151" s="9">
+        <f>IF(AND(TRIM($A151)="Finalized",$K151&lt;&gt;""),"",DATE(2026,8,27))</f>
         <v>46261</v>
       </c>
       <c r="P151" s="8" t="s">
@@ -30333,14 +30483,15 @@
         <v>-42</v>
       </c>
       <c r="M152" s="11">
-        <f ca="1">IF($F152="","",$F152+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A152)="Finalized",$K152&lt;&gt;""),"",IF($F152="","",$F152+365-TODAY()))</f>
         <v>203</v>
       </c>
       <c r="N152" s="11" t="str">
-        <f ca="1">IF($C152="","",$C152+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A152)="Finalized",$K152&lt;&gt;""),"",IF($C152="","",$C152+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O152" s="9">
+        <f>IF(AND(TRIM($A152)="Finalized",$K152&lt;&gt;""),"",DATE(2026,8,28))</f>
         <v>46262</v>
       </c>
       <c r="P152" s="8" t="s">
@@ -30451,14 +30602,15 @@
         <v>-41</v>
       </c>
       <c r="M153" s="11">
-        <f ca="1">IF($C153="","",$C153+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A153)="Finalized",$K153&lt;&gt;""),"",IF($C153="","",$C153+180-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="N153" s="11">
-        <f ca="1">IF($C153="","",$C153+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A153)="Finalized",$K153&lt;&gt;""),"",IF($C153="","",$C153+180-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="O153" s="9">
+        <f>IF(AND(TRIM($A153)="Finalized",$K153&lt;&gt;""),"",DATE(2026,8,29))</f>
         <v>46263</v>
       </c>
       <c r="P153" s="8" t="s">
@@ -30571,14 +30723,15 @@
         <v>-40</v>
       </c>
       <c r="M154" s="11">
-        <f ca="1">IF($F154="","",$F154+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A154)="Finalized",$K154&lt;&gt;""),"",IF($F154="","",$F154+90-TODAY()))</f>
         <v>-40</v>
       </c>
       <c r="N154" s="11">
-        <f ca="1">IF($C154="","",$C154+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A154)="Finalized",$K154&lt;&gt;""),"",IF($C154="","",$C154+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="O154" s="9">
+        <f>IF(AND(TRIM($A154)="Finalized",$K154&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P154" s="8" t="s">
@@ -30697,14 +30850,15 @@
         <v>-40</v>
       </c>
       <c r="M155" s="11">
-        <f ca="1">IF($C155="","",$C155+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A155)="Finalized",$K155&lt;&gt;""),"",IF($C155="","",$C155+180-TODAY()))</f>
         <v>130</v>
       </c>
       <c r="N155" s="11">
-        <f ca="1">IF($C155="","",$C155+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A155)="Finalized",$K155&lt;&gt;""),"",IF($C155="","",$C155+365-TODAY()))</f>
         <v>315</v>
       </c>
       <c r="O155" s="9">
+        <f>IF(AND(TRIM($A155)="Finalized",$K155&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P155" s="8" t="s">
@@ -30823,14 +30977,15 @@
         <v>-40</v>
       </c>
       <c r="M156" s="11">
-        <f ca="1">IF($C156="","",$C156+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A156)="Finalized",$K156&lt;&gt;""),"",IF($C156="","",$C156+180-TODAY()))</f>
         <v>132</v>
       </c>
       <c r="N156" s="11">
-        <f ca="1">IF($C156="","",$C156+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A156)="Finalized",$K156&lt;&gt;""),"",IF($C156="","",$C156+365-TODAY()))</f>
         <v>317</v>
       </c>
       <c r="O156" s="9">
+        <f>IF(AND(TRIM($A156)="Finalized",$K156&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P156" s="8" t="s">
@@ -30945,14 +31100,15 @@
         <v>-38</v>
       </c>
       <c r="M157" s="11">
-        <f ca="1">IF($F157="","",$F157+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A157)="Finalized",$K157&lt;&gt;""),"",IF($F157="","",$F157+90-TODAY()))</f>
         <v>-38</v>
       </c>
       <c r="N157" s="11">
-        <f ca="1">IF($C157="","",$C157+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A157)="Finalized",$K157&lt;&gt;""),"",IF($C157="","",$C157+180-TODAY()))</f>
         <v>79</v>
       </c>
       <c r="O157" s="9">
+        <f>IF(AND(TRIM($A157)="Finalized",$K157&lt;&gt;""),"",DATE(2026,9,1))</f>
         <v>46266</v>
       </c>
       <c r="P157" s="8" t="s">
@@ -31065,14 +31221,15 @@
         <v>-37</v>
       </c>
       <c r="M158" s="11">
-        <f ca="1">IF($F158="","",$F158+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A158)="Finalized",$K158&lt;&gt;""),"",IF($F158="","",$F158+90-TODAY()))</f>
         <v>-37</v>
       </c>
       <c r="N158" s="11">
-        <f ca="1">IF($C158="","",$C158+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A158)="Finalized",$K158&lt;&gt;""),"",IF($C158="","",$C158+540-TODAY()))</f>
         <v>461</v>
       </c>
       <c r="O158" s="9">
+        <f>IF(AND(TRIM($A158)="Finalized",$K158&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P158" s="8" t="s">
@@ -31187,14 +31344,15 @@
         <v>-37</v>
       </c>
       <c r="M159" s="11">
-        <f ca="1">IF($C159="","",$C159+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A159)="Finalized",$K159&lt;&gt;""),"",IF($C159="","",$C159+180-TODAY()))</f>
         <v>130</v>
       </c>
       <c r="N159" s="11">
-        <f ca="1">IF($C159="","",$C159+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A159)="Finalized",$K159&lt;&gt;""),"",IF($C159="","",$C159+365-TODAY()))</f>
         <v>315</v>
       </c>
       <c r="O159" s="9">
+        <f>IF(AND(TRIM($A159)="Finalized",$K159&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P159" s="8" t="s">
@@ -31311,14 +31469,15 @@
         <v>-37</v>
       </c>
       <c r="M160" s="11" t="str">
-        <f ca="1">IF($C160="","",$C160+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A160)="Finalized",$K160&lt;&gt;""),"",IF($C160="","",$C160+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N160" s="11" t="str">
-        <f ca="1">IF($C160="","",$C160+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A160)="Finalized",$K160&lt;&gt;""),"",IF($C160="","",$C160+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O160" s="9">
+        <f>IF(AND(TRIM($A160)="Finalized",$K160&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P160" s="8" t="s">
@@ -31429,14 +31588,15 @@
         <v>-36</v>
       </c>
       <c r="M161" s="11">
-        <f ca="1">IF($F161="","",$F161+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A161)="Finalized",$K161&lt;&gt;""),"",IF($F161="","",$F161+90-TODAY()))</f>
         <v>-36</v>
       </c>
       <c r="N161" s="11" t="str">
-        <f ca="1">IF($C161="","",$C161+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A161)="Finalized",$K161&lt;&gt;""),"",IF($C161="","",$C161+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O161" s="9">
+        <f>IF(AND(TRIM($A161)="Finalized",$K161&lt;&gt;""),"",DATE(2026,9,3))</f>
         <v>46268</v>
       </c>
       <c r="P161" s="8" t="s">
@@ -31549,14 +31709,15 @@
         <v>-35</v>
       </c>
       <c r="M162" s="11">
-        <f ca="1">IF($C162="","",$C162+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A162)="Finalized",$K162&lt;&gt;""),"",IF($C162="","",$C162+180-TODAY()))</f>
         <v>58</v>
       </c>
       <c r="N162" s="11">
-        <f ca="1">IF($C162="","",$C162+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A162)="Finalized",$K162&lt;&gt;""),"",IF($C162="","",$C162+180-TODAY()))</f>
         <v>58</v>
       </c>
       <c r="O162" s="9">
+        <f>IF(AND(TRIM($A162)="Finalized",$K162&lt;&gt;""),"",DATE(2026,9,4))</f>
         <v>46269</v>
       </c>
       <c r="P162" s="8" t="s">
@@ -31669,14 +31830,15 @@
         <v>-33</v>
       </c>
       <c r="M163" s="11">
-        <f ca="1">IF($C163="","",$C163+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A163)="Finalized",$K163&lt;&gt;""),"",IF($C163="","",$C163+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="N163" s="11">
-        <f ca="1">IF($C163="","",$C163+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A163)="Finalized",$K163&lt;&gt;""),"",IF($C163="","",$C163+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="O163" s="9">
+        <f>IF(AND(TRIM($A163)="Finalized",$K163&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P163" s="8" t="s">
@@ -31795,14 +31957,15 @@
         <v>-33</v>
       </c>
       <c r="M164" s="11" t="str">
-        <f ca="1">IF($C164="","",$C164+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A164)="Finalized",$K164&lt;&gt;""),"",IF($C164="","",$C164+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N164" s="11" t="str">
-        <f ca="1">IF($C164="","",$C164+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A164)="Finalized",$K164&lt;&gt;""),"",IF($C164="","",$C164+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O164" s="9">
+        <f>IF(AND(TRIM($A164)="Finalized",$K164&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P164" s="8" t="s">
@@ -31919,14 +32082,15 @@
         <v>-33</v>
       </c>
       <c r="M165" s="11">
-        <f ca="1">IF($F165="","",$F165+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A165)="Finalized",$K165&lt;&gt;""),"",IF($F165="","",$F165+90-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="N165" s="11">
-        <f ca="1">IF($C165="","",$C165+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A165)="Finalized",$K165&lt;&gt;""),"",IF($C165="","",$C165+540-TODAY()))</f>
         <v>472</v>
       </c>
       <c r="O165" s="9">
+        <f>IF(AND(TRIM($A165)="Finalized",$K165&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P165" s="8" t="s">
@@ -32045,14 +32209,15 @@
         <v>-33</v>
       </c>
       <c r="M166" s="11">
-        <f ca="1">IF($C166="","",$C166+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A166)="Finalized",$K166&lt;&gt;""),"",IF($C166="","",$C166+180-TODAY()))</f>
         <v>144</v>
       </c>
       <c r="N166" s="11">
-        <f ca="1">IF($C166="","",$C166+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A166)="Finalized",$K166&lt;&gt;""),"",IF($C166="","",$C166+365-TODAY()))</f>
         <v>329</v>
       </c>
       <c r="O166" s="9">
+        <f>IF(AND(TRIM($A166)="Finalized",$K166&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P166" s="8" t="s">
@@ -32171,14 +32336,15 @@
         <v>-33</v>
       </c>
       <c r="M167" s="11">
-        <f ca="1">IF($F167="","",$F167+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A167)="Finalized",$K167&lt;&gt;""),"",IF($F167="","",$F167+90-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="N167" s="11">
-        <f ca="1">IF($C167="","",$C167+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A167)="Finalized",$K167&lt;&gt;""),"",IF($C167="","",$C167+180-TODAY()))</f>
         <v>101</v>
       </c>
       <c r="O167" s="9">
+        <f>IF(AND(TRIM($A167)="Finalized",$K167&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P167" s="8" t="s">
@@ -32299,14 +32465,15 @@
         <v>-33</v>
       </c>
       <c r="M168" s="11">
-        <f ca="1">IF($F168="","",$F168+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A168)="Finalized",$K168&lt;&gt;""),"",IF($F168="","",$F168+90-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="N168" s="11">
-        <f ca="1">IF($C168="","",$C168+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A168)="Finalized",$K168&lt;&gt;""),"",IF($C168="","",$C168+365-TODAY()))</f>
         <v>342</v>
       </c>
       <c r="O168" s="9">
+        <f>IF(AND(TRIM($A168)="Finalized",$K168&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P168" s="8" t="s">
@@ -32417,14 +32584,15 @@
         <v>-33</v>
       </c>
       <c r="M169" s="11">
-        <f ca="1">IF($F169="","",$F169+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A169)="Finalized",$K169&lt;&gt;""),"",IF($F169="","",$F169+90-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="N169" s="11">
-        <f ca="1">IF($C169="","",$C169+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A169)="Finalized",$K169&lt;&gt;""),"",IF($C169="","",$C169+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O169" s="9">
+        <f>IF(AND(TRIM($A169)="Finalized",$K169&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P169" s="8" t="s">
@@ -32541,14 +32709,15 @@
         <v>-32</v>
       </c>
       <c r="M170" s="11">
-        <f ca="1">IF($C170="","",$C170+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A170)="Finalized",$K170&lt;&gt;""),"",IF($C170="","",$C170+365-TODAY()))</f>
         <v>292</v>
       </c>
       <c r="N170" s="11">
-        <f ca="1">IF($C170="","",$C170+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A170)="Finalized",$K170&lt;&gt;""),"",IF($C170="","",$C170+365-TODAY()))</f>
         <v>292</v>
       </c>
       <c r="O170" s="9">
+        <f>IF(AND(TRIM($A170)="Finalized",$K170&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P170" s="8" t="s">
@@ -32657,14 +32826,15 @@
         <v>-32</v>
       </c>
       <c r="M171" s="11">
-        <f ca="1">IF($C171="","",$C171+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A171)="Finalized",$K171&lt;&gt;""),"",IF($C171="","",$C171+180-TODAY()))</f>
         <v>115</v>
       </c>
       <c r="N171" s="11">
-        <f ca="1">IF($C171="","",$C171+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A171)="Finalized",$K171&lt;&gt;""),"",IF($C171="","",$C171+365-TODAY()))</f>
         <v>300</v>
       </c>
       <c r="O171" s="9">
+        <f>IF(AND(TRIM($A171)="Finalized",$K171&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P171" s="8" t="s">
@@ -32779,14 +32949,15 @@
         <v>-32</v>
       </c>
       <c r="M172" s="11">
-        <f ca="1">IF($C172="","",$C172+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A172)="Finalized",$K172&lt;&gt;""),"",IF($C172="","",$C172+180-TODAY()))</f>
         <v>123</v>
       </c>
       <c r="N172" s="11">
-        <f ca="1">IF($C172="","",$C172+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A172)="Finalized",$K172&lt;&gt;""),"",IF($C172="","",$C172+365-TODAY()))</f>
         <v>308</v>
       </c>
       <c r="O172" s="9">
+        <f>IF(AND(TRIM($A172)="Finalized",$K172&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P172" s="8" t="s">
@@ -32901,14 +33072,15 @@
         <v>-31</v>
       </c>
       <c r="M173" s="11">
-        <f ca="1">IF($C173="","",$C173+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A173)="Finalized",$K173&lt;&gt;""),"",IF($C173="","",$C173+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="N173" s="11">
-        <f ca="1">IF($C173="","",$C173+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A173)="Finalized",$K173&lt;&gt;""),"",IF($C173="","",$C173+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="O173" s="9">
+        <f>IF(AND(TRIM($A173)="Finalized",$K173&lt;&gt;""),"",DATE(2026,9,8))</f>
         <v>46273</v>
       </c>
       <c r="P173" s="8" t="s">
@@ -33019,14 +33191,15 @@
         <v>-31</v>
       </c>
       <c r="M174" s="11">
-        <f ca="1">IF($F174="","",$F174+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A174)="Finalized",$K174&lt;&gt;""),"",IF($F174="","",$F174+90-TODAY()))</f>
         <v>-31</v>
       </c>
       <c r="N174" s="11">
-        <f ca="1">IF($C174="","",$C174+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A174)="Finalized",$K174&lt;&gt;""),"",IF($C174="","",$C174+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="O174" s="9">
+        <f>IF(AND(TRIM($A174)="Finalized",$K174&lt;&gt;""),"",DATE(2026,9,8))</f>
         <v>46273</v>
       </c>
       <c r="P174" s="8" t="s">
@@ -33137,14 +33310,15 @@
         <v>-30</v>
       </c>
       <c r="M175" s="11">
-        <f ca="1">IF($F175="","",$F175+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A175)="Finalized",$K175&lt;&gt;""),"",IF($F175="","",$F175+90-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="N175" s="11">
-        <f ca="1">IF($C175="","",$C175+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A175)="Finalized",$K175&lt;&gt;""),"",IF($C175="","",$C175+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O175" s="9">
+        <f>IF(AND(TRIM($A175)="Finalized",$K175&lt;&gt;""),"",DATE(2026,9,9))</f>
         <v>46274</v>
       </c>
       <c r="P175" s="8" t="s">
@@ -33257,14 +33431,15 @@
         <v>-29</v>
       </c>
       <c r="M176" s="11">
-        <f ca="1">IF($C176="","",$C176+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A176)="Finalized",$K176&lt;&gt;""),"",IF($C176="","",$C176+180-TODAY()))</f>
         <v>73</v>
       </c>
       <c r="N176" s="11">
-        <f ca="1">IF($C176="","",$C176+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A176)="Finalized",$K176&lt;&gt;""),"",IF($C176="","",$C176+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O176" s="9">
+        <f>IF(AND(TRIM($A176)="Finalized",$K176&lt;&gt;""),"",DATE(2026,9,10))</f>
         <v>46275</v>
       </c>
       <c r="P176" s="8" t="s">
@@ -33375,14 +33550,15 @@
         <v>-29</v>
       </c>
       <c r="M177" s="11">
-        <f ca="1">IF($F177="","",$F177+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A177)="Finalized",$K177&lt;&gt;""),"",IF($F177="","",$F177+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="N177" s="11">
-        <f ca="1">IF($C177="","",$C177+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A177)="Finalized",$K177&lt;&gt;""),"",IF($C177="","",$C177+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="O177" s="9">
+        <f>IF(AND(TRIM($A177)="Finalized",$K177&lt;&gt;""),"",DATE(2026,9,10))</f>
         <v>46275</v>
       </c>
       <c r="P177" s="8" t="s">
@@ -33495,14 +33671,15 @@
         <v>-28</v>
       </c>
       <c r="M178" s="11">
-        <f ca="1">IF($C178="","",$C178+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A178)="Finalized",$K178&lt;&gt;""),"",IF($C178="","",$C178+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="N178" s="11">
-        <f ca="1">IF($C178="","",$C178+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A178)="Finalized",$K178&lt;&gt;""),"",IF($C178="","",$C178+90-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="O178" s="9">
+        <f>IF(AND(TRIM($A178)="Finalized",$K178&lt;&gt;""),"",DATE(2026,9,11))</f>
         <v>46276</v>
       </c>
       <c r="P178" s="8" t="s">
@@ -33615,14 +33792,15 @@
         <v>-25</v>
       </c>
       <c r="M179" s="11" t="str">
-        <f ca="1">IF($C179="","",$C179+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A179)="Finalized",$K179&lt;&gt;""),"",IF($C179="","",$C179+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N179" s="11" t="str">
-        <f ca="1">IF($C179="","",$C179+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A179)="Finalized",$K179&lt;&gt;""),"",IF($C179="","",$C179+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O179" s="9">
+        <f>IF(AND(TRIM($A179)="Finalized",$K179&lt;&gt;""),"",DATE(2026,9,14))</f>
         <v>46279</v>
       </c>
       <c r="P179" s="8" t="s">
@@ -33731,14 +33909,15 @@
         <v>-25</v>
       </c>
       <c r="M180" s="11">
-        <f ca="1">IF($C180="","",$C180+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A180)="Finalized",$K180&lt;&gt;""),"",IF($C180="","",$C180+180-TODAY()))</f>
         <v>116</v>
       </c>
       <c r="N180" s="11">
-        <f ca="1">IF($C180="","",$C180+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A180)="Finalized",$K180&lt;&gt;""),"",IF($C180="","",$C180+365-TODAY()))</f>
         <v>301</v>
       </c>
       <c r="O180" s="9">
+        <f>IF(AND(TRIM($A180)="Finalized",$K180&lt;&gt;""),"",DATE(2026,9,14))</f>
         <v>46279</v>
       </c>
       <c r="P180" s="8" t="s">
@@ -33849,14 +34028,15 @@
         <v>-24</v>
       </c>
       <c r="M181" s="11">
-        <f ca="1">IF($F181="","",$F181+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A181)="Finalized",$K181&lt;&gt;""),"",IF($F181="","",$F181+90-TODAY()))</f>
         <v>-24</v>
       </c>
       <c r="N181" s="11">
-        <f ca="1">IF($C181="","",$C181+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A181)="Finalized",$K181&lt;&gt;""),"",IF($C181="","",$C181+180-TODAY()))</f>
         <v>101</v>
       </c>
       <c r="O181" s="9">
+        <f>IF(AND(TRIM($A181)="Finalized",$K181&lt;&gt;""),"",DATE(2026,9,15))</f>
         <v>46280</v>
       </c>
       <c r="P181" s="8" t="s">
@@ -33971,14 +34151,15 @@
         <v>-23</v>
       </c>
       <c r="M182" s="11">
-        <f ca="1">IF($C182="","",$C182+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A182)="Finalized",$K182&lt;&gt;""),"",IF($C182="","",$C182+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="N182" s="11">
-        <f ca="1">IF($C182="","",$C182+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A182)="Finalized",$K182&lt;&gt;""),"",IF($C182="","",$C182+90-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="O182" s="9">
+        <f>IF(AND(TRIM($A182)="Finalized",$K182&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P182" s="8" t="s">
@@ -34093,14 +34274,15 @@
         <v>-23</v>
       </c>
       <c r="M183" s="11">
-        <f ca="1">IF($C183="","",$C183+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A183)="Finalized",$K183&lt;&gt;""),"",IF($C183="","",$C183+180-TODAY()))</f>
         <v>93</v>
       </c>
       <c r="N183" s="11">
-        <f ca="1">IF($C183="","",$C183+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A183)="Finalized",$K183&lt;&gt;""),"",IF($C183="","",$C183+365-TODAY()))</f>
         <v>278</v>
       </c>
       <c r="O183" s="9">
+        <f>IF(AND(TRIM($A183)="Finalized",$K183&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P183" s="8" t="s">
@@ -34211,14 +34393,15 @@
         <v>-23</v>
       </c>
       <c r="M184" s="11">
-        <f ca="1">IF($C184="","",$C184+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A184)="Finalized",$K184&lt;&gt;""),"",IF($C184="","",$C184+365-TODAY()))</f>
         <v>190</v>
       </c>
       <c r="N184" s="11">
-        <f ca="1">IF($C184="","",$C184+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A184)="Finalized",$K184&lt;&gt;""),"",IF($C184="","",$C184+365-TODAY()))</f>
         <v>190</v>
       </c>
       <c r="O184" s="9">
+        <f>IF(AND(TRIM($A184)="Finalized",$K184&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P184" s="8" t="s">
@@ -34329,14 +34512,15 @@
         <v>-23</v>
       </c>
       <c r="M185" s="11" t="str">
-        <f ca="1">IF($C185="","",$C185+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A185)="Finalized",$K185&lt;&gt;""),"",IF($C185="","",$C185+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N185" s="11" t="str">
-        <f ca="1">IF($C185="","",$C185+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A185)="Finalized",$K185&lt;&gt;""),"",IF($C185="","",$C185+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O185" s="9">
+        <f>IF(AND(TRIM($A185)="Finalized",$K185&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P185" s="8" t="s">
@@ -34445,14 +34629,15 @@
         <v>-23</v>
       </c>
       <c r="M186" s="11" t="str">
-        <f ca="1">IF($C186="","",$C186+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A186)="Finalized",$K186&lt;&gt;""),"",IF($C186="","",$C186+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N186" s="11" t="str">
-        <f ca="1">IF($C186="","",$C186+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A186)="Finalized",$K186&lt;&gt;""),"",IF($C186="","",$C186+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O186" s="9">
+        <f>IF(AND(TRIM($A186)="Finalized",$K186&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P186" s="8" t="s">
@@ -34567,14 +34752,15 @@
         <v>-19</v>
       </c>
       <c r="M187" s="11">
-        <f ca="1">IF($C187="","",$C187+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A187)="Finalized",$K187&lt;&gt;""),"",IF($C187="","",$C187+180-TODAY()))</f>
         <v>146</v>
       </c>
       <c r="N187" s="11">
-        <f ca="1">IF($C187="","",$C187+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A187)="Finalized",$K187&lt;&gt;""),"",IF($C187="","",$C187+365-TODAY()))</f>
         <v>331</v>
       </c>
       <c r="O187" s="9">
+        <f>IF(AND(TRIM($A187)="Finalized",$K187&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P187" s="8" t="s">
@@ -34693,14 +34879,15 @@
         <v>-19</v>
       </c>
       <c r="M188" s="11">
-        <f ca="1">IF($F188="","",$F188+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A188)="Finalized",$K188&lt;&gt;""),"",IF($F188="","",$F188+90-TODAY()))</f>
         <v>-19</v>
       </c>
       <c r="N188" s="11">
-        <f ca="1">IF($C188="","",$C188+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A188)="Finalized",$K188&lt;&gt;""),"",IF($C188="","",$C188+540-TODAY()))</f>
         <v>476</v>
       </c>
       <c r="O188" s="9">
+        <f>IF(AND(TRIM($A188)="Finalized",$K188&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P188" s="8" t="s">
@@ -34817,14 +35004,15 @@
         <v>-19</v>
       </c>
       <c r="M189" s="11">
-        <f ca="1">IF($C189="","",$C189+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A189)="Finalized",$K189&lt;&gt;""),"",IF($C189="","",$C189+180-TODAY()))</f>
         <v>80</v>
       </c>
       <c r="N189" s="11">
-        <f ca="1">IF($C189="","",$C189+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A189)="Finalized",$K189&lt;&gt;""),"",IF($C189="","",$C189+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="O189" s="9">
+        <f>IF(AND(TRIM($A189)="Finalized",$K189&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P189" s="8" t="s">
@@ -34937,14 +35125,15 @@
         <v>-19</v>
       </c>
       <c r="M190" s="11" t="str">
-        <f ca="1">IF($C190="","",$C190+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A190)="Finalized",$K190&lt;&gt;""),"",IF($C190="","",$C190+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N190" s="11" t="str">
-        <f ca="1">IF($C190="","",$C190+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A190)="Finalized",$K190&lt;&gt;""),"",IF($C190="","",$C190+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O190" s="9">
+        <f>IF(AND(TRIM($A190)="Finalized",$K190&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P190" s="8" t="s">
@@ -35053,14 +35242,15 @@
         <v>-18</v>
       </c>
       <c r="M191" s="11">
-        <f ca="1">IF($C191="","",$C191+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A191)="Finalized",$K191&lt;&gt;""),"",IF($C191="","",$C191+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="N191" s="11">
-        <f ca="1">IF($C191="","",$C191+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A191)="Finalized",$K191&lt;&gt;""),"",IF($C191="","",$C191+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="O191" s="9">
+        <f>IF(AND(TRIM($A191)="Finalized",$K191&lt;&gt;""),"",DATE(2026,9,21))</f>
         <v>46286</v>
       </c>
       <c r="P191" s="8" t="s">
@@ -35173,14 +35363,15 @@
         <v>-17</v>
       </c>
       <c r="M192" s="11">
-        <f ca="1">IF($C192="","",$C192+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A192)="Finalized",$K192&lt;&gt;""),"",IF($C192="","",$C192+180-TODAY()))</f>
         <v>148</v>
       </c>
       <c r="N192" s="11">
-        <f ca="1">IF($C192="","",$C192+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A192)="Finalized",$K192&lt;&gt;""),"",IF($C192="","",$C192+365-TODAY()))</f>
         <v>333</v>
       </c>
       <c r="O192" s="9">
+        <f>IF(AND(TRIM($A192)="Finalized",$K192&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P192" s="8" t="s">
@@ -35293,14 +35484,15 @@
         <v>-17</v>
       </c>
       <c r="M193" s="11">
-        <f ca="1">IF($F193="","",$F193+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A193)="Finalized",$K193&lt;&gt;""),"",IF($F193="","",$F193+90-TODAY()))</f>
         <v>-17</v>
       </c>
       <c r="N193" s="11" t="str">
-        <f ca="1">IF($C193="","",$C193+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A193)="Finalized",$K193&lt;&gt;""),"",IF($C193="","",$C193+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O193" s="9">
+        <f>IF(AND(TRIM($A193)="Finalized",$K193&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P193" s="8" t="s">
@@ -35409,14 +35601,15 @@
         <v>-17</v>
       </c>
       <c r="M194" s="11">
-        <f ca="1">IF($C194="","",$C194+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A194)="Finalized",$K194&lt;&gt;""),"",IF($C194="","",$C194+180-TODAY()))</f>
         <v>87</v>
       </c>
       <c r="N194" s="11">
-        <f ca="1">IF($C194="","",$C194+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A194)="Finalized",$K194&lt;&gt;""),"",IF($C194="","",$C194+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="O194" s="9">
+        <f>IF(AND(TRIM($A194)="Finalized",$K194&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P194" s="8" t="s">
@@ -35531,14 +35724,15 @@
         <v>-16</v>
       </c>
       <c r="M195" s="11">
-        <f ca="1">IF($F195="","",$F195+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A195)="Finalized",$K195&lt;&gt;""),"",IF($F195="","",$F195+365-TODAY()))</f>
         <v>229</v>
       </c>
       <c r="N195" s="11">
-        <f ca="1">IF($F195="","",$F195+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A195)="Finalized",$K195&lt;&gt;""),"",IF($F195="","",$F195+365-TODAY()))</f>
         <v>229</v>
       </c>
       <c r="O195" s="9">
+        <f>IF(AND(TRIM($A195)="Finalized",$K195&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P195" s="8" t="s">
@@ -35657,14 +35851,15 @@
         <v>-16</v>
       </c>
       <c r="M196" s="11" t="str">
-        <f ca="1">IF($C196="","",$C196+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A196)="Finalized",$K196&lt;&gt;""),"",IF($C196="","",$C196+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N196" s="11" t="str">
-        <f ca="1">IF($C196="","",$C196+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A196)="Finalized",$K196&lt;&gt;""),"",IF($C196="","",$C196+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O196" s="9">
+        <f>IF(AND(TRIM($A196)="Finalized",$K196&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P196" s="8" t="s">
@@ -35773,14 +35968,15 @@
         <v>-16</v>
       </c>
       <c r="M197" s="11" t="str">
-        <f ca="1">IF($C197="","",$C197+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A197)="Finalized",$K197&lt;&gt;""),"",IF($C197="","",$C197+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N197" s="11" t="str">
-        <f ca="1">IF($C197="","",$C197+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A197)="Finalized",$K197&lt;&gt;""),"",IF($C197="","",$C197+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O197" s="9">
+        <f>IF(AND(TRIM($A197)="Finalized",$K197&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P197" s="8" t="s">
@@ -35889,14 +36085,15 @@
         <v>-16</v>
       </c>
       <c r="M198" s="11" t="str">
-        <f ca="1">IF($C198="","",$C198+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A198)="Finalized",$K198&lt;&gt;""),"",IF($C198="","",$C198+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N198" s="11" t="str">
-        <f ca="1">IF($C198="","",$C198+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A198)="Finalized",$K198&lt;&gt;""),"",IF($C198="","",$C198+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O198" s="9">
+        <f>IF(AND(TRIM($A198)="Finalized",$K198&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P198" s="8" t="s">
@@ -36013,14 +36210,15 @@
         <v>-16</v>
       </c>
       <c r="M199" s="11">
-        <f ca="1">IF($C199="","",$C199+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A199)="Finalized",$K199&lt;&gt;""),"",IF($C199="","",$C199+180-TODAY()))</f>
         <v>86</v>
       </c>
       <c r="N199" s="11">
-        <f ca="1">IF($C199="","",$C199+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A199)="Finalized",$K199&lt;&gt;""),"",IF($C199="","",$C199+365-TODAY()))</f>
         <v>271</v>
       </c>
       <c r="O199" s="9">
+        <f>IF(AND(TRIM($A199)="Finalized",$K199&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P199" s="8" t="s">
@@ -36135,14 +36333,15 @@
         <v>-16</v>
       </c>
       <c r="M200" s="11">
-        <f ca="1">IF($C200="","",$C200+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A200)="Finalized",$K200&lt;&gt;""),"",IF($C200="","",$C200+365-TODAY()))</f>
         <v>320</v>
       </c>
       <c r="N200" s="11">
-        <f ca="1">IF($C200="","",$C200+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A200)="Finalized",$K200&lt;&gt;""),"",IF($C200="","",$C200+365-TODAY()))</f>
         <v>320</v>
       </c>
       <c r="O200" s="9">
+        <f>IF(AND(TRIM($A200)="Finalized",$K200&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P200" s="8" t="s">
@@ -36253,14 +36452,15 @@
         <v>-15</v>
       </c>
       <c r="M201" s="11">
-        <f ca="1">IF($C201="","",$C201+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A201)="Finalized",$K201&lt;&gt;""),"",IF($C201="","",$C201+180-TODAY()))</f>
         <v>71</v>
       </c>
       <c r="N201" s="11">
-        <f ca="1">IF($C201="","",$C201+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A201)="Finalized",$K201&lt;&gt;""),"",IF($C201="","",$C201+180-TODAY()))</f>
         <v>71</v>
       </c>
       <c r="O201" s="9">
+        <f>IF(AND(TRIM($A201)="Finalized",$K201&lt;&gt;""),"",DATE(2026,9,24))</f>
         <v>46289</v>
       </c>
       <c r="P201" s="8" t="s">
@@ -36371,14 +36571,15 @@
         <v>-12</v>
       </c>
       <c r="M202" s="11">
-        <f ca="1">IF($F202="","",$F202+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A202)="Finalized",$K202&lt;&gt;""),"",IF($F202="","",$F202+90-TODAY()))</f>
         <v>-12</v>
       </c>
       <c r="N202" s="11">
-        <f ca="1">IF($C202="","",$C202+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A202)="Finalized",$K202&lt;&gt;""),"",IF($C202="","",$C202+365-TODAY()))</f>
         <v>328</v>
       </c>
       <c r="O202" s="9">
+        <f>IF(AND(TRIM($A202)="Finalized",$K202&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P202" s="8" t="s">
@@ -36491,14 +36692,15 @@
         <v>-12</v>
       </c>
       <c r="M203" s="11">
-        <f ca="1">IF($C203="","",$C203+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A203)="Finalized",$K203&lt;&gt;""),"",IF($C203="","",$C203+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="N203" s="11">
-        <f ca="1">IF($C203="","",$C203+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A203)="Finalized",$K203&lt;&gt;""),"",IF($C203="","",$C203+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="O203" s="9">
+        <f>IF(AND(TRIM($A203)="Finalized",$K203&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P203" s="8" t="s">
@@ -36613,14 +36815,15 @@
         <v>-12</v>
       </c>
       <c r="M204" s="11">
-        <f ca="1">IF($F204="","",$F204+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A204)="Finalized",$K204&lt;&gt;""),"",IF($F204="","",$F204+90-TODAY()))</f>
         <v>-12</v>
       </c>
       <c r="N204" s="11">
-        <f ca="1">IF($C204="","",$C204+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A204)="Finalized",$K204&lt;&gt;""),"",IF($C204="","",$C204+365-TODAY()))</f>
         <v>271</v>
       </c>
       <c r="O204" s="9">
+        <f>IF(AND(TRIM($A204)="Finalized",$K204&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P204" s="8" t="s">
@@ -36731,14 +36934,15 @@
         <v>-12</v>
       </c>
       <c r="M205" s="11">
-        <f ca="1">IF($F205="","",$F205+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A205)="Finalized",$K205&lt;&gt;""),"",IF($F205="","",$F205+90-TODAY()))</f>
         <v>-12</v>
       </c>
       <c r="N205" s="11">
-        <f ca="1">IF($C205="","",$C205+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A205)="Finalized",$K205&lt;&gt;""),"",IF($C205="","",$C205+540-TODAY()))</f>
         <v>498</v>
       </c>
       <c r="O205" s="9">
+        <f>IF(AND(TRIM($A205)="Finalized",$K205&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P205" s="8" t="s">
@@ -36857,14 +37061,15 @@
         <v>-12</v>
       </c>
       <c r="M206" s="11">
-        <f ca="1">IF($C206="","",$C206+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A206)="Finalized",$K206&lt;&gt;""),"",IF($C206="","",$C206+180-TODAY()))</f>
         <v>152</v>
       </c>
       <c r="N206" s="11">
-        <f ca="1">IF($C206="","",$C206+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A206)="Finalized",$K206&lt;&gt;""),"",IF($C206="","",$C206+365-TODAY()))</f>
         <v>337</v>
       </c>
       <c r="O206" s="9">
+        <f>IF(AND(TRIM($A206)="Finalized",$K206&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P206" s="8" t="s">
@@ -36975,14 +37180,15 @@
         <v>-12</v>
       </c>
       <c r="M207" s="11">
-        <f ca="1">IF($C207="","",$C207+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A207)="Finalized",$K207&lt;&gt;""),"",IF($C207="","",$C207+365-TODAY()))</f>
         <v>326</v>
       </c>
       <c r="N207" s="11">
-        <f ca="1">IF($C207="","",$C207+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A207)="Finalized",$K207&lt;&gt;""),"",IF($C207="","",$C207+365-TODAY()))</f>
         <v>326</v>
       </c>
       <c r="O207" s="9">
+        <f>IF(AND(TRIM($A207)="Finalized",$K207&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P207" s="8" t="s">
@@ -37095,14 +37301,15 @@
         <v>-11</v>
       </c>
       <c r="M208" s="11">
-        <f ca="1">IF($C208="","",$C208+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A208)="Finalized",$K208&lt;&gt;""),"",IF($C208="","",$C208+180-TODAY()))</f>
         <v>156</v>
       </c>
       <c r="N208" s="11">
-        <f ca="1">IF($C208="","",$C208+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A208)="Finalized",$K208&lt;&gt;""),"",IF($C208="","",$C208+365-TODAY()))</f>
         <v>341</v>
       </c>
       <c r="O208" s="9">
+        <f>IF(AND(TRIM($A208)="Finalized",$K208&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P208" s="8" t="s">
@@ -37215,14 +37422,15 @@
         <v>-11</v>
       </c>
       <c r="M209" s="11">
-        <f ca="1">IF($C209="","",$C209+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A209)="Finalized",$K209&lt;&gt;""),"",IF($C209="","",$C209+365-TODAY()))</f>
         <v>326</v>
       </c>
       <c r="N209" s="11">
-        <f ca="1">IF($C209="","",$C209+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A209)="Finalized",$K209&lt;&gt;""),"",IF($C209="","",$C209+365-TODAY()))</f>
         <v>326</v>
       </c>
       <c r="O209" s="9">
+        <f>IF(AND(TRIM($A209)="Finalized",$K209&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P209" s="8" t="s">
@@ -37333,14 +37541,15 @@
         <v>-11</v>
       </c>
       <c r="M210" s="11">
-        <f ca="1">IF($F210="","",$F210+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A210)="Finalized",$K210&lt;&gt;""),"",IF($F210="","",$F210+90-TODAY()))</f>
         <v>-11</v>
       </c>
       <c r="N210" s="11">
-        <f ca="1">IF($C210="","",$C210+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A210)="Finalized",$K210&lt;&gt;""),"",IF($C210="","",$C210+180-TODAY()))</f>
         <v>99</v>
       </c>
       <c r="O210" s="9">
+        <f>IF(AND(TRIM($A210)="Finalized",$K210&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P210" s="8" t="s">
@@ -37453,14 +37662,15 @@
         <v>-2</v>
       </c>
       <c r="M211" s="11">
-        <f ca="1">IF($C211="","",$C211+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A211)="Finalized",$K211&lt;&gt;""),"",IF($C211="","",$C211+180-TODAY()))</f>
         <v>82</v>
       </c>
       <c r="N211" s="11">
-        <f ca="1">IF($C211="","",$C211+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A211)="Finalized",$K211&lt;&gt;""),"",IF($C211="","",$C211+180-TODAY()))</f>
         <v>82</v>
       </c>
       <c r="O211" s="9">
+        <f>IF(AND(TRIM($A211)="Finalized",$K211&lt;&gt;""),"",DATE(2026,10,7))</f>
         <v>46302</v>
       </c>
       <c r="P211" s="8" t="s">
@@ -37575,14 +37785,15 @@
         <v>6</v>
       </c>
       <c r="M212" s="11" t="str">
-        <f ca="1">IF($C212="","",$C212+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A212)="Finalized",$K212&lt;&gt;""),"",IF($C212="","",$C212+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N212" s="11" t="str">
-        <f ca="1">IF($C212="","",$C212+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A212)="Finalized",$K212&lt;&gt;""),"",IF($C212="","",$C212+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O212" s="9">
+        <f>IF(AND(TRIM($A212)="Finalized",$K212&lt;&gt;""),"",DATE(2026,10,15))</f>
         <v>46310</v>
       </c>
       <c r="P212" s="8" t="s">
@@ -37691,14 +37902,15 @@
         <v>7</v>
       </c>
       <c r="M213" s="11">
-        <f ca="1">IF($C213="","",$C213+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A213)="Finalized",$K213&lt;&gt;""),"",IF($C213="","",$C213+365-TODAY()))</f>
         <v>298</v>
       </c>
       <c r="N213" s="11">
-        <f ca="1">IF($C213="","",$C213+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A213)="Finalized",$K213&lt;&gt;""),"",IF($C213="","",$C213+90-TODAY()))</f>
         <v>23</v>
       </c>
       <c r="O213" s="9">
+        <f>IF(AND(TRIM($A213)="Finalized",$K213&lt;&gt;""),"",DATE(2026,10,16))</f>
         <v>46311</v>
       </c>
       <c r="P213" s="8" t="s">
@@ -37807,14 +38019,15 @@
         <v>8</v>
       </c>
       <c r="M214" s="11">
-        <f ca="1">IF($C214="","",$C214+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A214)="Finalized",$K214&lt;&gt;""),"",IF($C214="","",$C214+180-TODAY()))</f>
         <v>80</v>
       </c>
       <c r="N214" s="11">
-        <f ca="1">IF($C214="","",$C214+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A214)="Finalized",$K214&lt;&gt;""),"",IF($C214="","",$C214+180-TODAY()))</f>
         <v>80</v>
       </c>
       <c r="O214" s="9">
+        <f>IF(AND(TRIM($A214)="Finalized",$K214&lt;&gt;""),"",DATE(2026,10,17))</f>
         <v>46312</v>
       </c>
       <c r="P214" s="8" t="s">
@@ -37929,14 +38142,15 @@
         <v>14</v>
       </c>
       <c r="M215" s="11">
-        <f ca="1">IF($F215="","",$F215+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A215)="Finalized",$K215&lt;&gt;""),"",IF($F215="","",$F215+365-TODAY()))</f>
         <v>259</v>
       </c>
       <c r="N215" s="11" t="str">
-        <f ca="1">IF($C215="","",$C215+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A215)="Finalized",$K215&lt;&gt;""),"",IF($C215="","",$C215+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O215" s="9">
+        <f>IF(AND(TRIM($A215)="Finalized",$K215&lt;&gt;""),"",DATE(2026,10,23))</f>
         <v>46318</v>
       </c>
       <c r="P215" s="8" t="s">
@@ -38051,14 +38265,15 @@
         <v>22</v>
       </c>
       <c r="M216" s="11">
-        <f ca="1">IF($F216="","",$F216+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A216)="Finalized",$K216&lt;&gt;""),"",IF($F216="","",$F216+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="N216" s="11">
-        <f ca="1">IF($F216="","",$F216+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A216)="Finalized",$K216&lt;&gt;""),"",IF($F216="","",$F216+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="O216" s="9">
+        <f>IF(AND(TRIM($A216)="Finalized",$K216&lt;&gt;""),"",DATE(2026,10,31))</f>
         <v>46326</v>
       </c>
       <c r="P216" s="8" t="s">
@@ -38173,14 +38388,15 @@
         <v>36</v>
       </c>
       <c r="M217" s="11">
-        <f ca="1">IF($F217="","",$F217+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A217)="Finalized",$K217&lt;&gt;""),"",IF($F217="","",$F217+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="N217" s="11">
-        <f ca="1">IF($C217="","",$C217+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A217)="Finalized",$K217&lt;&gt;""),"",IF($C217="","",$C217+180-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="O217" s="9">
+        <f>IF(AND(TRIM($A217)="Finalized",$K217&lt;&gt;""),"",DATE(2026,11,14))</f>
         <v>46340</v>
       </c>
       <c r="P217" s="8" t="s">
@@ -38295,14 +38511,15 @@
         <v>46</v>
       </c>
       <c r="M218" s="11">
-        <f ca="1">IF($F218="","",$F218+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A218)="Finalized",$K218&lt;&gt;""),"",IF($F218="","",$F218+365-TODAY()))</f>
         <v>231</v>
       </c>
       <c r="N218" s="11">
-        <f ca="1">IF($F218="","",$F218+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A218)="Finalized",$K218&lt;&gt;""),"",IF($F218="","",$F218+365-TODAY()))</f>
         <v>231</v>
       </c>
       <c r="O218" s="9">
+        <f>IF(AND(TRIM($A218)="Finalized",$K218&lt;&gt;""),"",DATE(2026,11,24))</f>
         <v>46350</v>
       </c>
       <c r="P218" s="8" t="s">
@@ -38419,14 +38636,15 @@
         <v>48</v>
       </c>
       <c r="M219" s="11">
-        <f ca="1">IF($F219="","",$F219+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A219)="Finalized",$K219&lt;&gt;""),"",IF($F219="","",$F219+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N219" s="11">
-        <f ca="1">IF($F219="","",$F219+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A219)="Finalized",$K219&lt;&gt;""),"",IF($F219="","",$F219+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="O219" s="9">
+        <f>IF(AND(TRIM($A219)="Finalized",$K219&lt;&gt;""),"",DATE(2026,11,26))</f>
         <v>46352</v>
       </c>
       <c r="P219" s="8" t="s">
@@ -38537,14 +38755,15 @@
         <v>51</v>
       </c>
       <c r="M220" s="11">
-        <f ca="1">IF($F220="","",$F220+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A220)="Finalized",$K220&lt;&gt;""),"",IF($F220="","",$F220+365-TODAY()))</f>
         <v>236</v>
       </c>
       <c r="N220" s="11">
-        <f ca="1">IF($F220="","",$F220+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A220)="Finalized",$K220&lt;&gt;""),"",IF($F220="","",$F220+365-TODAY()))</f>
         <v>236</v>
       </c>
       <c r="O220" s="9">
+        <f>IF(AND(TRIM($A220)="Finalized",$K220&lt;&gt;""),"",DATE(2026,11,29))</f>
         <v>46355</v>
       </c>
       <c r="P220" s="8" t="s">
@@ -38657,14 +38876,15 @@
         <v>71</v>
       </c>
       <c r="M221" s="11">
-        <f ca="1">IF($F221="","",$F221+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A221)="Finalized",$K221&lt;&gt;""),"",IF($F221="","",$F221+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="N221" s="11">
-        <f ca="1">IF($F221="","",$F221+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A221)="Finalized",$K221&lt;&gt;""),"",IF($F221="","",$F221+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="O221" s="9">
+        <f>IF(AND(TRIM($A221)="Finalized",$K221&lt;&gt;""),"",DATE(2026,12,19))</f>
         <v>46375</v>
       </c>
       <c r="P221" s="8" t="s">
@@ -38783,14 +39003,15 @@
         <v>71</v>
       </c>
       <c r="M222" s="11">
-        <f ca="1">IF($F222="","",$F222+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A222)="Finalized",$K222&lt;&gt;""),"",IF($F222="","",$F222+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="N222" s="11">
-        <f ca="1">IF($F222="","",$F222+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A222)="Finalized",$K222&lt;&gt;""),"",IF($F222="","",$F222+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="O222" s="9">
+        <f>IF(AND(TRIM($A222)="Finalized",$K222&lt;&gt;""),"",DATE(2026,12,19))</f>
         <v>46375</v>
       </c>
       <c r="P222" s="8" t="s">
@@ -38907,14 +39128,15 @@
         <v>72</v>
       </c>
       <c r="M223" s="11">
-        <f ca="1">IF($F223="","",$F223+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A223)="Finalized",$K223&lt;&gt;""),"",IF($F223="","",$F223+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N223" s="11">
-        <f ca="1">IF($F223="","",$F223+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A223)="Finalized",$K223&lt;&gt;""),"",IF($F223="","",$F223+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="O223" s="9">
+        <f>IF(AND(TRIM($A223)="Finalized",$K223&lt;&gt;""),"",DATE(2026,12,20))</f>
         <v>46376</v>
       </c>
       <c r="P223" s="8" t="s">
@@ -39033,14 +39255,15 @@
         <v>92</v>
       </c>
       <c r="M224" s="11">
-        <f ca="1">IF($C224="","",$C224+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A224)="Finalized",$K224&lt;&gt;""),"",IF($C224="","",$C224+365-TODAY()))</f>
         <v>132</v>
       </c>
       <c r="N224" s="11">
-        <f ca="1">IF($C224="","",$C224+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A224)="Finalized",$K224&lt;&gt;""),"",IF($C224="","",$C224+120-TODAY()))</f>
         <v>-113</v>
       </c>
       <c r="O224" s="9">
+        <f>IF(AND(TRIM($A224)="Finalized",$K224&lt;&gt;""),"",DATE(2027,1,9))</f>
         <v>46396</v>
       </c>
       <c r="P224" s="8" t="s">
@@ -39153,14 +39376,15 @@
         <v>92</v>
       </c>
       <c r="M225" s="11">
-        <f ca="1">IF($C225="","",$C225+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A225)="Finalized",$K225&lt;&gt;""),"",IF($C225="","",$C225+365-TODAY()))</f>
         <v>209</v>
       </c>
       <c r="N225" s="11">
-        <f ca="1">IF($C225="","",$C225+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A225)="Finalized",$K225&lt;&gt;""),"",IF($C225="","",$C225+120-TODAY()))</f>
         <v>-36</v>
       </c>
       <c r="O225" s="9">
+        <f>IF(AND(TRIM($A225)="Finalized",$K225&lt;&gt;""),"",DATE(2027,1,9))</f>
         <v>46396</v>
       </c>
       <c r="P225" s="8" t="s">
@@ -39275,14 +39499,15 @@
         <v>95</v>
       </c>
       <c r="M226" s="11">
-        <f ca="1">IF($C226="","",$C226+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A226)="Finalized",$K226&lt;&gt;""),"",IF($C226="","",$C226+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="N226" s="11">
-        <f ca="1">IF($C226="","",$C226+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A226)="Finalized",$K226&lt;&gt;""),"",IF($C226="","",$C226+120-TODAY()))</f>
         <v>-49</v>
       </c>
       <c r="O226" s="9">
+        <f>IF(AND(TRIM($A226)="Finalized",$K226&lt;&gt;""),"",DATE(2027,1,12))</f>
         <v>46399</v>
       </c>
       <c r="P226" s="8" t="s">
@@ -39403,14 +39628,15 @@
         <v>102</v>
       </c>
       <c r="M227" s="11">
-        <f ca="1">IF($C227="","",$C227+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A227)="Finalized",$K227&lt;&gt;""),"",IF($C227="","",$C227+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N227" s="11">
-        <f ca="1">IF($C227="","",$C227+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A227)="Finalized",$K227&lt;&gt;""),"",IF($C227="","",$C227+120-TODAY()))</f>
         <v>-37</v>
       </c>
       <c r="O227" s="9">
+        <f>IF(AND(TRIM($A227)="Finalized",$K227&lt;&gt;""),"",DATE(2027,1,19))</f>
         <v>46406</v>
       </c>
       <c r="P227" s="8" t="s">
@@ -39527,14 +39753,15 @@
         <v>102</v>
       </c>
       <c r="M228" s="11">
-        <f ca="1">IF($C228="","",$C228+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A228)="Finalized",$K228&lt;&gt;""),"",IF($C228="","",$C228+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="N228" s="11">
-        <f ca="1">IF($C228="","",$C228+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A228)="Finalized",$K228&lt;&gt;""),"",IF($C228="","",$C228+120-TODAY()))</f>
         <v>-49</v>
       </c>
       <c r="O228" s="9">
+        <f>IF(AND(TRIM($A228)="Finalized",$K228&lt;&gt;""),"",DATE(2027,1,19))</f>
         <v>46406</v>
       </c>
       <c r="P228" s="8" t="s">
@@ -39657,14 +39884,15 @@
         <v>102</v>
       </c>
       <c r="M229" s="11">
-        <f ca="1">IF($C229="","",$C229+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A229)="Finalized",$K229&lt;&gt;""),"",IF($C229="","",$C229+365-TODAY()))</f>
         <v>181</v>
       </c>
       <c r="N229" s="11">
-        <f ca="1">IF($C229="","",$C229+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A229)="Finalized",$K229&lt;&gt;""),"",IF($C229="","",$C229+120-TODAY()))</f>
         <v>-64</v>
       </c>
       <c r="O229" s="9">
+        <f>IF(AND(TRIM($A229)="Finalized",$K229&lt;&gt;""),"",DATE(2027,1,19))</f>
         <v>46406</v>
       </c>
       <c r="P229" s="8" t="s">
@@ -39787,14 +40015,15 @@
         <v>104</v>
       </c>
       <c r="M230" s="11">
-        <f ca="1">IF($C230="","",$C230+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A230)="Finalized",$K230&lt;&gt;""),"",IF($C230="","",$C230+365-TODAY()))</f>
         <v>132</v>
       </c>
       <c r="N230" s="11">
-        <f ca="1">IF($C230="","",$C230+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A230)="Finalized",$K230&lt;&gt;""),"",IF($C230="","",$C230+120-TODAY()))</f>
         <v>-113</v>
       </c>
       <c r="O230" s="9">
+        <f>IF(AND(TRIM($A230)="Finalized",$K230&lt;&gt;""),"",DATE(2027,1,21))</f>
         <v>46408</v>
       </c>
       <c r="P230" s="8" t="s">
@@ -39907,14 +40136,15 @@
         <v>105</v>
       </c>
       <c r="M231" s="11">
-        <f ca="1">IF($C231="","",$C231+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A231)="Finalized",$K231&lt;&gt;""),"",IF($C231="","",$C231+365-TODAY()))</f>
         <v>190</v>
       </c>
       <c r="N231" s="11">
-        <f ca="1">IF($C231="","",$C231+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A231)="Finalized",$K231&lt;&gt;""),"",IF($C231="","",$C231+120-TODAY()))</f>
         <v>-55</v>
       </c>
       <c r="O231" s="9">
+        <f>IF(AND(TRIM($A231)="Finalized",$K231&lt;&gt;""),"",DATE(2027,1,22))</f>
         <v>46409</v>
       </c>
       <c r="P231" s="8" t="s">
@@ -40025,14 +40255,15 @@
         <v>109</v>
       </c>
       <c r="M232" s="11">
-        <f ca="1">IF($C232="","",$C232+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A232)="Finalized",$K232&lt;&gt;""),"",IF($C232="","",$C232+365-TODAY()))</f>
         <v>181</v>
       </c>
       <c r="N232" s="11">
-        <f ca="1">IF($C232="","",$C232+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A232)="Finalized",$K232&lt;&gt;""),"",IF($C232="","",$C232+120-TODAY()))</f>
         <v>-64</v>
       </c>
       <c r="O232" s="9">
+        <f>IF(AND(TRIM($A232)="Finalized",$K232&lt;&gt;""),"",DATE(2027,1,26))</f>
         <v>46413</v>
       </c>
       <c r="P232" s="8" t="s">
@@ -40155,14 +40386,15 @@
         <v>109</v>
       </c>
       <c r="M233" s="11">
-        <f ca="1">IF($C233="","",$C233+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A233)="Finalized",$K233&lt;&gt;""),"",IF($C233="","",$C233+365-TODAY()))</f>
         <v>160</v>
       </c>
       <c r="N233" s="11">
-        <f ca="1">IF($C233="","",$C233+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A233)="Finalized",$K233&lt;&gt;""),"",IF($C233="","",$C233+120-TODAY()))</f>
         <v>-85</v>
       </c>
       <c r="O233" s="9">
+        <f>IF(AND(TRIM($A233)="Finalized",$K233&lt;&gt;""),"",DATE(2027,1,26))</f>
         <v>46413</v>
       </c>
       <c r="P233" s="8" t="s">
@@ -40283,14 +40515,15 @@
         <v>111</v>
       </c>
       <c r="M234" s="11">
-        <f ca="1">IF($C234="","",$C234+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A234)="Finalized",$K234&lt;&gt;""),"",IF($C234="","",$C234+365-TODAY()))</f>
         <v>133</v>
       </c>
       <c r="N234" s="11">
-        <f ca="1">IF($C234="","",$C234+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A234)="Finalized",$K234&lt;&gt;""),"",IF($C234="","",$C234+120-TODAY()))</f>
         <v>-112</v>
       </c>
       <c r="O234" s="9">
+        <f>IF(AND(TRIM($A234)="Finalized",$K234&lt;&gt;""),"",DATE(2027,1,28))</f>
         <v>46415</v>
       </c>
       <c r="P234" s="8" t="s">
@@ -40403,14 +40636,15 @@
         <v>112</v>
       </c>
       <c r="M235" s="11">
-        <f ca="1">IF($C235="","",$C235+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A235)="Finalized",$K235&lt;&gt;""),"",IF($C235="","",$C235+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N235" s="11">
-        <f ca="1">IF($C235="","",$C235+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A235)="Finalized",$K235&lt;&gt;""),"",IF($C235="","",$C235+120-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O235" s="9">
+        <f>IF(AND(TRIM($A235)="Finalized",$K235&lt;&gt;""),"",DATE(2027,1,29))</f>
         <v>46416</v>
       </c>
       <c r="P235" s="8" t="s">
@@ -40527,14 +40761,15 @@
         <v>116</v>
       </c>
       <c r="M236" s="11">
-        <f ca="1">IF($C236="","",$C236+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A236)="Finalized",$K236&lt;&gt;""),"",IF($C236="","",$C236+180-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="N236" s="11">
-        <f ca="1">IF($C236="","",$C236+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A236)="Finalized",$K236&lt;&gt;""),"",IF($C236="","",$C236+365-TODAY()))</f>
         <v>216</v>
       </c>
       <c r="O236" s="9">
+        <f>IF(AND(TRIM($A236)="Finalized",$K236&lt;&gt;""),"",DATE(2027,2,2))</f>
         <v>46420</v>
       </c>
       <c r="P236" s="8" t="s">
@@ -40655,14 +40890,15 @@
         <v>116</v>
       </c>
       <c r="M237" s="11">
-        <f ca="1">IF($C237="","",$C237+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A237)="Finalized",$K237&lt;&gt;""),"",IF($C237="","",$C237+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="N237" s="11">
-        <f ca="1">IF($C237="","",$C237+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A237)="Finalized",$K237&lt;&gt;""),"",IF($C237="","",$C237+120-TODAY()))</f>
         <v>-49</v>
       </c>
       <c r="O237" s="9">
+        <f>IF(AND(TRIM($A237)="Finalized",$K237&lt;&gt;""),"",DATE(2027,2,2))</f>
         <v>46420</v>
       </c>
       <c r="P237" s="8" t="s">
@@ -40785,14 +41021,15 @@
         <v>118</v>
       </c>
       <c r="M238" s="11">
-        <f ca="1">IF($C238="","",$C238+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A238)="Finalized",$K238&lt;&gt;""),"",IF($C238="","",$C238+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N238" s="11">
-        <f ca="1">IF($C238="","",$C238+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A238)="Finalized",$K238&lt;&gt;""),"",IF($C238="","",$C238+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O238" s="9">
+        <f>IF(AND(TRIM($A238)="Finalized",$K238&lt;&gt;""),"",DATE(2027,2,4))</f>
         <v>46422</v>
       </c>
       <c r="P238" s="8" t="s">
@@ -40911,14 +41148,15 @@
         <v>123</v>
       </c>
       <c r="M239" s="11">
-        <f ca="1">IF($C239="","",$C239+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A239)="Finalized",$K239&lt;&gt;""),"",IF($C239="","",$C239+365-TODAY()))</f>
         <v>187</v>
       </c>
       <c r="N239" s="11">
-        <f ca="1">IF($C239="","",$C239+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A239)="Finalized",$K239&lt;&gt;""),"",IF($C239="","",$C239+120-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="O239" s="9">
+        <f>IF(AND(TRIM($A239)="Finalized",$K239&lt;&gt;""),"",DATE(2027,2,9))</f>
         <v>46427</v>
       </c>
       <c r="P239" s="8" t="s">
@@ -41033,14 +41271,15 @@
         <v>124</v>
       </c>
       <c r="M240" s="11">
-        <f ca="1">IF($C240="","",$C240+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A240)="Finalized",$K240&lt;&gt;""),"",IF($C240="","",$C240+365-TODAY()))</f>
         <v>166</v>
       </c>
       <c r="N240" s="11">
-        <f ca="1">IF($C240="","",$C240+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A240)="Finalized",$K240&lt;&gt;""),"",IF($C240="","",$C240+120-TODAY()))</f>
         <v>-79</v>
       </c>
       <c r="O240" s="9">
+        <f>IF(AND(TRIM($A240)="Finalized",$K240&lt;&gt;""),"",DATE(2027,2,10))</f>
         <v>46428</v>
       </c>
       <c r="P240" s="8" t="s">
@@ -41155,14 +41394,15 @@
         <v>126</v>
       </c>
       <c r="M241" s="11">
-        <f ca="1">IF($C241="","",$C241+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A241)="Finalized",$K241&lt;&gt;""),"",IF($C241="","",$C241+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N241" s="11">
-        <f ca="1">IF($C241="","",$C241+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A241)="Finalized",$K241&lt;&gt;""),"",IF($C241="","",$C241+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O241" s="9">
+        <f>IF(AND(TRIM($A241)="Finalized",$K241&lt;&gt;""),"",DATE(2027,2,12))</f>
         <v>46430</v>
       </c>
       <c r="P241" s="8" t="s">
@@ -41275,14 +41515,15 @@
         <v>126</v>
       </c>
       <c r="M242" s="11">
-        <f ca="1">IF($C242="","",$C242+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A242)="Finalized",$K242&lt;&gt;""),"",IF($C242="","",$C242+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N242" s="11">
-        <f ca="1">IF($C242="","",$C242+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A242)="Finalized",$K242&lt;&gt;""),"",IF($C242="","",$C242+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O242" s="9">
+        <f>IF(AND(TRIM($A242)="Finalized",$K242&lt;&gt;""),"",DATE(2027,2,12))</f>
         <v>46430</v>
       </c>
       <c r="P242" s="8" t="s">
@@ -41401,14 +41642,15 @@
         <v>127</v>
       </c>
       <c r="M243" s="11">
-        <f ca="1">IF($C243="","",$C243+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A243)="Finalized",$K243&lt;&gt;""),"",IF($C243="","",$C243+365-TODAY()))</f>
         <v>194</v>
       </c>
       <c r="N243" s="11">
-        <f ca="1">IF($C243="","",$C243+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A243)="Finalized",$K243&lt;&gt;""),"",IF($C243="","",$C243+120-TODAY()))</f>
         <v>-51</v>
       </c>
       <c r="O243" s="9">
+        <f>IF(AND(TRIM($A243)="Finalized",$K243&lt;&gt;""),"",DATE(2027,2,13))</f>
         <v>46431</v>
       </c>
       <c r="P243" s="8" t="s">
@@ -41527,14 +41769,15 @@
         <v>130</v>
       </c>
       <c r="M244" s="11">
-        <f ca="1">IF($C244="","",$C244+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A244)="Finalized",$K244&lt;&gt;""),"",IF($C244="","",$C244+180-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="N244" s="11">
-        <f ca="1">IF($C244="","",$C244+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A244)="Finalized",$K244&lt;&gt;""),"",IF($C244="","",$C244+365-TODAY()))</f>
         <v>216</v>
       </c>
       <c r="O244" s="9">
+        <f>IF(AND(TRIM($A244)="Finalized",$K244&lt;&gt;""),"",DATE(2027,2,16))</f>
         <v>46434</v>
       </c>
       <c r="P244" s="8" t="s">
@@ -41655,14 +41898,15 @@
         <v>131</v>
       </c>
       <c r="M245" s="11">
-        <f ca="1">IF($C245="","",$C245+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A245)="Finalized",$K245&lt;&gt;""),"",IF($C245="","",$C245+365-TODAY()))</f>
         <v>271</v>
       </c>
       <c r="N245" s="11">
-        <f ca="1">IF($C245="","",$C245+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A245)="Finalized",$K245&lt;&gt;""),"",IF($C245="","",$C245+120-TODAY()))</f>
         <v>26</v>
       </c>
       <c r="O245" s="9">
+        <f>IF(AND(TRIM($A245)="Finalized",$K245&lt;&gt;""),"",DATE(2027,2,17))</f>
         <v>46435</v>
       </c>
       <c r="P245" s="8" t="s">
@@ -41775,14 +42019,15 @@
         <v>131</v>
       </c>
       <c r="M246" s="11">
-        <f ca="1">IF($C246="","",$C246+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A246)="Finalized",$K246&lt;&gt;""),"",IF($C246="","",$C246+365-TODAY()))</f>
         <v>189</v>
       </c>
       <c r="N246" s="11">
-        <f ca="1">IF($C246="","",$C246+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A246)="Finalized",$K246&lt;&gt;""),"",IF($C246="","",$C246+120-TODAY()))</f>
         <v>-56</v>
       </c>
       <c r="O246" s="9">
+        <f>IF(AND(TRIM($A246)="Finalized",$K246&lt;&gt;""),"",DATE(2027,2,17))</f>
         <v>46435</v>
       </c>
       <c r="P246" s="8" t="s">
@@ -41897,14 +42142,15 @@
         <v>132</v>
       </c>
       <c r="M247" s="11">
-        <f ca="1">IF($C247="","",$C247+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A247)="Finalized",$K247&lt;&gt;""),"",IF($C247="","",$C247+365-TODAY()))</f>
         <v>271</v>
       </c>
       <c r="N247" s="11">
-        <f ca="1">IF($C247="","",$C247+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A247)="Finalized",$K247&lt;&gt;""),"",IF($C247="","",$C247+120-TODAY()))</f>
         <v>26</v>
       </c>
       <c r="O247" s="9">
+        <f>IF(AND(TRIM($A247)="Finalized",$K247&lt;&gt;""),"",DATE(2027,2,18))</f>
         <v>46436</v>
       </c>
       <c r="P247" s="8" t="s">
@@ -42017,14 +42263,15 @@
         <v>134</v>
       </c>
       <c r="M248" s="11">
-        <f ca="1">IF($C248="","",$C248+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A248)="Finalized",$K248&lt;&gt;""),"",IF($C248="","",$C248+365-TODAY()))</f>
         <v>152</v>
       </c>
       <c r="N248" s="11">
-        <f ca="1">IF($C248="","",$C248+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A248)="Finalized",$K248&lt;&gt;""),"",IF($C248="","",$C248+120-TODAY()))</f>
         <v>-93</v>
       </c>
       <c r="O248" s="9">
+        <f>IF(AND(TRIM($A248)="Finalized",$K248&lt;&gt;""),"",DATE(2027,2,20))</f>
         <v>46438</v>
       </c>
       <c r="P248" s="8" t="s">
@@ -42137,14 +42384,15 @@
         <v>137</v>
       </c>
       <c r="M249" s="11">
-        <f ca="1">IF($C249="","",$C249+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A249)="Finalized",$K249&lt;&gt;""),"",IF($C249="","",$C249+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N249" s="11">
-        <f ca="1">IF($C249="","",$C249+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A249)="Finalized",$K249&lt;&gt;""),"",IF($C249="","",$C249+120-TODAY()))</f>
         <v>-37</v>
       </c>
       <c r="O249" s="9">
+        <f>IF(AND(TRIM($A249)="Finalized",$K249&lt;&gt;""),"",DATE(2027,2,23))</f>
         <v>46441</v>
       </c>
       <c r="P249" s="8" t="s">
@@ -42259,14 +42507,15 @@
         <v>140</v>
       </c>
       <c r="M250" s="11">
-        <f ca="1">IF($C250="","",$C250+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A250)="Finalized",$K250&lt;&gt;""),"",IF($C250="","",$C250+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N250" s="11">
-        <f ca="1">IF($C250="","",$C250+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A250)="Finalized",$K250&lt;&gt;""),"",IF($C250="","",$C250+120-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="O250" s="9">
+        <f>IF(AND(TRIM($A250)="Finalized",$K250&lt;&gt;""),"",DATE(2027,2,26))</f>
         <v>46444</v>
       </c>
       <c r="P250" s="8" t="s">
@@ -42387,14 +42636,15 @@
         <v>144</v>
       </c>
       <c r="M251" s="11">
-        <f ca="1">IF($C251="","",$C251+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A251)="Finalized",$K251&lt;&gt;""),"",IF($C251="","",$C251+365-TODAY()))</f>
         <v>168</v>
       </c>
       <c r="N251" s="11">
-        <f ca="1">IF($C251="","",$C251+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A251)="Finalized",$K251&lt;&gt;""),"",IF($C251="","",$C251+120-TODAY()))</f>
         <v>-77</v>
       </c>
       <c r="O251" s="9">
+        <f>IF(AND(TRIM($A251)="Finalized",$K251&lt;&gt;""),"",DATE(2027,3,2))</f>
         <v>46448</v>
       </c>
       <c r="P251" s="8" t="s">
@@ -42507,14 +42757,15 @@
         <v>146</v>
       </c>
       <c r="M252" s="11">
-        <f ca="1">IF($C252="","",$C252+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A252)="Finalized",$K252&lt;&gt;""),"",IF($C252="","",$C252+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="N252" s="11">
-        <f ca="1">IF($C252="","",$C252+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A252)="Finalized",$K252&lt;&gt;""),"",IF($C252="","",$C252+120-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="O252" s="9">
+        <f>IF(AND(TRIM($A252)="Finalized",$K252&lt;&gt;""),"",DATE(2027,3,4))</f>
         <v>46450</v>
       </c>
       <c r="P252" s="8" t="s">
@@ -42631,14 +42882,15 @@
         <v>152</v>
       </c>
       <c r="M253" s="11">
-        <f ca="1">IF($C253="","",$C253+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A253)="Finalized",$K253&lt;&gt;""),"",IF($C253="","",$C253+365-TODAY()))</f>
         <v>174</v>
       </c>
       <c r="N253" s="11">
-        <f ca="1">IF($C253="","",$C253+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A253)="Finalized",$K253&lt;&gt;""),"",IF($C253="","",$C253+120-TODAY()))</f>
         <v>-71</v>
       </c>
       <c r="O253" s="9">
+        <f>IF(AND(TRIM($A253)="Finalized",$K253&lt;&gt;""),"",DATE(2027,3,10))</f>
         <v>46456</v>
       </c>
       <c r="P253" s="8" t="s">
@@ -42753,14 +43005,15 @@
         <v>154</v>
       </c>
       <c r="M254" s="11">
-        <f ca="1">IF($C254="","",$C254+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A254)="Finalized",$K254&lt;&gt;""),"",IF($C254="","",$C254+365-TODAY()))</f>
         <v>344</v>
       </c>
       <c r="N254" s="11">
-        <f ca="1">IF($C254="","",$C254+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A254)="Finalized",$K254&lt;&gt;""),"",IF($C254="","",$C254+120-TODAY()))</f>
         <v>99</v>
       </c>
       <c r="O254" s="9">
+        <f>IF(AND(TRIM($A254)="Finalized",$K254&lt;&gt;""),"",DATE(2027,3,12))</f>
         <v>46458</v>
       </c>
       <c r="P254" s="8" t="s">
@@ -42869,14 +43122,15 @@
         <v>160</v>
       </c>
       <c r="M255" s="11">
-        <f ca="1">IF($C255="","",$C255+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A255)="Finalized",$K255&lt;&gt;""),"",IF($C255="","",$C255+365-TODAY()))</f>
         <v>169</v>
       </c>
       <c r="N255" s="11">
-        <f ca="1">IF($C255="","",$C255+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A255)="Finalized",$K255&lt;&gt;""),"",IF($C255="","",$C255+120-TODAY()))</f>
         <v>-76</v>
       </c>
       <c r="O255" s="9">
+        <f>IF(AND(TRIM($A255)="Finalized",$K255&lt;&gt;""),"",DATE(2027,3,18))</f>
         <v>46464</v>
       </c>
       <c r="P255" s="8" t="s">
@@ -42989,14 +43243,15 @@
         <v>165</v>
       </c>
       <c r="M256" s="11">
-        <f ca="1">IF($C256="","",$C256+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A256)="Finalized",$K256&lt;&gt;""),"",IF($C256="","",$C256+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="N256" s="11">
-        <f ca="1">IF($C256="","",$C256+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A256)="Finalized",$K256&lt;&gt;""),"",IF($C256="","",$C256+120-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="O256" s="9">
+        <f>IF(AND(TRIM($A256)="Finalized",$K256&lt;&gt;""),"",DATE(2027,3,23))</f>
         <v>46469</v>
       </c>
       <c r="P256" s="8" t="s">
@@ -43115,14 +43370,15 @@
         <v>165</v>
       </c>
       <c r="M257" s="11">
-        <f ca="1">IF($C257="","",$C257+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A257)="Finalized",$K257&lt;&gt;""),"",IF($C257="","",$C257+365-TODAY()))</f>
         <v>183</v>
       </c>
       <c r="N257" s="11">
-        <f ca="1">IF($C257="","",$C257+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A257)="Finalized",$K257&lt;&gt;""),"",IF($C257="","",$C257+120-TODAY()))</f>
         <v>-62</v>
       </c>
       <c r="O257" s="9">
+        <f>IF(AND(TRIM($A257)="Finalized",$K257&lt;&gt;""),"",DATE(2027,3,23))</f>
         <v>46469</v>
       </c>
       <c r="P257" s="8" t="s">
@@ -43239,14 +43495,15 @@
         <v>167</v>
       </c>
       <c r="M258" s="11">
-        <f ca="1">IF($C258="","",$C258+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A258)="Finalized",$K258&lt;&gt;""),"",IF($C258="","",$C258+365-TODAY()))</f>
         <v>183</v>
       </c>
       <c r="N258" s="11">
-        <f ca="1">IF($C258="","",$C258+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A258)="Finalized",$K258&lt;&gt;""),"",IF($C258="","",$C258+120-TODAY()))</f>
         <v>-62</v>
       </c>
       <c r="O258" s="9">
+        <f>IF(AND(TRIM($A258)="Finalized",$K258&lt;&gt;""),"",DATE(2027,3,25))</f>
         <v>46471</v>
       </c>
       <c r="P258" s="8" t="s">
@@ -43359,14 +43616,15 @@
         <v>169</v>
       </c>
       <c r="M259" s="11">
-        <f ca="1">IF($C259="","",$C259+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A259)="Finalized",$K259&lt;&gt;""),"",IF($C259="","",$C259+365-TODAY()))</f>
         <v>329</v>
       </c>
       <c r="N259" s="11">
-        <f ca="1">IF($C259="","",$C259+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A259)="Finalized",$K259&lt;&gt;""),"",IF($C259="","",$C259+120-TODAY()))</f>
         <v>84</v>
       </c>
       <c r="O259" s="9">
+        <f>IF(AND(TRIM($A259)="Finalized",$K259&lt;&gt;""),"",DATE(2027,3,27))</f>
         <v>46473</v>
       </c>
       <c r="P259" s="8" t="s">
@@ -43475,14 +43733,15 @@
         <v>169</v>
       </c>
       <c r="M260" s="11">
-        <f ca="1">IF($C260="","",$C260+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A260)="Finalized",$K260&lt;&gt;""),"",IF($C260="","",$C260+365-TODAY()))</f>
         <v>195</v>
       </c>
       <c r="N260" s="11">
-        <f ca="1">IF($C260="","",$C260+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A260)="Finalized",$K260&lt;&gt;""),"",IF($C260="","",$C260+120-TODAY()))</f>
         <v>-50</v>
       </c>
       <c r="O260" s="9">
+        <f>IF(AND(TRIM($A260)="Finalized",$K260&lt;&gt;""),"",DATE(2027,3,27))</f>
         <v>46473</v>
       </c>
       <c r="P260" s="8" t="s">
@@ -43595,14 +43854,15 @@
         <v>169</v>
       </c>
       <c r="M261" s="11">
-        <f ca="1">IF($C261="","",$C261+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A261)="Finalized",$K261&lt;&gt;""),"",IF($C261="","",$C261+365-TODAY()))</f>
         <v>187</v>
       </c>
       <c r="N261" s="11">
-        <f ca="1">IF($C261="","",$C261+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A261)="Finalized",$K261&lt;&gt;""),"",IF($C261="","",$C261+120-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="O261" s="9">
+        <f>IF(AND(TRIM($A261)="Finalized",$K261&lt;&gt;""),"",DATE(2027,3,27))</f>
         <v>46473</v>
       </c>
       <c r="P261" s="8" t="s">
@@ -43717,14 +43977,15 @@
         <v>172</v>
       </c>
       <c r="M262" s="11">
-        <f ca="1">IF($C262="","",$C262+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A262)="Finalized",$K262&lt;&gt;""),"",IF($C262="","",$C262+365-TODAY()))</f>
         <v>186</v>
       </c>
       <c r="N262" s="11">
-        <f ca="1">IF($C262="","",$C262+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A262)="Finalized",$K262&lt;&gt;""),"",IF($C262="","",$C262+120-TODAY()))</f>
         <v>-59</v>
       </c>
       <c r="O262" s="9">
+        <f>IF(AND(TRIM($A262)="Finalized",$K262&lt;&gt;""),"",DATE(2027,3,30))</f>
         <v>46476</v>
       </c>
       <c r="P262" s="8" t="s">
@@ -43835,14 +44096,15 @@
         <v>173</v>
       </c>
       <c r="M263" s="11">
-        <f ca="1">IF($C263="","",$C263+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A263)="Finalized",$K263&lt;&gt;""),"",IF($C263="","",$C263+365-TODAY()))</f>
         <v>187</v>
       </c>
       <c r="N263" s="11">
-        <f ca="1">IF($C263="","",$C263+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A263)="Finalized",$K263&lt;&gt;""),"",IF($C263="","",$C263+120-TODAY()))</f>
         <v>-58</v>
       </c>
       <c r="O263" s="9">
+        <f>IF(AND(TRIM($A263)="Finalized",$K263&lt;&gt;""),"",DATE(2027,3,31))</f>
         <v>46477</v>
       </c>
       <c r="P263" s="8" t="s">
@@ -43957,14 +44219,15 @@
         <v>174</v>
       </c>
       <c r="M264" s="11">
-        <f ca="1">IF($C264="","",$C264+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A264)="Finalized",$K264&lt;&gt;""),"",IF($C264="","",$C264+365-TODAY()))</f>
         <v>218</v>
       </c>
       <c r="N264" s="11">
-        <f ca="1">IF($C264="","",$C264+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A264)="Finalized",$K264&lt;&gt;""),"",IF($C264="","",$C264+120-TODAY()))</f>
         <v>-27</v>
       </c>
       <c r="O264" s="9">
+        <f>IF(AND(TRIM($A264)="Finalized",$K264&lt;&gt;""),"",DATE(2027,4,1))</f>
         <v>46478</v>
       </c>
       <c r="P264" s="8" t="s">
@@ -44075,14 +44338,15 @@
         <v>175</v>
       </c>
       <c r="M265" s="11">
-        <f ca="1">IF($C265="","",$C265+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A265)="Finalized",$K265&lt;&gt;""),"",IF($C265="","",$C265+365-TODAY()))</f>
         <v>188</v>
       </c>
       <c r="N265" s="11">
-        <f ca="1">IF($C265="","",$C265+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A265)="Finalized",$K265&lt;&gt;""),"",IF($C265="","",$C265+120-TODAY()))</f>
         <v>-57</v>
       </c>
       <c r="O265" s="9">
+        <f>IF(AND(TRIM($A265)="Finalized",$K265&lt;&gt;""),"",DATE(2027,4,2))</f>
         <v>46479</v>
       </c>
       <c r="P265" s="8" t="s">
@@ -44199,14 +44463,15 @@
         <v>179</v>
       </c>
       <c r="M266" s="11">
-        <f ca="1">IF($C266="","",$C266+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A266)="Finalized",$K266&lt;&gt;""),"",IF($C266="","",$C266+365-TODAY()))</f>
         <v>196</v>
       </c>
       <c r="N266" s="11">
-        <f ca="1">IF($C266="","",$C266+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A266)="Finalized",$K266&lt;&gt;""),"",IF($C266="","",$C266+120-TODAY()))</f>
         <v>-49</v>
       </c>
       <c r="O266" s="9">
+        <f>IF(AND(TRIM($A266)="Finalized",$K266&lt;&gt;""),"",DATE(2027,4,6))</f>
         <v>46483</v>
       </c>
       <c r="P266" s="8" t="s">
@@ -44319,14 +44584,15 @@
         <v>179</v>
       </c>
       <c r="M267" s="11">
-        <f ca="1">IF($C267="","",$C267+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A267)="Finalized",$K267&lt;&gt;""),"",IF($C267="","",$C267+365-TODAY()))</f>
         <v>201</v>
       </c>
       <c r="N267" s="11">
-        <f ca="1">IF($C267="","",$C267+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A267)="Finalized",$K267&lt;&gt;""),"",IF($C267="","",$C267+120-TODAY()))</f>
         <v>-44</v>
       </c>
       <c r="O267" s="9">
+        <f>IF(AND(TRIM($A267)="Finalized",$K267&lt;&gt;""),"",DATE(2027,4,6))</f>
         <v>46483</v>
       </c>
       <c r="P267" s="8" t="s">
@@ -44439,14 +44705,15 @@
         <v>181</v>
       </c>
       <c r="M268" s="11">
-        <f ca="1">IF($C268="","",$C268+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A268)="Finalized",$K268&lt;&gt;""),"",IF($C268="","",$C268+365-TODAY()))</f>
         <v>218</v>
       </c>
       <c r="N268" s="11">
-        <f ca="1">IF($C268="","",$C268+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A268)="Finalized",$K268&lt;&gt;""),"",IF($C268="","",$C268+120-TODAY()))</f>
         <v>-27</v>
       </c>
       <c r="O268" s="9">
+        <f>IF(AND(TRIM($A268)="Finalized",$K268&lt;&gt;""),"",DATE(2027,4,8))</f>
         <v>46485</v>
       </c>
       <c r="P268" s="8" t="s">
@@ -44559,14 +44826,15 @@
         <v>186</v>
       </c>
       <c r="M269" s="11">
-        <f ca="1">IF($C269="","",$C269+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A269)="Finalized",$K269&lt;&gt;""),"",IF($C269="","",$C269+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N269" s="11">
-        <f ca="1">IF($C269="","",$C269+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A269)="Finalized",$K269&lt;&gt;""),"",IF($C269="","",$C269+120-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="O269" s="9">
+        <f>IF(AND(TRIM($A269)="Finalized",$K269&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P269" s="8" t="s">
@@ -44681,14 +44949,15 @@
         <v>186</v>
       </c>
       <c r="M270" s="11">
-        <f ca="1">IF($C270="","",$C270+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A270)="Finalized",$K270&lt;&gt;""),"",IF($C270="","",$C270+180-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="N270" s="11">
-        <f ca="1">IF($C270="","",$C270+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A270)="Finalized",$K270&lt;&gt;""),"",IF($C270="","",$C270+365-TODAY()))</f>
         <v>251</v>
       </c>
       <c r="O270" s="9">
+        <f>IF(AND(TRIM($A270)="Finalized",$K270&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P270" s="8" t="s">
@@ -44809,14 +45078,15 @@
         <v>186</v>
       </c>
       <c r="M271" s="11">
-        <f ca="1">IF($C271="","",$C271+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A271)="Finalized",$K271&lt;&gt;""),"",IF($C271="","",$C271+365-TODAY()))</f>
         <v>308</v>
       </c>
       <c r="N271" s="11">
-        <f ca="1">IF($C271="","",$C271+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A271)="Finalized",$K271&lt;&gt;""),"",IF($C271="","",$C271+120-TODAY()))</f>
         <v>63</v>
       </c>
       <c r="O271" s="9">
+        <f>IF(AND(TRIM($A271)="Finalized",$K271&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P271" s="8" t="s">
@@ -44929,14 +45199,15 @@
         <v>189</v>
       </c>
       <c r="M272" s="11">
-        <f ca="1">IF($C272="","",$C272+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A272)="Finalized",$K272&lt;&gt;""),"",IF($C272="","",$C272+365-TODAY()))</f>
         <v>197</v>
       </c>
       <c r="N272" s="11">
-        <f ca="1">IF($C272="","",$C272+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A272)="Finalized",$K272&lt;&gt;""),"",IF($C272="","",$C272+120-TODAY()))</f>
         <v>-48</v>
       </c>
       <c r="O272" s="9">
+        <f>IF(AND(TRIM($A272)="Finalized",$K272&lt;&gt;""),"",DATE(2027,4,16))</f>
         <v>46493</v>
       </c>
       <c r="P272" s="8" t="s">
@@ -45047,14 +45318,15 @@
         <v>193</v>
       </c>
       <c r="M273" s="11">
-        <f ca="1">IF($C273="","",$C273+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A273)="Finalized",$K273&lt;&gt;""),"",IF($C273="","",$C273+365-TODAY()))</f>
         <v>197</v>
       </c>
       <c r="N273" s="11">
-        <f ca="1">IF($C273="","",$C273+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A273)="Finalized",$K273&lt;&gt;""),"",IF($C273="","",$C273+120-TODAY()))</f>
         <v>-48</v>
       </c>
       <c r="O273" s="9">
+        <f>IF(AND(TRIM($A273)="Finalized",$K273&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P273" s="8" t="s">
@@ -45167,14 +45439,15 @@
         <v>193</v>
       </c>
       <c r="M274" s="11">
-        <f ca="1">IF($C274="","",$C274+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A274)="Finalized",$K274&lt;&gt;""),"",IF($C274="","",$C274+365-TODAY()))</f>
         <v>342</v>
       </c>
       <c r="N274" s="11">
-        <f ca="1">IF($C274="","",$C274+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A274)="Finalized",$K274&lt;&gt;""),"",IF($C274="","",$C274+120-TODAY()))</f>
         <v>97</v>
       </c>
       <c r="O274" s="9">
+        <f>IF(AND(TRIM($A274)="Finalized",$K274&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P274" s="8" t="s">
@@ -45287,14 +45560,15 @@
         <v>193</v>
       </c>
       <c r="M275" s="11">
-        <f ca="1">IF($C275="","",$C275+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A275)="Finalized",$K275&lt;&gt;""),"",IF($C275="","",$C275+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="N275" s="11">
-        <f ca="1">IF($C275="","",$C275+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A275)="Finalized",$K275&lt;&gt;""),"",IF($C275="","",$C275+120-TODAY()))</f>
         <v>15</v>
       </c>
       <c r="O275" s="9">
+        <f>IF(AND(TRIM($A275)="Finalized",$K275&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P275" s="8" t="s">
@@ -45407,14 +45681,15 @@
         <v>194</v>
       </c>
       <c r="M276" s="11">
-        <f ca="1">IF($C276="","",$C276+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A276)="Finalized",$K276&lt;&gt;""),"",IF($C276="","",$C276+365-TODAY()))</f>
         <v>231</v>
       </c>
       <c r="N276" s="11">
-        <f ca="1">IF($C276="","",$C276+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A276)="Finalized",$K276&lt;&gt;""),"",IF($C276="","",$C276+120-TODAY()))</f>
         <v>-14</v>
       </c>
       <c r="O276" s="9">
+        <f>IF(AND(TRIM($A276)="Finalized",$K276&lt;&gt;""),"",DATE(2027,4,21))</f>
         <v>46498</v>
       </c>
       <c r="P276" s="8" t="s">
@@ -45531,14 +45806,15 @@
         <v>194</v>
       </c>
       <c r="M277" s="11" t="str">
-        <f ca="1">IF($C277="","",$C277+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A277)="Finalized",$K277&lt;&gt;""),"",IF($C277="","",$C277+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N277" s="11" t="str">
-        <f ca="1">IF($C277="","",$C277+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A277)="Finalized",$K277&lt;&gt;""),"",IF($C277="","",$C277+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O277" s="9">
+        <f>IF(AND(TRIM($A277)="Finalized",$K277&lt;&gt;""),"",DATE(2027,4,21))</f>
         <v>46498</v>
       </c>
       <c r="P277" s="8" t="s">
@@ -45651,14 +45927,15 @@
         <v>195</v>
       </c>
       <c r="M278" s="11">
-        <f ca="1">IF($C278="","",$C278+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A278)="Finalized",$K278&lt;&gt;""),"",IF($C278="","",$C278+365-TODAY()))</f>
         <v>216</v>
       </c>
       <c r="N278" s="11">
-        <f ca="1">IF($C278="","",$C278+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A278)="Finalized",$K278&lt;&gt;""),"",IF($C278="","",$C278+120-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="O278" s="9">
+        <f>IF(AND(TRIM($A278)="Finalized",$K278&lt;&gt;""),"",DATE(2027,4,22))</f>
         <v>46499</v>
       </c>
       <c r="P278" s="8" t="s">
@@ -45775,14 +46052,15 @@
         <v>196</v>
       </c>
       <c r="M279" s="11">
-        <f ca="1">IF($C279="","",$C279+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A279)="Finalized",$K279&lt;&gt;""),"",IF($C279="","",$C279+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N279" s="11">
-        <f ca="1">IF($C279="","",$C279+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A279)="Finalized",$K279&lt;&gt;""),"",IF($C279="","",$C279+120-TODAY()))</f>
         <v>-37</v>
       </c>
       <c r="O279" s="9">
+        <f>IF(AND(TRIM($A279)="Finalized",$K279&lt;&gt;""),"",DATE(2027,4,23))</f>
         <v>46500</v>
       </c>
       <c r="P279" s="8" t="s">
@@ -45897,14 +46175,15 @@
         <v>200</v>
       </c>
       <c r="M280" s="11">
-        <f ca="1">IF($C280="","",$C280+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A280)="Finalized",$K280&lt;&gt;""),"",IF($C280="","",$C280+365-TODAY()))</f>
         <v>203</v>
       </c>
       <c r="N280" s="11">
-        <f ca="1">IF($C280="","",$C280+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A280)="Finalized",$K280&lt;&gt;""),"",IF($C280="","",$C280+120-TODAY()))</f>
         <v>-42</v>
       </c>
       <c r="O280" s="9">
+        <f>IF(AND(TRIM($A280)="Finalized",$K280&lt;&gt;""),"",DATE(2027,4,27))</f>
         <v>46504</v>
       </c>
       <c r="P280" s="8" t="s">
@@ -46017,14 +46296,15 @@
         <v>201</v>
       </c>
       <c r="M281" s="11">
-        <f ca="1">IF($C281="","",$C281+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A281)="Finalized",$K281&lt;&gt;""),"",IF($C281="","",$C281+365-TODAY()))</f>
         <v>215</v>
       </c>
       <c r="N281" s="11">
-        <f ca="1">IF($C281="","",$C281+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A281)="Finalized",$K281&lt;&gt;""),"",IF($C281="","",$C281+120-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="O281" s="9">
+        <f>IF(AND(TRIM($A281)="Finalized",$K281&lt;&gt;""),"",DATE(2027,4,28))</f>
         <v>46505</v>
       </c>
       <c r="P281" s="8" t="s">
@@ -46135,14 +46415,15 @@
         <v>202</v>
       </c>
       <c r="M282" s="11">
-        <f ca="1">IF($C282="","",$C282+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A282)="Finalized",$K282&lt;&gt;""),"",IF($C282="","",$C282+365-TODAY()))</f>
         <v>215</v>
       </c>
       <c r="N282" s="11">
-        <f ca="1">IF($C282="","",$C282+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A282)="Finalized",$K282&lt;&gt;""),"",IF($C282="","",$C282+120-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="O282" s="9">
+        <f>IF(AND(TRIM($A282)="Finalized",$K282&lt;&gt;""),"",DATE(2027,4,29))</f>
         <v>46506</v>
       </c>
       <c r="P282" s="8" t="s">
@@ -46253,14 +46534,15 @@
         <v>202</v>
       </c>
       <c r="M283" s="11">
-        <f ca="1">IF($C283="","",$C283+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A283)="Finalized",$K283&lt;&gt;""),"",IF($C283="","",$C283+365-TODAY()))</f>
         <v>215</v>
       </c>
       <c r="N283" s="11">
-        <f ca="1">IF($C283="","",$C283+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A283)="Finalized",$K283&lt;&gt;""),"",IF($C283="","",$C283+120-TODAY()))</f>
         <v>-30</v>
       </c>
       <c r="O283" s="9">
+        <f>IF(AND(TRIM($A283)="Finalized",$K283&lt;&gt;""),"",DATE(2027,4,29))</f>
         <v>46506</v>
       </c>
       <c r="P283" s="8" t="s">
@@ -46371,14 +46653,15 @@
         <v>203</v>
       </c>
       <c r="M284" s="11">
-        <f ca="1">IF($C284="","",$C284+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A284)="Finalized",$K284&lt;&gt;""),"",IF($C284="","",$C284+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N284" s="11">
-        <f ca="1">IF($C284="","",$C284+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A284)="Finalized",$K284&lt;&gt;""),"",IF($C284="","",$C284+120-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="O284" s="9">
+        <f>IF(AND(TRIM($A284)="Finalized",$K284&lt;&gt;""),"",DATE(2027,4,30))</f>
         <v>46507</v>
       </c>
       <c r="P284" s="8" t="s">
@@ -46495,14 +46778,15 @@
         <v>204</v>
       </c>
       <c r="M285" s="11">
-        <f ca="1">IF($C285="","",$C285+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A285)="Finalized",$K285&lt;&gt;""),"",IF($C285="","",$C285+365-TODAY()))</f>
         <v>218</v>
       </c>
       <c r="N285" s="11">
-        <f ca="1">IF($C285="","",$C285+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A285)="Finalized",$K285&lt;&gt;""),"",IF($C285="","",$C285+120-TODAY()))</f>
         <v>-27</v>
       </c>
       <c r="O285" s="9">
+        <f>IF(AND(TRIM($A285)="Finalized",$K285&lt;&gt;""),"",DATE(2027,5,1))</f>
         <v>46508</v>
       </c>
       <c r="P285" s="8" t="s">
@@ -46615,14 +46899,15 @@
         <v>207</v>
       </c>
       <c r="M286" s="11">
-        <f ca="1">IF($C286="","",$C286+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A286)="Finalized",$K286&lt;&gt;""),"",IF($C286="","",$C286+365-TODAY()))</f>
         <v>251</v>
       </c>
       <c r="N286" s="11">
-        <f ca="1">IF($C286="","",$C286+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A286)="Finalized",$K286&lt;&gt;""),"",IF($C286="","",$C286+120-TODAY()))</f>
         <v>6</v>
       </c>
       <c r="O286" s="9">
+        <f>IF(AND(TRIM($A286)="Finalized",$K286&lt;&gt;""),"",DATE(2027,5,4))</f>
         <v>46511</v>
       </c>
       <c r="P286" s="8" t="s">
@@ -46733,14 +47018,15 @@
         <v>207</v>
       </c>
       <c r="M287" s="11">
-        <f ca="1">IF($C287="","",$C287+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A287)="Finalized",$K287&lt;&gt;""),"",IF($C287="","",$C287+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="N287" s="11">
-        <f ca="1">IF($C287="","",$C287+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A287)="Finalized",$K287&lt;&gt;""),"",IF($C287="","",$C287+120-TODAY()))</f>
         <v>-23</v>
       </c>
       <c r="O287" s="9">
+        <f>IF(AND(TRIM($A287)="Finalized",$K287&lt;&gt;""),"",DATE(2027,5,4))</f>
         <v>46511</v>
       </c>
       <c r="P287" s="8" t="s">
@@ -46857,14 +47143,15 @@
         <v>208</v>
       </c>
       <c r="M288" s="11">
-        <f ca="1">IF($C288="","",$C288+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A288)="Finalized",$K288&lt;&gt;""),"",IF($C288="","",$C288+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N288" s="11">
-        <f ca="1">IF($C288="","",$C288+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A288)="Finalized",$K288&lt;&gt;""),"",IF($C288="","",$C288+120-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O288" s="9">
+        <f>IF(AND(TRIM($A288)="Finalized",$K288&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P288" s="8" t="s">
@@ -46977,14 +47264,15 @@
         <v>208</v>
       </c>
       <c r="M289" s="11">
-        <f ca="1">IF($C289="","",$C289+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A289)="Finalized",$K289&lt;&gt;""),"",IF($C289="","",$C289+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="N289" s="11">
-        <f ca="1">IF($C289="","",$C289+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A289)="Finalized",$K289&lt;&gt;""),"",IF($C289="","",$C289+120-TODAY()))</f>
         <v>-28</v>
       </c>
       <c r="O289" s="9">
+        <f>IF(AND(TRIM($A289)="Finalized",$K289&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P289" s="8" t="s">
@@ -47097,14 +47385,15 @@
         <v>208</v>
       </c>
       <c r="M290" s="11">
-        <f ca="1">IF($C290="","",$C290+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A290)="Finalized",$K290&lt;&gt;""),"",IF($C290="","",$C290+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="N290" s="11">
-        <f ca="1">IF($C290="","",$C290+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A290)="Finalized",$K290&lt;&gt;""),"",IF($C290="","",$C290+120-TODAY()))</f>
         <v>-13</v>
       </c>
       <c r="O290" s="9">
+        <f>IF(AND(TRIM($A290)="Finalized",$K290&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P290" s="8" t="s">
@@ -47219,14 +47508,15 @@
         <v>208</v>
       </c>
       <c r="M291" s="11">
-        <f ca="1">IF($C291="","",$C291+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A291)="Finalized",$K291&lt;&gt;""),"",IF($C291="","",$C291+365-TODAY()))</f>
         <v>310</v>
       </c>
       <c r="N291" s="11">
-        <f ca="1">IF($C291="","",$C291+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A291)="Finalized",$K291&lt;&gt;""),"",IF($C291="","",$C291+120-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="O291" s="9">
+        <f>IF(AND(TRIM($A291)="Finalized",$K291&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P291" s="8" t="s">
@@ -47341,14 +47631,15 @@
         <v>211</v>
       </c>
       <c r="M292" s="11">
-        <f ca="1">IF($C292="","",$C292+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A292)="Finalized",$K292&lt;&gt;""),"",IF($C292="","",$C292+365-TODAY()))</f>
         <v>251</v>
       </c>
       <c r="N292" s="11">
-        <f ca="1">IF($C292="","",$C292+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A292)="Finalized",$K292&lt;&gt;""),"",IF($C292="","",$C292+120-TODAY()))</f>
         <v>6</v>
       </c>
       <c r="O292" s="9">
+        <f>IF(AND(TRIM($A292)="Finalized",$K292&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P292" s="8" t="s">
@@ -47459,14 +47750,15 @@
         <v>211</v>
       </c>
       <c r="M293" s="11">
-        <f ca="1">IF($C293="","",$C293+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A293)="Finalized",$K293&lt;&gt;""),"",IF($C293="","",$C293+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="N293" s="11">
-        <f ca="1">IF($C293="","",$C293+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A293)="Finalized",$K293&lt;&gt;""),"",IF($C293="","",$C293+120-TODAY()))</f>
         <v>1</v>
       </c>
       <c r="O293" s="9">
+        <f>IF(AND(TRIM($A293)="Finalized",$K293&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P293" s="8" t="s">
@@ -47583,14 +47875,15 @@
         <v>211</v>
       </c>
       <c r="M294" s="11">
-        <f ca="1">IF($C294="","",$C294+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A294)="Finalized",$K294&lt;&gt;""),"",IF($C294="","",$C294+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N294" s="11">
-        <f ca="1">IF($C294="","",$C294+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A294)="Finalized",$K294&lt;&gt;""),"",IF($C294="","",$C294+120-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="O294" s="9">
+        <f>IF(AND(TRIM($A294)="Finalized",$K294&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P294" s="8" t="s">
@@ -47707,14 +48000,15 @@
         <v>214</v>
       </c>
       <c r="M295" s="11">
-        <f ca="1">IF($C295="","",$C295+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A295)="Finalized",$K295&lt;&gt;""),"",IF($C295="","",$C295+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="N295" s="11">
-        <f ca="1">IF($C295="","",$C295+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A295)="Finalized",$K295&lt;&gt;""),"",IF($C295="","",$C295+120-TODAY()))</f>
         <v>1</v>
       </c>
       <c r="O295" s="9">
+        <f>IF(AND(TRIM($A295)="Finalized",$K295&lt;&gt;""),"",DATE(2027,5,11))</f>
         <v>46518</v>
       </c>
       <c r="P295" s="8" t="s">
@@ -47835,14 +48129,15 @@
         <v>214</v>
       </c>
       <c r="M296" s="11">
-        <f ca="1">IF($C296="","",$C296+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A296)="Finalized",$K296&lt;&gt;""),"",IF($C296="","",$C296+365-TODAY()))</f>
         <v>306</v>
       </c>
       <c r="N296" s="11">
-        <f ca="1">IF($C296="","",$C296+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A296)="Finalized",$K296&lt;&gt;""),"",IF($C296="","",$C296+120-TODAY()))</f>
         <v>61</v>
       </c>
       <c r="O296" s="9">
+        <f>IF(AND(TRIM($A296)="Finalized",$K296&lt;&gt;""),"",DATE(2027,5,11))</f>
         <v>46518</v>
       </c>
       <c r="P296" s="8" t="s">
@@ -47953,14 +48248,15 @@
         <v>215</v>
       </c>
       <c r="M297" s="11">
-        <f ca="1">IF($C297="","",$C297+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A297)="Finalized",$K297&lt;&gt;""),"",IF($C297="","",$C297+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="N297" s="11">
-        <f ca="1">IF($C297="","",$C297+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A297)="Finalized",$K297&lt;&gt;""),"",IF($C297="","",$C297+120-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="O297" s="9">
+        <f>IF(AND(TRIM($A297)="Finalized",$K297&lt;&gt;""),"",DATE(2027,5,12))</f>
         <v>46519</v>
       </c>
       <c r="P297" s="8" t="s">
@@ -48071,14 +48367,15 @@
         <v>216</v>
       </c>
       <c r="M298" s="11">
-        <f ca="1">IF($C298="","",$C298+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A298)="Finalized",$K298&lt;&gt;""),"",IF($C298="","",$C298+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N298" s="11">
-        <f ca="1">IF($C298="","",$C298+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A298)="Finalized",$K298&lt;&gt;""),"",IF($C298="","",$C298+120-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O298" s="9">
+        <f>IF(AND(TRIM($A298)="Finalized",$K298&lt;&gt;""),"",DATE(2027,5,13))</f>
         <v>46520</v>
       </c>
       <c r="P298" s="8" t="s">
@@ -48191,14 +48488,15 @@
         <v>216</v>
       </c>
       <c r="M299" s="11">
-        <f ca="1">IF($C299="","",$C299+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A299)="Finalized",$K299&lt;&gt;""),"",IF($C299="","",$C299+365-TODAY()))</f>
         <v>229</v>
       </c>
       <c r="N299" s="11">
-        <f ca="1">IF($C299="","",$C299+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A299)="Finalized",$K299&lt;&gt;""),"",IF($C299="","",$C299+120-TODAY()))</f>
         <v>-16</v>
       </c>
       <c r="O299" s="9">
+        <f>IF(AND(TRIM($A299)="Finalized",$K299&lt;&gt;""),"",DATE(2027,5,13))</f>
         <v>46520</v>
       </c>
       <c r="P299" s="8" t="s">
@@ -48311,14 +48609,15 @@
         <v>217</v>
       </c>
       <c r="M300" s="11">
-        <f ca="1">IF($C300="","",$C300+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A300)="Finalized",$K300&lt;&gt;""),"",IF($C300="","",$C300+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N300" s="11">
-        <f ca="1">IF($C300="","",$C300+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A300)="Finalized",$K300&lt;&gt;""),"",IF($C300="","",$C300+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O300" s="9">
+        <f>IF(AND(TRIM($A300)="Finalized",$K300&lt;&gt;""),"",DATE(2027,5,14))</f>
         <v>46521</v>
       </c>
       <c r="P300" s="8" t="s">
@@ -48435,14 +48734,15 @@
         <v>218</v>
       </c>
       <c r="M301" s="11">
-        <f ca="1">IF($C301="","",$C301+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A301)="Finalized",$K301&lt;&gt;""),"",IF($C301="","",$C301+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N301" s="11">
-        <f ca="1">IF($C301="","",$C301+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A301)="Finalized",$K301&lt;&gt;""),"",IF($C301="","",$C301+120-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O301" s="9">
+        <f>IF(AND(TRIM($A301)="Finalized",$K301&lt;&gt;""),"",DATE(2027,5,15))</f>
         <v>46522</v>
       </c>
       <c r="P301" s="8" t="s">
@@ -48555,14 +48855,15 @@
         <v>218</v>
       </c>
       <c r="M302" s="11">
-        <f ca="1">IF($C302="","",$C302+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A302)="Finalized",$K302&lt;&gt;""),"",IF($C302="","",$C302+365-TODAY()))</f>
         <v>229</v>
       </c>
       <c r="N302" s="11">
-        <f ca="1">IF($C302="","",$C302+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A302)="Finalized",$K302&lt;&gt;""),"",IF($C302="","",$C302+120-TODAY()))</f>
         <v>-16</v>
       </c>
       <c r="O302" s="9">
+        <f>IF(AND(TRIM($A302)="Finalized",$K302&lt;&gt;""),"",DATE(2027,5,15))</f>
         <v>46522</v>
       </c>
       <c r="P302" s="8" t="s">
@@ -48677,14 +48978,15 @@
         <v>221</v>
       </c>
       <c r="M303" s="11">
-        <f ca="1">IF($C303="","",$C303+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A303)="Finalized",$K303&lt;&gt;""),"",IF($C303="","",$C303+365-TODAY()))</f>
         <v>313</v>
       </c>
       <c r="N303" s="11">
-        <f ca="1">IF($C303="","",$C303+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A303)="Finalized",$K303&lt;&gt;""),"",IF($C303="","",$C303+120-TODAY()))</f>
         <v>68</v>
       </c>
       <c r="O303" s="9">
+        <f>IF(AND(TRIM($A303)="Finalized",$K303&lt;&gt;""),"",DATE(2027,5,18))</f>
         <v>46525</v>
       </c>
       <c r="P303" s="8" t="s">
@@ -48807,14 +49109,15 @@
         <v>222</v>
       </c>
       <c r="M304" s="11">
-        <f ca="1">IF($C304="","",$C304+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A304)="Finalized",$K304&lt;&gt;""),"",IF($C304="","",$C304+365-TODAY()))</f>
         <v>239</v>
       </c>
       <c r="N304" s="11">
-        <f ca="1">IF($C304="","",$C304+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A304)="Finalized",$K304&lt;&gt;""),"",IF($C304="","",$C304+120-TODAY()))</f>
         <v>-6</v>
       </c>
       <c r="O304" s="9">
+        <f>IF(AND(TRIM($A304)="Finalized",$K304&lt;&gt;""),"",DATE(2027,5,19))</f>
         <v>46526</v>
       </c>
       <c r="P304" s="8" t="s">
@@ -48929,14 +49232,15 @@
         <v>223</v>
       </c>
       <c r="M305" s="11">
-        <f ca="1">IF($C305="","",$C305+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A305)="Finalized",$K305&lt;&gt;""),"",IF($C305="","",$C305+365-TODAY()))</f>
         <v>239</v>
       </c>
       <c r="N305" s="11">
-        <f ca="1">IF($C305="","",$C305+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A305)="Finalized",$K305&lt;&gt;""),"",IF($C305="","",$C305+120-TODAY()))</f>
         <v>-6</v>
       </c>
       <c r="O305" s="9">
+        <f>IF(AND(TRIM($A305)="Finalized",$K305&lt;&gt;""),"",DATE(2027,5,20))</f>
         <v>46527</v>
       </c>
       <c r="P305" s="8" t="s">
@@ -49047,14 +49351,15 @@
         <v>229</v>
       </c>
       <c r="M306" s="11">
-        <f ca="1">IF($C306="","",$C306+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A306)="Finalized",$K306&lt;&gt;""),"",IF($C306="","",$C306+365-TODAY()))</f>
         <v>270</v>
       </c>
       <c r="N306" s="11">
-        <f ca="1">IF($C306="","",$C306+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A306)="Finalized",$K306&lt;&gt;""),"",IF($C306="","",$C306+120-TODAY()))</f>
         <v>25</v>
       </c>
       <c r="O306" s="9">
+        <f>IF(AND(TRIM($A306)="Finalized",$K306&lt;&gt;""),"",DATE(2027,5,26))</f>
         <v>46533</v>
       </c>
       <c r="P306" s="8" t="s">
@@ -49169,14 +49474,15 @@
         <v>229</v>
       </c>
       <c r="M307" s="11">
-        <f ca="1">IF($C307="","",$C307+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A307)="Finalized",$K307&lt;&gt;""),"",IF($C307="","",$C307+365-TODAY()))</f>
         <v>310</v>
       </c>
       <c r="N307" s="11">
-        <f ca="1">IF($C307="","",$C307+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A307)="Finalized",$K307&lt;&gt;""),"",IF($C307="","",$C307+120-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="O307" s="9">
+        <f>IF(AND(TRIM($A307)="Finalized",$K307&lt;&gt;""),"",DATE(2027,5,26))</f>
         <v>46533</v>
       </c>
       <c r="P307" s="8" t="s">
@@ -49289,14 +49595,15 @@
         <v>231</v>
       </c>
       <c r="M308" s="11">
-        <f ca="1">IF($C308="","",$C308+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A308)="Finalized",$K308&lt;&gt;""),"",IF($C308="","",$C308+365-TODAY()))</f>
         <v>257</v>
       </c>
       <c r="N308" s="11">
-        <f ca="1">IF($C308="","",$C308+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A308)="Finalized",$K308&lt;&gt;""),"",IF($C308="","",$C308+120-TODAY()))</f>
         <v>12</v>
       </c>
       <c r="O308" s="9">
+        <f>IF(AND(TRIM($A308)="Finalized",$K308&lt;&gt;""),"",DATE(2027,5,28))</f>
         <v>46535</v>
       </c>
       <c r="P308" s="8" t="s">
@@ -49409,14 +49716,15 @@
         <v>231</v>
       </c>
       <c r="M309" s="11">
-        <f ca="1">IF($C309="","",$C309+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A309)="Finalized",$K309&lt;&gt;""),"",IF($C309="","",$C309+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="N309" s="11">
-        <f ca="1">IF($C309="","",$C309+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A309)="Finalized",$K309&lt;&gt;""),"",IF($C309="","",$C309+120-TODAY()))</f>
         <v>20</v>
       </c>
       <c r="O309" s="9">
+        <f>IF(AND(TRIM($A309)="Finalized",$K309&lt;&gt;""),"",DATE(2027,5,28))</f>
         <v>46535</v>
       </c>
       <c r="P309" s="8" t="s">
@@ -49535,14 +49843,15 @@
         <v>232</v>
       </c>
       <c r="M310" s="11">
-        <f ca="1">IF($C310="","",$C310+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A310)="Finalized",$K310&lt;&gt;""),"",IF($C310="","",$C310+365-TODAY()))</f>
         <v>250</v>
       </c>
       <c r="N310" s="11">
-        <f ca="1">IF($C310="","",$C310+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A310)="Finalized",$K310&lt;&gt;""),"",IF($C310="","",$C310+120-TODAY()))</f>
         <v>5</v>
       </c>
       <c r="O310" s="9">
+        <f>IF(AND(TRIM($A310)="Finalized",$K310&lt;&gt;""),"",DATE(2027,5,29))</f>
         <v>46536</v>
       </c>
       <c r="P310" s="8" t="s">
@@ -49657,14 +49966,15 @@
         <v>235</v>
       </c>
       <c r="M311" s="11">
-        <f ca="1">IF($C311="","",$C311+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A311)="Finalized",$K311&lt;&gt;""),"",IF($C311="","",$C311+180-TODAY()))</f>
         <v>101</v>
       </c>
       <c r="N311" s="11">
-        <f ca="1">IF($C311="","",$C311+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A311)="Finalized",$K311&lt;&gt;""),"",IF($C311="","",$C311+365-TODAY()))</f>
         <v>286</v>
       </c>
       <c r="O311" s="9">
+        <f>IF(AND(TRIM($A311)="Finalized",$K311&lt;&gt;""),"",DATE(2027,6,1))</f>
         <v>46539</v>
       </c>
       <c r="P311" s="8" t="s">
@@ -49785,14 +50095,15 @@
         <v>236</v>
       </c>
       <c r="M312" s="11">
-        <f ca="1">IF($C312="","",$C312+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A312)="Finalized",$K312&lt;&gt;""),"",IF($C312="","",$C312+365-TODAY()))</f>
         <v>286</v>
       </c>
       <c r="N312" s="11">
-        <f ca="1">IF($C312="","",$C312+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A312)="Finalized",$K312&lt;&gt;""),"",IF($C312="","",$C312+120-TODAY()))</f>
         <v>41</v>
       </c>
       <c r="O312" s="9">
+        <f>IF(AND(TRIM($A312)="Finalized",$K312&lt;&gt;""),"",DATE(2027,6,2))</f>
         <v>46540</v>
       </c>
       <c r="P312" s="8" t="s">
@@ -49903,14 +50214,15 @@
         <v>236</v>
       </c>
       <c r="M313" s="11">
-        <f ca="1">IF($C313="","",$C313+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A313)="Finalized",$K313&lt;&gt;""),"",IF($C313="","",$C313+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N313" s="11">
-        <f ca="1">IF($C313="","",$C313+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A313)="Finalized",$K313&lt;&gt;""),"",IF($C313="","",$C313+120-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="O313" s="9">
+        <f>IF(AND(TRIM($A313)="Finalized",$K313&lt;&gt;""),"",DATE(2027,6,2))</f>
         <v>46540</v>
       </c>
       <c r="P313" s="8" t="s">
@@ -50023,14 +50335,15 @@
         <v>238</v>
       </c>
       <c r="M314" s="11">
-        <f ca="1">IF($C314="","",$C314+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A314)="Finalized",$K314&lt;&gt;""),"",IF($C314="","",$C314+365-TODAY()))</f>
         <v>249</v>
       </c>
       <c r="N314" s="11">
-        <f ca="1">IF($C314="","",$C314+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A314)="Finalized",$K314&lt;&gt;""),"",IF($C314="","",$C314+120-TODAY()))</f>
         <v>4</v>
       </c>
       <c r="O314" s="9">
+        <f>IF(AND(TRIM($A314)="Finalized",$K314&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P314" s="8" t="s">
@@ -50143,14 +50456,15 @@
         <v>238</v>
       </c>
       <c r="M315" s="11">
-        <f ca="1">IF($C315="","",$C315+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A315)="Finalized",$K315&lt;&gt;""),"",IF($C315="","",$C315+365-TODAY()))</f>
         <v>249</v>
       </c>
       <c r="N315" s="11">
-        <f ca="1">IF($C315="","",$C315+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A315)="Finalized",$K315&lt;&gt;""),"",IF($C315="","",$C315+120-TODAY()))</f>
         <v>4</v>
       </c>
       <c r="O315" s="9">
+        <f>IF(AND(TRIM($A315)="Finalized",$K315&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P315" s="8" t="s">
@@ -50265,14 +50579,15 @@
         <v>238</v>
       </c>
       <c r="M316" s="11">
-        <f ca="1">IF($C316="","",$C316+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A316)="Finalized",$K316&lt;&gt;""),"",IF($C316="","",$C316+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="N316" s="11">
-        <f ca="1">IF($C316="","",$C316+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A316)="Finalized",$K316&lt;&gt;""),"",IF($C316="","",$C316+120-TODAY()))</f>
         <v>11</v>
       </c>
       <c r="O316" s="9">
+        <f>IF(AND(TRIM($A316)="Finalized",$K316&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P316" s="8" t="s">
@@ -50387,14 +50702,15 @@
         <v>239</v>
       </c>
       <c r="M317" s="11">
-        <f ca="1">IF($C317="","",$C317+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A317)="Finalized",$K317&lt;&gt;""),"",IF($C317="","",$C317+365-TODAY()))</f>
         <v>278</v>
       </c>
       <c r="N317" s="11">
-        <f ca="1">IF($C317="","",$C317+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A317)="Finalized",$K317&lt;&gt;""),"",IF($C317="","",$C317+120-TODAY()))</f>
         <v>33</v>
       </c>
       <c r="O317" s="9">
+        <f>IF(AND(TRIM($A317)="Finalized",$K317&lt;&gt;""),"",DATE(2027,6,5))</f>
         <v>46543</v>
       </c>
       <c r="P317" s="8" t="s">
@@ -50509,14 +50825,15 @@
         <v>239</v>
       </c>
       <c r="M318" s="11" t="str">
-        <f ca="1">IF($C318="","",$C318+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A318)="Finalized",$K318&lt;&gt;""),"",IF($C318="","",$C318+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N318" s="11" t="str">
-        <f ca="1">IF($C318="","",$C318+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A318)="Finalized",$K318&lt;&gt;""),"",IF($C318="","",$C318+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O318" s="9">
+        <f>IF(AND(TRIM($A318)="Finalized",$K318&lt;&gt;""),"",DATE(2027,6,5))</f>
         <v>46543</v>
       </c>
       <c r="P318" s="8" t="s">
@@ -50625,14 +50942,15 @@
         <v>242</v>
       </c>
       <c r="M319" s="11" t="str">
-        <f ca="1">IF($C319="","",$C319+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A319)="Finalized",$K319&lt;&gt;""),"",IF($C319="","",$C319+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N319" s="11" t="str">
-        <f ca="1">IF($C319="","",$C319+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A319)="Finalized",$K319&lt;&gt;""),"",IF($C319="","",$C319+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O319" s="9">
+        <f>IF(AND(TRIM($A319)="Finalized",$K319&lt;&gt;""),"",DATE(2027,6,8))</f>
         <v>46546</v>
       </c>
       <c r="P319" s="8" t="s">
@@ -50743,14 +51061,15 @@
         <v>243</v>
       </c>
       <c r="M320" s="11">
-        <f ca="1">IF($C320="","",$C320+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A320)="Finalized",$K320&lt;&gt;""),"",IF($C320="","",$C320+365-TODAY()))</f>
         <v>287</v>
       </c>
       <c r="N320" s="11">
-        <f ca="1">IF($C320="","",$C320+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A320)="Finalized",$K320&lt;&gt;""),"",IF($C320="","",$C320+120-TODAY()))</f>
         <v>42</v>
       </c>
       <c r="O320" s="9">
+        <f>IF(AND(TRIM($A320)="Finalized",$K320&lt;&gt;""),"",DATE(2027,6,9))</f>
         <v>46547</v>
       </c>
       <c r="P320" s="8" t="s">
@@ -50861,14 +51180,15 @@
         <v>243</v>
       </c>
       <c r="M321" s="11" t="str">
-        <f ca="1">IF($C321="","",$C321+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A321)="Finalized",$K321&lt;&gt;""),"",IF($C321="","",$C321+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N321" s="11" t="str">
-        <f ca="1">IF($C321="","",$C321+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A321)="Finalized",$K321&lt;&gt;""),"",IF($C321="","",$C321+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O321" s="9">
+        <f>IF(AND(TRIM($A321)="Finalized",$K321&lt;&gt;""),"",DATE(2027,6,9))</f>
         <v>46547</v>
       </c>
       <c r="P321" s="8" t="s">
@@ -50979,14 +51299,15 @@
         <v>244</v>
       </c>
       <c r="M322" s="11">
-        <f ca="1">IF($C322="","",$C322+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A322)="Finalized",$K322&lt;&gt;""),"",IF($C322="","",$C322+365-TODAY()))</f>
         <v>287</v>
       </c>
       <c r="N322" s="11">
-        <f ca="1">IF($C322="","",$C322+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A322)="Finalized",$K322&lt;&gt;""),"",IF($C322="","",$C322+120-TODAY()))</f>
         <v>42</v>
       </c>
       <c r="O322" s="9">
+        <f>IF(AND(TRIM($A322)="Finalized",$K322&lt;&gt;""),"",DATE(2027,6,10))</f>
         <v>46548</v>
       </c>
       <c r="P322" s="8" t="s">
@@ -51097,14 +51418,15 @@
         <v>249</v>
       </c>
       <c r="M323" s="11">
-        <f ca="1">IF($C323="","",$C323+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A323)="Finalized",$K323&lt;&gt;""),"",IF($C323="","",$C323+365-TODAY()))</f>
         <v>256</v>
       </c>
       <c r="N323" s="11">
-        <f ca="1">IF($C323="","",$C323+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A323)="Finalized",$K323&lt;&gt;""),"",IF($C323="","",$C323+120-TODAY()))</f>
         <v>11</v>
       </c>
       <c r="O323" s="9">
+        <f>IF(AND(TRIM($A323)="Finalized",$K323&lt;&gt;""),"",DATE(2027,6,15))</f>
         <v>46553</v>
       </c>
       <c r="P323" s="8" t="s">
@@ -51217,14 +51539,15 @@
         <v>250</v>
       </c>
       <c r="M324" s="11">
-        <f ca="1">IF($C324="","",$C324+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A324)="Finalized",$K324&lt;&gt;""),"",IF($C324="","",$C324+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N324" s="11">
-        <f ca="1">IF($C324="","",$C324+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A324)="Finalized",$K324&lt;&gt;""),"",IF($C324="","",$C324+120-TODAY()))</f>
         <v>18</v>
       </c>
       <c r="O324" s="9">
+        <f>IF(AND(TRIM($A324)="Finalized",$K324&lt;&gt;""),"",DATE(2027,6,16))</f>
         <v>46554</v>
       </c>
       <c r="P324" s="8" t="s">
@@ -51337,14 +51660,15 @@
         <v>252</v>
       </c>
       <c r="M325" s="11">
-        <f ca="1">IF($C325="","",$C325+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A325)="Finalized",$K325&lt;&gt;""),"",IF($C325="","",$C325+365-TODAY()))</f>
         <v>273</v>
       </c>
       <c r="N325" s="11">
-        <f ca="1">IF($C325="","",$C325+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A325)="Finalized",$K325&lt;&gt;""),"",IF($C325="","",$C325+120-TODAY()))</f>
         <v>28</v>
       </c>
       <c r="O325" s="9">
+        <f>IF(AND(TRIM($A325)="Finalized",$K325&lt;&gt;""),"",DATE(2027,6,18))</f>
         <v>46556</v>
       </c>
       <c r="P325" s="8" t="s">
@@ -51459,14 +51783,15 @@
         <v>252</v>
       </c>
       <c r="M326" s="11">
-        <f ca="1">IF($C326="","",$C326+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A326)="Finalized",$K326&lt;&gt;""),"",IF($C326="","",$C326+365-TODAY()))</f>
         <v>279</v>
       </c>
       <c r="N326" s="11">
-        <f ca="1">IF($C326="","",$C326+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A326)="Finalized",$K326&lt;&gt;""),"",IF($C326="","",$C326+120-TODAY()))</f>
         <v>34</v>
       </c>
       <c r="O326" s="9">
+        <f>IF(AND(TRIM($A326)="Finalized",$K326&lt;&gt;""),"",DATE(2027,6,18))</f>
         <v>46556</v>
       </c>
       <c r="P326" s="8" t="s">
@@ -51579,14 +51904,15 @@
         <v>253</v>
       </c>
       <c r="M327" s="11">
-        <f ca="1">IF($C327="","",$C327+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A327)="Finalized",$K327&lt;&gt;""),"",IF($C327="","",$C327+365-TODAY()))</f>
         <v>286</v>
       </c>
       <c r="N327" s="11">
-        <f ca="1">IF($C327="","",$C327+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A327)="Finalized",$K327&lt;&gt;""),"",IF($C327="","",$C327+120-TODAY()))</f>
         <v>41</v>
       </c>
       <c r="O327" s="9">
+        <f>IF(AND(TRIM($A327)="Finalized",$K327&lt;&gt;""),"",DATE(2027,6,19))</f>
         <v>46557</v>
       </c>
       <c r="P327" s="8" t="s">
@@ -51697,14 +52023,15 @@
         <v>253</v>
       </c>
       <c r="M328" s="11">
-        <f ca="1">IF($C328="","",$C328+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A328)="Finalized",$K328&lt;&gt;""),"",IF($C328="","",$C328+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N328" s="11">
-        <f ca="1">IF($C328="","",$C328+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A328)="Finalized",$K328&lt;&gt;""),"",IF($C328="","",$C328+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O328" s="9">
+        <f>IF(AND(TRIM($A328)="Finalized",$K328&lt;&gt;""),"",DATE(2027,6,19))</f>
         <v>46557</v>
       </c>
       <c r="P328" s="8" t="s">
@@ -51821,14 +52148,15 @@
         <v>256</v>
       </c>
       <c r="M329" s="11">
-        <f ca="1">IF($C329="","",$C329+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A329)="Finalized",$K329&lt;&gt;""),"",IF($C329="","",$C329+365-TODAY()))</f>
         <v>272</v>
       </c>
       <c r="N329" s="11">
-        <f ca="1">IF($C329="","",$C329+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A329)="Finalized",$K329&lt;&gt;""),"",IF($C329="","",$C329+120-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O329" s="9">
+        <f>IF(AND(TRIM($A329)="Finalized",$K329&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P329" s="8" t="s">
@@ -51947,14 +52275,15 @@
         <v>256</v>
       </c>
       <c r="M330" s="11" t="str">
-        <f ca="1">IF($C330="","",$C330+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A330)="Finalized",$K330&lt;&gt;""),"",IF($C330="","",$C330+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N330" s="11" t="str">
-        <f ca="1">IF($C330="","",$C330+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A330)="Finalized",$K330&lt;&gt;""),"",IF($C330="","",$C330+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O330" s="9">
+        <f>IF(AND(TRIM($A330)="Finalized",$K330&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P330" s="8" t="s">
@@ -52065,14 +52394,15 @@
         <v>256</v>
       </c>
       <c r="M331" s="11">
-        <f ca="1">IF($C331="","",$C331+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A331)="Finalized",$K331&lt;&gt;""),"",IF($C331="","",$C331+365-TODAY()))</f>
         <v>329</v>
       </c>
       <c r="N331" s="11">
-        <f ca="1">IF($C331="","",$C331+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A331)="Finalized",$K331&lt;&gt;""),"",IF($C331="","",$C331+120-TODAY()))</f>
         <v>84</v>
       </c>
       <c r="O331" s="9">
+        <f>IF(AND(TRIM($A331)="Finalized",$K331&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P331" s="8" t="s">
@@ -52191,14 +52521,15 @@
         <v>258</v>
       </c>
       <c r="M332" s="11">
-        <f ca="1">IF($C332="","",$C332+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A332)="Finalized",$K332&lt;&gt;""),"",IF($C332="","",$C332+365-TODAY()))</f>
         <v>270</v>
       </c>
       <c r="N332" s="11">
-        <f ca="1">IF($C332="","",$C332+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A332)="Finalized",$K332&lt;&gt;""),"",IF($C332="","",$C332+120-TODAY()))</f>
         <v>25</v>
       </c>
       <c r="O332" s="9">
+        <f>IF(AND(TRIM($A332)="Finalized",$K332&lt;&gt;""),"",DATE(2027,6,24))</f>
         <v>46562</v>
       </c>
       <c r="P332" s="8" t="s">
@@ -52313,14 +52644,15 @@
         <v>260</v>
       </c>
       <c r="M333" s="11" t="str">
-        <f ca="1">IF($C333="","",$C333+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A333)="Finalized",$K333&lt;&gt;""),"",IF($C333="","",$C333+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N333" s="11" t="str">
-        <f ca="1">IF($C333="","",$C333+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A333)="Finalized",$K333&lt;&gt;""),"",IF($C333="","",$C333+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O333" s="9">
+        <f>IF(AND(TRIM($A333)="Finalized",$K333&lt;&gt;""),"",DATE(2027,6,26))</f>
         <v>46564</v>
       </c>
       <c r="P333" s="8" t="s">
@@ -52429,14 +52761,15 @@
         <v>260</v>
       </c>
       <c r="M334" s="11" t="str">
-        <f ca="1">IF($C334="","",$C334+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A334)="Finalized",$K334&lt;&gt;""),"",IF($C334="","",$C334+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N334" s="11" t="str">
-        <f ca="1">IF($C334="","",$C334+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A334)="Finalized",$K334&lt;&gt;""),"",IF($C334="","",$C334+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O334" s="9">
+        <f>IF(AND(TRIM($A334)="Finalized",$K334&lt;&gt;""),"",DATE(2027,6,26))</f>
         <v>46564</v>
       </c>
       <c r="P334" s="8" t="s">
@@ -52549,14 +52882,15 @@
         <v>263</v>
       </c>
       <c r="M335" s="11">
-        <f ca="1">IF($C335="","",$C335+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A335)="Finalized",$K335&lt;&gt;""),"",IF($C335="","",$C335+365-TODAY()))</f>
         <v>286</v>
       </c>
       <c r="N335" s="11">
-        <f ca="1">IF($C335="","",$C335+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A335)="Finalized",$K335&lt;&gt;""),"",IF($C335="","",$C335+120-TODAY()))</f>
         <v>41</v>
       </c>
       <c r="O335" s="9">
+        <f>IF(AND(TRIM($A335)="Finalized",$K335&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P335" s="8" t="s">
@@ -52667,14 +53001,15 @@
         <v>263</v>
       </c>
       <c r="M336" s="11">
-        <f ca="1">IF($C336="","",$C336+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A336)="Finalized",$K336&lt;&gt;""),"",IF($C336="","",$C336+365-TODAY()))</f>
         <v>280</v>
       </c>
       <c r="N336" s="11">
-        <f ca="1">IF($C336="","",$C336+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A336)="Finalized",$K336&lt;&gt;""),"",IF($C336="","",$C336+120-TODAY()))</f>
         <v>35</v>
       </c>
       <c r="O336" s="9">
+        <f>IF(AND(TRIM($A336)="Finalized",$K336&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P336" s="8" t="s">
@@ -52789,14 +53124,15 @@
         <v>263</v>
       </c>
       <c r="M337" s="11">
-        <f ca="1">IF($C337="","",$C337+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A337)="Finalized",$K337&lt;&gt;""),"",IF($C337="","",$C337+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="N337" s="11">
-        <f ca="1">IF($C337="","",$C337+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A337)="Finalized",$K337&lt;&gt;""),"",IF($C337="","",$C337+120-TODAY()))</f>
         <v>40</v>
       </c>
       <c r="O337" s="9">
+        <f>IF(AND(TRIM($A337)="Finalized",$K337&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P337" s="8" t="s">
@@ -52909,14 +53245,15 @@
         <v>263</v>
       </c>
       <c r="M338" s="11" t="str">
-        <f ca="1">IF($C338="","",$C338+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A338)="Finalized",$K338&lt;&gt;""),"",IF($C338="","",$C338+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N338" s="11" t="str">
-        <f ca="1">IF($C338="","",$C338+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A338)="Finalized",$K338&lt;&gt;""),"",IF($C338="","",$C338+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O338" s="9">
+        <f>IF(AND(TRIM($A338)="Finalized",$K338&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P338" s="8" t="s">
@@ -53035,14 +53372,15 @@
         <v>264</v>
       </c>
       <c r="M339" s="11" t="str">
-        <f ca="1">IF($C339="","",$C339+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A339)="Finalized",$K339&lt;&gt;""),"",IF($C339="","",$C339+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N339" s="11" t="str">
-        <f ca="1">IF($C339="","",$C339+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A339)="Finalized",$K339&lt;&gt;""),"",IF($C339="","",$C339+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O339" s="9">
+        <f>IF(AND(TRIM($A339)="Finalized",$K339&lt;&gt;""),"",DATE(2027,6,30))</f>
         <v>46568</v>
       </c>
       <c r="P339" s="8" t="s">
@@ -53256,7 +53594,7 @@
       </c>
       <c r="M341" s="11"/>
       <c r="N341" s="11">
-        <f ca="1">IF($C341="","",$C341+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A341)="Finalized",$K341&lt;&gt;""),"",IF($C341="","",$C341+180-TODAY()))</f>
         <v>-17</v>
       </c>
       <c r="O341" s="9"/>
@@ -53365,7 +53703,7 @@
       </c>
       <c r="M342" s="11"/>
       <c r="N342" s="11">
-        <f ca="1">IF($C342="","",$C342+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A342)="Finalized",$K342&lt;&gt;""),"",IF($C342="","",$C342+180-TODAY()))</f>
         <v>8</v>
       </c>
       <c r="O342" s="9"/>
@@ -54502,7 +54840,7 @@
       </c>
       <c r="M353" s="11"/>
       <c r="N353" s="11">
-        <f ca="1">IF($C353="","",$C353+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A353)="Finalized",$K353&lt;&gt;""),"",IF($C353="","",$C353+180-TODAY()))</f>
         <v>17</v>
       </c>
       <c r="O353" s="9"/>
@@ -55337,7 +55675,7 @@
       </c>
       <c r="M361" s="11"/>
       <c r="N361" s="11">
-        <f ca="1">IF($C361="","",$C361+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A361)="Finalized",$K361&lt;&gt;""),"",IF($C361="","",$C361+180-TODAY()))</f>
         <v>33</v>
       </c>
       <c r="O361" s="9"/>
@@ -56156,7 +56494,7 @@
       </c>
       <c r="M369" s="11"/>
       <c r="N369" s="11">
-        <f ca="1">IF($C369="","",$C369+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A369)="Finalized",$K369&lt;&gt;""),"",IF($C369="","",$C369+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="O369" s="9"/>
@@ -56665,7 +57003,7 @@
       </c>
       <c r="M374" s="11"/>
       <c r="N374" s="11">
-        <f ca="1">IF($C374="","",$C374+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A374)="Finalized",$K374&lt;&gt;""),"",IF($C374="","",$C374+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="O374" s="9"/>
@@ -56772,7 +57110,7 @@
       </c>
       <c r="M375" s="11"/>
       <c r="N375" s="11" t="str">
-        <f ca="1">IF($C375="","",$C375+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A375)="Finalized",$K375&lt;&gt;""),"",IF($C375="","",$C375+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O375" s="9"/>
@@ -57477,20 +57815,21 @@
         <f>IFERROR(IF(INDEX([2]ORTHO!$K$2:$K$11,MATCH($D382,[2]ORTHO!$D$2:$D$11,0))="","",INDEX([2]ORTHO!$K$2:$K$11,MATCH($D382,[2]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>46195</v>
       </c>
-      <c r="L382" s="11">
+      <c t="str" r="L382" s="11">
         <f ca="1">IF($O382="","",$O382-TODAY())</f>
-        <v>-156</v>
-      </c>
-      <c r="M382" s="11">
-        <f ca="1">IF($C382="","",$C382+365-TODAY())</f>
-        <v>203</v>
-      </c>
-      <c r="N382" s="11">
-        <f ca="1">IF($C382="","",$C382+365-TODAY())</f>
-        <v>203</v>
-      </c>
-      <c r="O382" s="9">
-        <v>46148</v>
+        <v/>
+      </c>
+      <c t="str" r="M382" s="11">
+        <f ca="1">IF(AND(TRIM($A382)="Finalized",$K382&lt;&gt;""),"",IF($C382="","",$C382+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N382" s="11">
+        <f ca="1">IF(AND(TRIM($A382)="Finalized",$K382&lt;&gt;""),"",IF($C382="","",$C382+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O382" s="9">
+        <f>IF(AND(TRIM($A382)="Finalized",$K382&lt;&gt;""),"",DATE(2026,5,6))</f>
+        <v/>
       </c>
       <c r="P382" s="8" t="s">
         <v>86</v>
@@ -57601,20 +57940,21 @@
         <f>IFERROR(IF(INDEX([2]ORTHO!$K$2:$K$11,MATCH($D383,[2]ORTHO!$D$2:$D$11,0))="","",INDEX([2]ORTHO!$K$2:$K$11,MATCH($D383,[2]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>46192</v>
       </c>
-      <c r="L383" s="11">
+      <c t="str" r="L383" s="11">
         <f ca="1">IF($O383="","",$O383-TODAY())</f>
-        <v>-142</v>
-      </c>
-      <c r="M383" s="11">
-        <f ca="1">IF($C383="","",$C383+180-TODAY())</f>
-        <v>109</v>
-      </c>
-      <c r="N383" s="11">
-        <f ca="1">IF($C383="","",$C383+365-TODAY())</f>
-        <v>294</v>
-      </c>
-      <c r="O383" s="9">
-        <v>46162</v>
+        <v/>
+      </c>
+      <c t="str" r="M383" s="11">
+        <f ca="1">IF(AND(TRIM($A383)="Finalized",$K383&lt;&gt;""),"",IF($C383="","",$C383+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N383" s="11">
+        <f ca="1">IF(AND(TRIM($A383)="Finalized",$K383&lt;&gt;""),"",IF($C383="","",$C383+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O383" s="9">
+        <f>IF(AND(TRIM($A383)="Finalized",$K383&lt;&gt;""),"",DATE(2026,5,20))</f>
+        <v/>
       </c>
       <c r="P383" s="8" t="s">
         <v>86</v>
@@ -57727,20 +58067,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D384,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D384,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46257</v>
       </c>
-      <c r="L384" s="11">
+      <c t="str" r="L384" s="11">
         <f ca="1">IF($O384="","",$O384-TODAY())</f>
-        <v>-122</v>
-      </c>
-      <c r="M384" s="11">
-        <f ca="1">IF($C384="","",$C384+365-TODAY())</f>
-        <v>190</v>
-      </c>
-      <c r="N384" s="11">
-        <f ca="1">IF($C384="","",$C384+365-TODAY())</f>
-        <v>190</v>
-      </c>
-      <c r="O384" s="9">
-        <v>46182</v>
+        <v/>
+      </c>
+      <c t="str" r="M384" s="11">
+        <f ca="1">IF(AND(TRIM($A384)="Finalized",$K384&lt;&gt;""),"",IF($C384="","",$C384+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N384" s="11">
+        <f ca="1">IF(AND(TRIM($A384)="Finalized",$K384&lt;&gt;""),"",IF($C384="","",$C384+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O384" s="9">
+        <f>IF(AND(TRIM($A384)="Finalized",$K384&lt;&gt;""),"",DATE(2026,6,9))</f>
+        <v/>
       </c>
       <c r="P384" s="8" t="s">
         <v>86</v>
@@ -57847,20 +58188,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D385,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D385,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46286</v>
       </c>
-      <c r="L385" s="11">
+      <c t="str" r="L385" s="11">
         <f ca="1">IF($O385="","",$O385-TODAY())</f>
-        <v>-120</v>
-      </c>
-      <c r="M385" s="11">
-        <f ca="1">IF($C385="","",$C385+180-TODAY())</f>
-        <v>164</v>
-      </c>
-      <c r="N385" s="11">
-        <f ca="1">IF($C385="","",$C385+365-TODAY())</f>
-        <v>349</v>
-      </c>
-      <c r="O385" s="9">
-        <v>46184</v>
+        <v/>
+      </c>
+      <c t="str" r="M385" s="11">
+        <f ca="1">IF(AND(TRIM($A385)="Finalized",$K385&lt;&gt;""),"",IF($C385="","",$C385+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N385" s="11">
+        <f ca="1">IF(AND(TRIM($A385)="Finalized",$K385&lt;&gt;""),"",IF($C385="","",$C385+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O385" s="9">
+        <f>IF(AND(TRIM($A385)="Finalized",$K385&lt;&gt;""),"",DATE(2026,6,11))</f>
+        <v/>
       </c>
       <c r="P385" s="8" t="s">
         <v>86</v>
@@ -57967,20 +58309,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D386,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D386,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L386" s="11">
+      <c t="str" r="L386" s="11">
         <f ca="1">IF($O386="","",$O386-TODAY())</f>
-        <v>-117</v>
-      </c>
-      <c r="M386" s="11">
-        <f ca="1">IF($C386="","",$C386+365-TODAY())</f>
-        <v>288</v>
-      </c>
-      <c r="N386" s="11">
-        <f ca="1">IF($C386="","",$C386+365-TODAY())</f>
-        <v>288</v>
-      </c>
-      <c r="O386" s="9">
-        <v>46187</v>
+        <v/>
+      </c>
+      <c t="str" r="M386" s="11">
+        <f ca="1">IF(AND(TRIM($A386)="Finalized",$K386&lt;&gt;""),"",IF($C386="","",$C386+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N386" s="11">
+        <f ca="1">IF(AND(TRIM($A386)="Finalized",$K386&lt;&gt;""),"",IF($C386="","",$C386+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O386" s="9">
+        <f>IF(AND(TRIM($A386)="Finalized",$K386&lt;&gt;""),"",DATE(2026,6,14))</f>
+        <v/>
       </c>
       <c r="P386" s="8" t="s">
         <v>86</v>
@@ -58089,20 +58432,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D387,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D387,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46266</v>
       </c>
-      <c r="L387" s="11">
+      <c t="str" r="L387" s="11">
         <f ca="1">IF($O387="","",$O387-TODAY())</f>
-        <v>-110</v>
-      </c>
-      <c r="M387" s="11">
-        <f ca="1">IF($C387="","",$C387+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="N387" s="11">
-        <f ca="1">IF($C387="","",$C387+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="O387" s="9">
-        <v>46194</v>
+        <v/>
+      </c>
+      <c t="str" r="M387" s="11">
+        <f ca="1">IF(AND(TRIM($A387)="Finalized",$K387&lt;&gt;""),"",IF($C387="","",$C387+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N387" s="11">
+        <f ca="1">IF(AND(TRIM($A387)="Finalized",$K387&lt;&gt;""),"",IF($C387="","",$C387+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O387" s="9">
+        <f>IF(AND(TRIM($A387)="Finalized",$K387&lt;&gt;""),"",DATE(2026,6,21))</f>
+        <v/>
       </c>
       <c r="P387" s="8" t="s">
         <v>86</v>
@@ -58209,20 +58553,21 @@
         <f>IFERROR(IF(INDEX([3]US!$K$2:$K$15,MATCH($D388,[3]US!$D$2:$D$15,0))="","",INDEX([3]US!$K$2:$K$15,MATCH($D388,[3]US!$D$2:$D$15,0))),"")</f>
         <v>46269</v>
       </c>
-      <c r="L388" s="11">
+      <c t="str" r="L388" s="11">
         <f ca="1">IF($O388="","",$O388-TODAY())</f>
-        <v>-109</v>
-      </c>
-      <c r="M388" s="11">
-        <f ca="1">IF($F388="","",$F388+90-TODAY())</f>
-        <v>-109</v>
-      </c>
-      <c r="N388" s="11">
-        <f ca="1">IF($C388="","",$C388+180-TODAY())</f>
-        <v>3</v>
-      </c>
-      <c r="O388" s="9">
-        <v>46195</v>
+        <v/>
+      </c>
+      <c t="str" r="M388" s="11">
+        <f ca="1">IF(AND(TRIM($A388)="Finalized",$K388&lt;&gt;""),"",IF($F388="","",$F388+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N388" s="11">
+        <f ca="1">IF(AND(TRIM($A388)="Finalized",$K388&lt;&gt;""),"",IF($C388="","",$C388+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O388" s="9">
+        <f>IF(AND(TRIM($A388)="Finalized",$K388&lt;&gt;""),"",DATE(2026,6,22))</f>
+        <v/>
       </c>
       <c r="P388" s="8" t="s">
         <v>86</v>
@@ -58329,20 +58674,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D389,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D389,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46268</v>
       </c>
-      <c r="L389" s="11">
+      <c t="str" r="L389" s="11">
         <f ca="1">IF($O389="","",$O389-TODAY())</f>
-        <v>-108</v>
-      </c>
-      <c r="M389" s="11">
-        <f ca="1">IF($F389="","",$F389+90-TODAY())</f>
-        <v>-108</v>
-      </c>
-      <c r="N389" s="11">
-        <f ca="1">IF($C389="","",$C389+540-TODAY())</f>
-        <v>359</v>
-      </c>
-      <c r="O389" s="9">
-        <v>46196</v>
+        <v/>
+      </c>
+      <c t="str" r="M389" s="11">
+        <f ca="1">IF(AND(TRIM($A389)="Finalized",$K389&lt;&gt;""),"",IF($F389="","",$F389+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N389" s="11">
+        <f ca="1">IF(AND(TRIM($A389)="Finalized",$K389&lt;&gt;""),"",IF($C389="","",$C389+540-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O389" s="9">
+        <f>IF(AND(TRIM($A389)="Finalized",$K389&lt;&gt;""),"",DATE(2026,6,23))</f>
+        <v/>
       </c>
       <c r="P389" s="8" t="s">
         <v>86</v>
@@ -58449,20 +58795,21 @@
         <f>IFERROR(IF(INDEX([4]ORTHO!$K$2:$K$21,MATCH($D390,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$K$2:$K$21,MATCH($D390,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>46269</v>
       </c>
-      <c r="L390" s="11">
+      <c t="str" r="L390" s="11">
         <f ca="1">IF($O390="","",$O390-TODAY())</f>
-        <v>-101</v>
-      </c>
-      <c r="M390" s="11">
-        <f ca="1">IF($C390="","",$C390+180-TODAY())</f>
-        <v>137</v>
-      </c>
-      <c r="N390" s="11">
-        <f ca="1">IF($C390="","",$C390+365-TODAY())</f>
-        <v>322</v>
-      </c>
-      <c r="O390" s="9">
-        <v>46203</v>
+        <v/>
+      </c>
+      <c t="str" r="M390" s="11">
+        <f ca="1">IF(AND(TRIM($A390)="Finalized",$K390&lt;&gt;""),"",IF($C390="","",$C390+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N390" s="11">
+        <f ca="1">IF(AND(TRIM($A390)="Finalized",$K390&lt;&gt;""),"",IF($C390="","",$C390+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O390" s="9">
+        <f>IF(AND(TRIM($A390)="Finalized",$K390&lt;&gt;""),"",DATE(2026,6,30))</f>
+        <v/>
       </c>
       <c r="P390" s="8" t="s">
         <v>86</v>
@@ -58569,20 +58916,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D391,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D391,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46284</v>
       </c>
-      <c r="L391" s="11">
+      <c t="str" r="L391" s="11">
         <f ca="1">IF($O391="","",$O391-TODAY())</f>
-        <v>-96</v>
-      </c>
-      <c r="M391" s="11">
-        <f ca="1">IF($C391="","",$C391+180-TODAY())</f>
-        <v>3</v>
-      </c>
-      <c r="N391" s="11">
-        <f ca="1">IF($C391="","",$C391+365-TODAY())</f>
-        <v>188</v>
-      </c>
-      <c r="O391" s="9">
-        <v>46208</v>
+        <v/>
+      </c>
+      <c t="str" r="M391" s="11">
+        <f ca="1">IF(AND(TRIM($A391)="Finalized",$K391&lt;&gt;""),"",IF($C391="","",$C391+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N391" s="11">
+        <f ca="1">IF(AND(TRIM($A391)="Finalized",$K391&lt;&gt;""),"",IF($C391="","",$C391+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O391" s="9">
+        <f>IF(AND(TRIM($A391)="Finalized",$K391&lt;&gt;""),"",DATE(2026,7,5))</f>
+        <v/>
       </c>
       <c r="P391" s="8" t="s">
         <v>86</v>
@@ -58689,20 +59037,21 @@
         <f>IFERROR(IF(INDEX([3]US!$K$2:$K$15,MATCH($D392,[3]US!$D$2:$D$15,0))="","",INDEX([3]US!$K$2:$K$15,MATCH($D392,[3]US!$D$2:$D$15,0))),"")</f>
         <v>46278</v>
       </c>
-      <c r="L392" s="11">
+      <c t="str" r="L392" s="11">
         <f ca="1">IF($O392="","",$O392-TODAY())</f>
-        <v>-92</v>
-      </c>
-      <c r="M392" s="11">
-        <f ca="1">IF($C392="","",$C392+180-TODAY())</f>
-        <v>5</v>
-      </c>
-      <c r="N392" s="11">
-        <f ca="1">IF($C392="","",$C392+180-TODAY())</f>
-        <v>5</v>
-      </c>
-      <c r="O392" s="9">
-        <v>46212</v>
+        <v/>
+      </c>
+      <c t="str" r="M392" s="11">
+        <f ca="1">IF(AND(TRIM($A392)="Finalized",$K392&lt;&gt;""),"",IF($C392="","",$C392+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N392" s="11">
+        <f ca="1">IF(AND(TRIM($A392)="Finalized",$K392&lt;&gt;""),"",IF($C392="","",$C392+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O392" s="9">
+        <f>IF(AND(TRIM($A392)="Finalized",$K392&lt;&gt;""),"",DATE(2026,7,9))</f>
+        <v/>
       </c>
       <c r="P392" s="8" t="s">
         <v>208</v>
@@ -58809,20 +59158,21 @@
         <f>IFERROR(IF(INDEX([4]ORTHO!$K$2:$K$21,MATCH($D393,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$K$2:$K$21,MATCH($D393,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>46278</v>
       </c>
-      <c r="L393" s="11">
+      <c t="str" r="L393" s="11">
         <f ca="1">IF($O393="","",$O393-TODAY())</f>
-        <v>-89</v>
-      </c>
-      <c r="M393" s="11">
-        <f ca="1">IF($F393="","",$F393+90-TODAY())</f>
-        <v>-89</v>
-      </c>
-      <c r="N393" s="11">
-        <f ca="1">IF($C393="","",$C393+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="O393" s="9">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M393" s="11">
+        <f ca="1">IF(AND(TRIM($A393)="Finalized",$K393&lt;&gt;""),"",IF($F393="","",$F393+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N393" s="11">
+        <f ca="1">IF(AND(TRIM($A393)="Finalized",$K393&lt;&gt;""),"",IF($C393="","",$C393+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O393" s="9">
+        <f>IF(AND(TRIM($A393)="Finalized",$K393&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P393" s="8" t="s">
         <v>86</v>
@@ -58927,20 +59277,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D394,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D394,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L394" s="11">
+      <c t="str" r="L394" s="11">
         <f ca="1">IF($O394="","",$O394-TODAY())</f>
-        <v>-89</v>
-      </c>
-      <c r="M394" s="11">
-        <f ca="1">IF($C394="","",$C394+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="N394" s="11">
-        <f ca="1">IF($C394="","",$C394+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="O394" s="9">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M394" s="11">
+        <f ca="1">IF(AND(TRIM($A394)="Finalized",$K394&lt;&gt;""),"",IF($C394="","",$C394+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N394" s="11">
+        <f ca="1">IF(AND(TRIM($A394)="Finalized",$K394&lt;&gt;""),"",IF($C394="","",$C394+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O394" s="9">
+        <f>IF(AND(TRIM($A394)="Finalized",$K394&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P394" s="8" t="s">
         <v>86</v>
@@ -59049,20 +59400,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D395,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D395,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L395" s="11">
+      <c t="str" r="L395" s="11">
         <f ca="1">IF($O395="","",$O395-TODAY())</f>
-        <v>-89</v>
-      </c>
-      <c r="M395" s="11">
-        <f ca="1">IF($C395="","",$C395+365-TODAY())</f>
-        <v>228</v>
-      </c>
-      <c r="N395" s="11">
-        <f ca="1">IF($C395="","",$C395+365-TODAY())</f>
-        <v>228</v>
-      </c>
-      <c r="O395" s="9">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M395" s="11">
+        <f ca="1">IF(AND(TRIM($A395)="Finalized",$K395&lt;&gt;""),"",IF($C395="","",$C395+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N395" s="11">
+        <f ca="1">IF(AND(TRIM($A395)="Finalized",$K395&lt;&gt;""),"",IF($C395="","",$C395+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O395" s="9">
+        <f>IF(AND(TRIM($A395)="Finalized",$K395&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P395" s="8" t="s">
         <v>86</v>
@@ -59171,20 +59523,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D396,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D396,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L396" s="11">
+      <c t="str" r="L396" s="11">
         <f ca="1">IF($O396="","",$O396-TODAY())</f>
-        <v>-86</v>
-      </c>
-      <c r="M396" s="11">
-        <f ca="1">IF($C396="","",$C396+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="N396" s="11">
-        <f ca="1">IF($C396="","",$C396+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="O396" s="9">
-        <v>46218</v>
+        <v/>
+      </c>
+      <c t="str" r="M396" s="11">
+        <f ca="1">IF(AND(TRIM($A396)="Finalized",$K396&lt;&gt;""),"",IF($C396="","",$C396+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N396" s="11">
+        <f ca="1">IF(AND(TRIM($A396)="Finalized",$K396&lt;&gt;""),"",IF($C396="","",$C396+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O396" s="9">
+        <f>IF(AND(TRIM($A396)="Finalized",$K396&lt;&gt;""),"",DATE(2026,7,15))</f>
+        <v/>
       </c>
       <c r="P396" s="8" t="s">
         <v>86</v>
@@ -59293,20 +59646,21 @@
         <f>IFERROR(IF(INDEX([4]ORTHO!$K$2:$K$21,MATCH($D397,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$K$2:$K$21,MATCH($D397,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>46278</v>
       </c>
-      <c r="L397" s="11">
+      <c t="str" r="L397" s="11">
         <f ca="1">IF($O397="","",$O397-TODAY())</f>
-        <v>-85</v>
-      </c>
-      <c r="M397" s="11">
-        <f ca="1">IF($C397="","",$C397+180-TODAY())</f>
-        <v>59</v>
-      </c>
-      <c r="N397" s="11">
-        <f ca="1">IF($C397="","",$C397+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="O397" s="9">
-        <v>46219</v>
+        <v/>
+      </c>
+      <c t="str" r="M397" s="11">
+        <f ca="1">IF(AND(TRIM($A397)="Finalized",$K397&lt;&gt;""),"",IF($C397="","",$C397+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N397" s="11">
+        <f ca="1">IF(AND(TRIM($A397)="Finalized",$K397&lt;&gt;""),"",IF($C397="","",$C397+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O397" s="9">
+        <f>IF(AND(TRIM($A397)="Finalized",$K397&lt;&gt;""),"",DATE(2026,7,16))</f>
+        <v/>
       </c>
       <c r="P397" s="8" t="s">
         <v>86</v>
@@ -59411,20 +59765,21 @@
         <f>IFERROR(IF(INDEX([4]BH!$K$2:$K$12,MATCH($D398,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$K$2:$K$12,MATCH($D398,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>46265</v>
       </c>
-      <c r="L398" s="11">
+      <c t="str" r="L398" s="11">
         <f ca="1">IF($O398="","",$O398-TODAY())</f>
-        <v>-79</v>
-      </c>
-      <c r="M398" s="11">
-        <f ca="1">IF($F398="","",$F398+90-TODAY())</f>
-        <v>-79</v>
-      </c>
-      <c r="N398" s="11">
-        <f ca="1">IF($C398="","",$C398+540-TODAY())</f>
-        <v>393</v>
-      </c>
-      <c r="O398" s="9">
-        <v>46225</v>
+        <v/>
+      </c>
+      <c t="str" r="M398" s="11">
+        <f ca="1">IF(AND(TRIM($A398)="Finalized",$K398&lt;&gt;""),"",IF($F398="","",$F398+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N398" s="11">
+        <f ca="1">IF(AND(TRIM($A398)="Finalized",$K398&lt;&gt;""),"",IF($C398="","",$C398+540-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O398" s="9">
+        <f>IF(AND(TRIM($A398)="Finalized",$K398&lt;&gt;""),"",DATE(2026,7,22))</f>
+        <v/>
       </c>
       <c r="P398" s="8" t="s">
         <v>86</v>
@@ -59531,20 +59886,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D399,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D399,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L399" s="11">
+      <c t="str" r="L399" s="11">
         <f ca="1">IF($O399="","",$O399-TODAY())</f>
-        <v>-79</v>
-      </c>
-      <c r="M399" s="11">
-        <f ca="1">IF($C399="","",$C399+180-TODAY())</f>
-        <v>30</v>
-      </c>
-      <c r="N399" s="11">
-        <f ca="1">IF($C399="","",$C399+365-TODAY())</f>
-        <v>215</v>
-      </c>
-      <c r="O399" s="9">
-        <v>46225</v>
+        <v/>
+      </c>
+      <c t="str" r="M399" s="11">
+        <f ca="1">IF(AND(TRIM($A399)="Finalized",$K399&lt;&gt;""),"",IF($C399="","",$C399+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N399" s="11">
+        <f ca="1">IF(AND(TRIM($A399)="Finalized",$K399&lt;&gt;""),"",IF($C399="","",$C399+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O399" s="9">
+        <f>IF(AND(TRIM($A399)="Finalized",$K399&lt;&gt;""),"",DATE(2026,7,22))</f>
+        <v/>
       </c>
       <c r="P399" s="8" t="s">
         <v>86</v>
@@ -59649,20 +60005,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D400,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D400,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L400" s="11">
+      <c t="str" r="L400" s="11">
         <f ca="1">IF($O400="","",$O400-TODAY())</f>
-        <v>-75</v>
-      </c>
-      <c r="M400" s="11">
-        <f ca="1">IF($C400="","",$C400+180-TODAY())</f>
-        <v>32</v>
-      </c>
-      <c r="N400" s="11">
-        <f ca="1">IF($C400="","",$C400+365-TODAY())</f>
-        <v>217</v>
-      </c>
-      <c r="O400" s="9">
-        <v>46229</v>
+        <v/>
+      </c>
+      <c t="str" r="M400" s="11">
+        <f ca="1">IF(AND(TRIM($A400)="Finalized",$K400&lt;&gt;""),"",IF($C400="","",$C400+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N400" s="11">
+        <f ca="1">IF(AND(TRIM($A400)="Finalized",$K400&lt;&gt;""),"",IF($C400="","",$C400+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O400" s="9">
+        <f>IF(AND(TRIM($A400)="Finalized",$K400&lt;&gt;""),"",DATE(2026,7,26))</f>
+        <v/>
       </c>
       <c r="P400" s="8" t="s">
         <v>86</v>
@@ -59771,20 +60128,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D401,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D401,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46285</v>
       </c>
-      <c r="L401" s="11">
+      <c t="str" r="L401" s="11">
         <f ca="1">IF($O401="","",$O401-TODAY())</f>
-        <v>-75</v>
-      </c>
-      <c r="M401" s="11">
-        <f ca="1">IF($C401="","",$C401+365-TODAY())</f>
-        <v>278</v>
-      </c>
-      <c r="N401" s="11">
-        <f ca="1">IF($C401="","",$C401+365-TODAY())</f>
-        <v>278</v>
-      </c>
-      <c r="O401" s="9">
-        <v>46229</v>
+        <v/>
+      </c>
+      <c t="str" r="M401" s="11">
+        <f ca="1">IF(AND(TRIM($A401)="Finalized",$K401&lt;&gt;""),"",IF($C401="","",$C401+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N401" s="11">
+        <f ca="1">IF(AND(TRIM($A401)="Finalized",$K401&lt;&gt;""),"",IF($C401="","",$C401+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O401" s="9">
+        <f>IF(AND(TRIM($A401)="Finalized",$K401&lt;&gt;""),"",DATE(2026,7,26))</f>
+        <v/>
       </c>
       <c r="P401" s="8" t="s">
         <v>86</v>
@@ -59893,20 +60251,21 @@
         <f>IFERROR(IF(INDEX([3]US!$K$2:$K$15,MATCH($D402,[3]US!$D$2:$D$15,0))="","",INDEX([3]US!$K$2:$K$15,MATCH($D402,[3]US!$D$2:$D$15,0))),"")</f>
         <v>46278</v>
       </c>
-      <c r="L402" s="11">
+      <c t="str" r="L402" s="11">
         <f ca="1">IF($O402="","",$O402-TODAY())</f>
-        <v>-72</v>
-      </c>
-      <c r="M402" s="11">
-        <f ca="1">IF($C402="","",$C402+180-TODAY())</f>
-        <v>3</v>
-      </c>
-      <c r="N402" s="11">
-        <f ca="1">IF($C402="","",$C402+180-TODAY())</f>
-        <v>3</v>
-      </c>
-      <c r="O402" s="9">
-        <v>46232</v>
+        <v/>
+      </c>
+      <c t="str" r="M402" s="11">
+        <f ca="1">IF(AND(TRIM($A402)="Finalized",$K402&lt;&gt;""),"",IF($C402="","",$C402+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N402" s="11">
+        <f ca="1">IF(AND(TRIM($A402)="Finalized",$K402&lt;&gt;""),"",IF($C402="","",$C402+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O402" s="9">
+        <f>IF(AND(TRIM($A402)="Finalized",$K402&lt;&gt;""),"",DATE(2026,7,29))</f>
+        <v/>
       </c>
       <c r="P402" s="8" t="s">
         <v>208</v>
@@ -60013,20 +60372,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D403,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D403,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46253</v>
       </c>
-      <c r="L403" s="11">
+      <c t="str" r="L403" s="11">
         <f ca="1">IF($O403="","",$O403-TODAY())</f>
-        <v>-71</v>
-      </c>
-      <c r="M403" s="11">
-        <f ca="1">IF($C403="","",$C403+180-TODAY())</f>
-        <v>46</v>
-      </c>
-      <c r="N403" s="11">
-        <f ca="1">IF($C403="","",$C403+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="O403" s="9">
-        <v>46233</v>
+        <v/>
+      </c>
+      <c t="str" r="M403" s="11">
+        <f ca="1">IF(AND(TRIM($A403)="Finalized",$K403&lt;&gt;""),"",IF($C403="","",$C403+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N403" s="11">
+        <f ca="1">IF(AND(TRIM($A403)="Finalized",$K403&lt;&gt;""),"",IF($C403="","",$C403+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O403" s="9">
+        <f>IF(AND(TRIM($A403)="Finalized",$K403&lt;&gt;""),"",DATE(2026,7,30))</f>
+        <v/>
       </c>
       <c r="P403" s="8" t="s">
         <v>86</v>
@@ -60133,20 +60493,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D404,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D404,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46253</v>
       </c>
-      <c r="L404" s="11">
+      <c t="str" r="L404" s="11">
         <f ca="1">IF($O404="","",$O404-TODAY())</f>
-        <v>-64</v>
-      </c>
-      <c r="M404" s="11">
-        <f ca="1">IF($C404="","",$C404+180-TODAY())</f>
-        <v>71</v>
-      </c>
-      <c r="N404" s="11">
-        <f ca="1">IF($C404="","",$C404+365-TODAY())</f>
-        <v>256</v>
-      </c>
-      <c r="O404" s="9">
-        <v>46240</v>
+        <v/>
+      </c>
+      <c t="str" r="M404" s="11">
+        <f ca="1">IF(AND(TRIM($A404)="Finalized",$K404&lt;&gt;""),"",IF($C404="","",$C404+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N404" s="11">
+        <f ca="1">IF(AND(TRIM($A404)="Finalized",$K404&lt;&gt;""),"",IF($C404="","",$C404+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O404" s="9">
+        <f>IF(AND(TRIM($A404)="Finalized",$K404&lt;&gt;""),"",DATE(2026,8,6))</f>
+        <v/>
       </c>
       <c r="P404" s="8" t="s">
         <v>86</v>
@@ -60259,20 +60620,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D405,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D405,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46253</v>
       </c>
-      <c r="L405" s="11">
+      <c t="str" r="L405" s="11">
         <f ca="1">IF($O405="","",$O405-TODAY())</f>
-        <v>-61</v>
-      </c>
-      <c r="M405" s="11">
-        <f ca="1">IF($C405="","",$C405+365-TODAY())</f>
-        <v>259</v>
-      </c>
-      <c r="N405" s="11">
-        <f ca="1">IF($C405="","",$C405+365-TODAY())</f>
-        <v>259</v>
-      </c>
-      <c r="O405" s="9">
-        <v>46243</v>
+        <v/>
+      </c>
+      <c t="str" r="M405" s="11">
+        <f ca="1">IF(AND(TRIM($A405)="Finalized",$K405&lt;&gt;""),"",IF($C405="","",$C405+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N405" s="11">
+        <f ca="1">IF(AND(TRIM($A405)="Finalized",$K405&lt;&gt;""),"",IF($C405="","",$C405+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O405" s="9">
+        <f>IF(AND(TRIM($A405)="Finalized",$K405&lt;&gt;""),"",DATE(2026,8,9))</f>
+        <v/>
       </c>
       <c r="P405" s="8" t="s">
         <v>86</v>
@@ -60381,20 +60743,21 @@
         <f>IFERROR(IF(INDEX([5]GAE!$K$2:$K$7,MATCH($D406,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$K$2:$K$7,MATCH($D406,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>46255</v>
       </c>
-      <c r="L406" s="11">
+      <c t="str" r="L406" s="11">
         <f ca="1">IF($O406="","",$O406-TODAY())</f>
-        <v>-61</v>
-      </c>
-      <c r="M406" s="11">
-        <f ca="1">IF($F406="","",$F406+90-TODAY())</f>
-        <v>-61</v>
-      </c>
-      <c r="N406" s="11">
-        <f ca="1">IF($C406="","",$C406+60-TODAY())</f>
-        <v>-57</v>
-      </c>
-      <c r="O406" s="9">
-        <v>46243</v>
+        <v/>
+      </c>
+      <c t="str" r="M406" s="11">
+        <f ca="1">IF(AND(TRIM($A406)="Finalized",$K406&lt;&gt;""),"",IF($F406="","",$F406+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N406" s="11">
+        <f ca="1">IF(AND(TRIM($A406)="Finalized",$K406&lt;&gt;""),"",IF($C406="","",$C406+60-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O406" s="9">
+        <f>IF(AND(TRIM($A406)="Finalized",$K406&lt;&gt;""),"",DATE(2026,8,9))</f>
+        <v/>
       </c>
       <c r="P406" s="8" t="s">
         <v>86</v>
@@ -60507,20 +60870,21 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D407,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D407,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L407" s="11">
+      <c t="str" r="L407" s="11">
         <f ca="1">IF($O407="","",$O407-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="M407" s="11">
-        <f ca="1">IF($F407="","",$F407+90-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="N407" s="11">
-        <f ca="1">IF($C407="","",$C407+365-TODAY())</f>
-        <v>277</v>
-      </c>
-      <c r="O407" s="9">
-        <v>46244</v>
+        <v/>
+      </c>
+      <c t="str" r="M407" s="11">
+        <f ca="1">IF(AND(TRIM($A407)="Finalized",$K407&lt;&gt;""),"",IF($F407="","",$F407+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N407" s="11">
+        <f ca="1">IF(AND(TRIM($A407)="Finalized",$K407&lt;&gt;""),"",IF($C407="","",$C407+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O407" s="9">
+        <f>IF(AND(TRIM($A407)="Finalized",$K407&lt;&gt;""),"",DATE(2026,8,10))</f>
+        <v/>
       </c>
       <c r="P407" s="8" t="s">
         <v>86</v>
@@ -60625,20 +60989,21 @@
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D408,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D408,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46261</v>
       </c>
-      <c r="L408" s="11">
+      <c t="str" r="L408" s="11">
         <f ca="1">IF($O408="","",$O408-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="M408" s="11">
-        <f ca="1">IF($C408="","",$C408+365-TODAY())</f>
-        <v>259</v>
-      </c>
-      <c r="N408" s="11">
-        <f ca="1">IF($C408="","",$C408+90-TODAY())</f>
-        <v>-16</v>
-      </c>
-      <c r="O408" s="9">
-        <v>46244</v>
+        <v/>
+      </c>
+      <c t="str" r="M408" s="11">
+        <f ca="1">IF(AND(TRIM($A408)="Finalized",$K408&lt;&gt;""),"",IF($C408="","",$C408+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N408" s="11">
+        <f ca="1">IF(AND(TRIM($A408)="Finalized",$K408&lt;&gt;""),"",IF($C408="","",$C408+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O408" s="9">
+        <f>IF(AND(TRIM($A408)="Finalized",$K408&lt;&gt;""),"",DATE(2026,8,10))</f>
+        <v/>
       </c>
       <c r="P408" s="8" t="s">
         <v>71</v>
@@ -60749,20 +61114,21 @@
         <f>IFERROR(IF(INDEX([4]US!$K$2:$K$23,MATCH($D409,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$K$2:$K$23,MATCH($D409,[4]US!$D$2:$D$23,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L409" s="11">
+      <c t="str" r="L409" s="11">
         <f ca="1">IF($O409="","",$O409-TODAY())</f>
-        <v>-58</v>
-      </c>
-      <c r="M409" s="11">
-        <f ca="1">IF($C409="","",$C409+180-TODAY())</f>
-        <v>75</v>
-      </c>
-      <c r="N409" s="11">
-        <f ca="1">IF($C409="","",$C409+180-TODAY())</f>
-        <v>75</v>
-      </c>
-      <c r="O409" s="9">
-        <v>46246</v>
+        <v/>
+      </c>
+      <c t="str" r="M409" s="11">
+        <f ca="1">IF(AND(TRIM($A409)="Finalized",$K409&lt;&gt;""),"",IF($C409="","",$C409+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N409" s="11">
+        <f ca="1">IF(AND(TRIM($A409)="Finalized",$K409&lt;&gt;""),"",IF($C409="","",$C409+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O409" s="9">
+        <f>IF(AND(TRIM($A409)="Finalized",$K409&lt;&gt;""),"",DATE(2026,8,12))</f>
+        <v/>
       </c>
       <c r="P409" s="8" t="s">
         <v>208</v>
@@ -60869,20 +61235,21 @@
         <f>IFERROR(IF(INDEX([6]ORTHO!$K$2:$K$39,MATCH($D410,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$K$2:$K$39,MATCH($D410,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>46246</v>
       </c>
-      <c r="L410" s="11">
+      <c t="str" r="L410" s="11">
         <f ca="1">IF($O410="","",$O410-TODAY())</f>
-        <v>-54</v>
-      </c>
-      <c r="M410" s="11">
-        <f ca="1">IF($C410="","",$C410+365-TODAY())</f>
-        <v>293</v>
-      </c>
-      <c r="N410" s="11">
-        <f ca="1">IF($C410="","",$C410+90-TODAY())</f>
-        <v>18</v>
-      </c>
-      <c r="O410" s="9">
-        <v>46250</v>
+        <v/>
+      </c>
+      <c t="str" r="M410" s="11">
+        <f ca="1">IF(AND(TRIM($A410)="Finalized",$K410&lt;&gt;""),"",IF($C410="","",$C410+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N410" s="11">
+        <f ca="1">IF(AND(TRIM($A410)="Finalized",$K410&lt;&gt;""),"",IF($C410="","",$C410+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O410" s="9">
+        <f>IF(AND(TRIM($A410)="Finalized",$K410&lt;&gt;""),"",DATE(2026,8,16))</f>
+        <v/>
       </c>
       <c r="P410" s="8" t="s">
         <v>71</v>
@@ -60985,20 +61352,21 @@
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D411,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D411,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L411" s="11">
+      <c t="str" r="L411" s="11">
         <f ca="1">IF($O411="","",$O411-TODAY())</f>
-        <v>-52</v>
-      </c>
-      <c r="M411" s="11">
-        <f ca="1">IF($C411="","",$C411+90-TODAY())</f>
-        <v>-44</v>
-      </c>
-      <c r="N411" s="11">
-        <f ca="1">IF($C411="","",$C411+90-TODAY())</f>
-        <v>-44</v>
-      </c>
-      <c r="O411" s="9">
-        <v>46252</v>
+        <v/>
+      </c>
+      <c t="str" r="M411" s="11">
+        <f ca="1">IF(AND(TRIM($A411)="Finalized",$K411&lt;&gt;""),"",IF($C411="","",$C411+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N411" s="11">
+        <f ca="1">IF(AND(TRIM($A411)="Finalized",$K411&lt;&gt;""),"",IF($C411="","",$C411+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O411" s="9">
+        <f>IF(AND(TRIM($A411)="Finalized",$K411&lt;&gt;""),"",DATE(2026,8,18))</f>
+        <v/>
       </c>
       <c r="P411" s="8" t="s">
         <v>188</v>
@@ -61107,20 +61475,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D412,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D412,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L412" s="11">
+      <c t="str" r="L412" s="11">
         <f ca="1">IF($O412="","",$O412-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="M412" s="11">
-        <f ca="1">IF($C412="","",$C412+180-TODAY())</f>
-        <v>59</v>
-      </c>
-      <c r="N412" s="11">
-        <f ca="1">IF($C412="","",$C412+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="O412" s="9">
-        <v>46253</v>
+        <v/>
+      </c>
+      <c t="str" r="M412" s="11">
+        <f ca="1">IF(AND(TRIM($A412)="Finalized",$K412&lt;&gt;""),"",IF($C412="","",$C412+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N412" s="11">
+        <f ca="1">IF(AND(TRIM($A412)="Finalized",$K412&lt;&gt;""),"",IF($C412="","",$C412+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O412" s="9">
+        <f>IF(AND(TRIM($A412)="Finalized",$K412&lt;&gt;""),"",DATE(2026,8,19))</f>
+        <v/>
       </c>
       <c r="P412" s="8" t="s">
         <v>86</v>
@@ -61229,20 +61598,21 @@
         <f>IFERROR(IF(INDEX([5]US!$K$2:$K$19,MATCH($D413,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$K$2:$K$19,MATCH($D413,[5]US!$D$2:$D$19,0))),"")</f>
         <v>46246</v>
       </c>
-      <c r="L413" s="11">
+      <c t="str" r="L413" s="11">
         <f ca="1">IF($O413="","",$O413-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="M413" s="11">
-        <f ca="1">IF($F413="","",$F413+90-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="N413" s="11">
-        <f ca="1">IF($C413="","",$C413+180-TODAY())</f>
-        <v>58</v>
-      </c>
-      <c r="O413" s="9">
-        <v>46253</v>
+        <v/>
+      </c>
+      <c t="str" r="M413" s="11">
+        <f ca="1">IF(AND(TRIM($A413)="Finalized",$K413&lt;&gt;""),"",IF($F413="","",$F413+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N413" s="11">
+        <f ca="1">IF(AND(TRIM($A413)="Finalized",$K413&lt;&gt;""),"",IF($C413="","",$C413+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O413" s="9">
+        <f>IF(AND(TRIM($A413)="Finalized",$K413&lt;&gt;""),"",DATE(2026,8,19))</f>
+        <v/>
       </c>
       <c r="P413" s="8" t="s">
         <v>86</v>
@@ -61347,20 +61717,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D414,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D414,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L414" s="11">
+      <c t="str" r="L414" s="11">
         <f ca="1">IF($O414="","",$O414-TODAY())</f>
-        <v>-50</v>
-      </c>
-      <c r="M414" s="11">
-        <f ca="1">IF($C414="","",$C414+365-TODAY())</f>
-        <v>255</v>
-      </c>
-      <c r="N414" s="11">
-        <f ca="1">IF($C414="","",$C414+365-TODAY())</f>
-        <v>255</v>
-      </c>
-      <c r="O414" s="9">
-        <v>46254</v>
+        <v/>
+      </c>
+      <c t="str" r="M414" s="11">
+        <f ca="1">IF(AND(TRIM($A414)="Finalized",$K414&lt;&gt;""),"",IF($C414="","",$C414+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N414" s="11">
+        <f ca="1">IF(AND(TRIM($A414)="Finalized",$K414&lt;&gt;""),"",IF($C414="","",$C414+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O414" s="9">
+        <f>IF(AND(TRIM($A414)="Finalized",$K414&lt;&gt;""),"",DATE(2026,8,20))</f>
+        <v/>
       </c>
       <c r="P414" s="8" t="s">
         <v>86</v>
@@ -61469,20 +61840,21 @@
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D415,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D415,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L415" s="11">
+      <c t="str" r="L415" s="11">
         <f ca="1">IF($O415="","",$O415-TODAY())</f>
-        <v>-46</v>
-      </c>
-      <c r="M415" s="11">
-        <f ca="1">IF($F415="","",$F415+90-TODAY())</f>
-        <v>-46</v>
-      </c>
-      <c r="N415" s="11">
-        <f ca="1">IF($C415="","",$C415+180-TODAY())</f>
-        <v>107</v>
-      </c>
-      <c r="O415" s="9">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M415" s="11">
+        <f ca="1">IF(AND(TRIM($A415)="Finalized",$K415&lt;&gt;""),"",IF($F415="","",$F415+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N415" s="11">
+        <f ca="1">IF(AND(TRIM($A415)="Finalized",$K415&lt;&gt;""),"",IF($C415="","",$C415+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O415" s="9">
+        <f>IF(AND(TRIM($A415)="Finalized",$K415&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P415" s="8" t="s">
         <v>86</v>
@@ -61587,20 +61959,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D416,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D416,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46248</v>
       </c>
-      <c r="L416" s="11">
+      <c t="str" r="L416" s="11">
         <f ca="1">IF($O416="","",$O416-TODAY())</f>
-        <v>-46</v>
-      </c>
-      <c r="M416" s="11">
-        <f ca="1">IF($C416="","",$C416+180-TODAY())</f>
-        <v>67</v>
-      </c>
-      <c r="N416" s="11">
-        <f ca="1">IF($C416="","",$C416+365-TODAY())</f>
-        <v>252</v>
-      </c>
-      <c r="O416" s="9">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M416" s="11">
+        <f ca="1">IF(AND(TRIM($A416)="Finalized",$K416&lt;&gt;""),"",IF($C416="","",$C416+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N416" s="11">
+        <f ca="1">IF(AND(TRIM($A416)="Finalized",$K416&lt;&gt;""),"",IF($C416="","",$C416+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O416" s="9">
+        <f>IF(AND(TRIM($A416)="Finalized",$K416&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P416" s="8" t="s">
         <v>86</v>
@@ -61711,20 +62084,21 @@
         <f>IFERROR(IF(INDEX([5]US!$K$2:$K$19,MATCH($D417,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$K$2:$K$19,MATCH($D417,[5]US!$D$2:$D$19,0))),"")</f>
         <v>46251</v>
       </c>
-      <c r="L417" s="11">
+      <c t="str" r="L417" s="11">
         <f ca="1">IF($O417="","",$O417-TODAY())</f>
-        <v>-46</v>
-      </c>
-      <c r="M417" s="11">
-        <f ca="1">IF($F417="","",$F417+90-TODAY())</f>
-        <v>-46</v>
-      </c>
-      <c r="N417" s="11">
-        <f ca="1">IF($C417="","",$C417+60-TODAY())</f>
-        <v>-69</v>
-      </c>
-      <c r="O417" s="9">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M417" s="11">
+        <f ca="1">IF(AND(TRIM($A417)="Finalized",$K417&lt;&gt;""),"",IF($F417="","",$F417+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N417" s="11">
+        <f ca="1">IF(AND(TRIM($A417)="Finalized",$K417&lt;&gt;""),"",IF($C417="","",$C417+60-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O417" s="9">
+        <f>IF(AND(TRIM($A417)="Finalized",$K417&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P417" s="8" t="s">
         <v>86</v>
@@ -61831,20 +62205,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D418,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D418,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L418" s="11">
+      <c t="str" r="L418" s="11">
         <f ca="1">IF($O418="","",$O418-TODAY())</f>
-        <v>-44</v>
-      </c>
-      <c r="M418" s="11">
-        <f ca="1">IF($C418="","",$C418+365-TODAY())</f>
-        <v>231</v>
-      </c>
-      <c r="N418" s="11">
-        <f ca="1">IF($C418="","",$C418+90-TODAY())</f>
-        <v>-44</v>
-      </c>
-      <c r="O418" s="9">
-        <v>46260</v>
+        <v/>
+      </c>
+      <c t="str" r="M418" s="11">
+        <f ca="1">IF(AND(TRIM($A418)="Finalized",$K418&lt;&gt;""),"",IF($C418="","",$C418+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N418" s="11">
+        <f ca="1">IF(AND(TRIM($A418)="Finalized",$K418&lt;&gt;""),"",IF($C418="","",$C418+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O418" s="9">
+        <f>IF(AND(TRIM($A418)="Finalized",$K418&lt;&gt;""),"",DATE(2026,8,26))</f>
+        <v/>
       </c>
       <c r="P418" s="8" t="s">
         <v>208</v>
@@ -61955,20 +62330,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D419,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D419,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46272</v>
       </c>
-      <c r="L419" s="11">
+      <c t="str" r="L419" s="11">
         <f ca="1">IF($O419="","",$O419-TODAY())</f>
-        <v>-40</v>
-      </c>
-      <c r="M419" s="11">
-        <f ca="1">IF($C419="","",$C419+180-TODAY())</f>
-        <v>88</v>
-      </c>
-      <c r="N419" s="11">
-        <f ca="1">IF($C419="","",$C419+365-TODAY())</f>
-        <v>273</v>
-      </c>
-      <c r="O419" s="9">
-        <v>46264</v>
+        <v/>
+      </c>
+      <c t="str" r="M419" s="11">
+        <f ca="1">IF(AND(TRIM($A419)="Finalized",$K419&lt;&gt;""),"",IF($C419="","",$C419+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N419" s="11">
+        <f ca="1">IF(AND(TRIM($A419)="Finalized",$K419&lt;&gt;""),"",IF($C419="","",$C419+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O419" s="9">
+        <f>IF(AND(TRIM($A419)="Finalized",$K419&lt;&gt;""),"",DATE(2026,8,30))</f>
+        <v/>
       </c>
       <c r="P419" s="8" t="s">
         <v>86</v>
@@ -62075,20 +62451,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D420,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D420,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46276</v>
       </c>
-      <c r="L420" s="11">
+      <c t="str" r="L420" s="11">
         <f ca="1">IF($O420="","",$O420-TODAY())</f>
-        <v>-40</v>
-      </c>
-      <c r="M420" s="11">
-        <f ca="1">IF($C420="","",$C420+365-TODAY())</f>
-        <v>285</v>
-      </c>
-      <c r="N420" s="11">
-        <f ca="1">IF($C420="","",$C420+365-TODAY())</f>
-        <v>285</v>
-      </c>
-      <c r="O420" s="9">
-        <v>46264</v>
+        <v/>
+      </c>
+      <c t="str" r="M420" s="11">
+        <f ca="1">IF(AND(TRIM($A420)="Finalized",$K420&lt;&gt;""),"",IF($C420="","",$C420+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N420" s="11">
+        <f ca="1">IF(AND(TRIM($A420)="Finalized",$K420&lt;&gt;""),"",IF($C420="","",$C420+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O420" s="9">
+        <f>IF(AND(TRIM($A420)="Finalized",$K420&lt;&gt;""),"",DATE(2026,8,30))</f>
+        <v/>
       </c>
       <c r="P420" s="8" t="s">
         <v>86</v>
@@ -62197,20 +62574,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D421,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D421,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46272</v>
       </c>
-      <c r="L421" s="11">
+      <c t="str" r="L421" s="11">
         <f ca="1">IF($O421="","",$O421-TODAY())</f>
-        <v>-39</v>
-      </c>
-      <c r="M421" s="11">
-        <f ca="1">IF($C421="","",$C421+365-TODAY())</f>
-        <v>273</v>
-      </c>
-      <c r="N421" s="11">
-        <f ca="1">IF($C421="","",$C421+365-TODAY())</f>
-        <v>273</v>
-      </c>
-      <c r="O421" s="9">
-        <v>46265</v>
+        <v/>
+      </c>
+      <c t="str" r="M421" s="11">
+        <f ca="1">IF(AND(TRIM($A421)="Finalized",$K421&lt;&gt;""),"",IF($C421="","",$C421+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N421" s="11">
+        <f ca="1">IF(AND(TRIM($A421)="Finalized",$K421&lt;&gt;""),"",IF($C421="","",$C421+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O421" s="9">
+        <f>IF(AND(TRIM($A421)="Finalized",$K421&lt;&gt;""),"",DATE(2026,8,31))</f>
+        <v/>
       </c>
       <c r="P421" s="8" t="s">
         <v>86</v>
@@ -62319,17 +62697,18 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D422,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D422,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46248</v>
       </c>
-      <c r="L422" s="11">
+      <c t="str" r="L422" s="11">
         <f ca="1">IF($O422="","",$O422-TODAY())</f>
-        <v>-38</v>
+        <v/>
       </c>
       <c r="M422" s="11"/>
-      <c r="N422" s="11">
-        <f ca="1">IF($C422="","",$C422+65-TODAY())</f>
-        <v>-16</v>
-      </c>
-      <c r="O422" s="9">
-        <v>46266</v>
+      <c t="str" r="N422" s="11">
+        <f ca="1">IF(AND(TRIM($A422)="Finalized",$K422&lt;&gt;""),"",IF($C422="","",$C422+65-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O422" s="9">
+        <f>IF(AND(TRIM($A422)="Finalized",$K422&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P422" s="8" t="s">
         <v>208</v>
@@ -62432,20 +62811,21 @@
         <f>IFERROR(IF(INDEX([5]GAE!$K$2:$K$7,MATCH($D423,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$K$2:$K$7,MATCH($D423,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>46248</v>
       </c>
-      <c r="L423" s="11">
+      <c t="str" r="L423" s="11">
         <f ca="1">IF($O423="","",$O423-TODAY())</f>
-        <v>-38</v>
-      </c>
-      <c r="M423" s="11">
-        <f ca="1">IF($C423="","",$C423+180-TODAY())</f>
-        <v>71</v>
-      </c>
-      <c r="N423" s="11">
-        <f ca="1">IF($C423="","",$C423+180-TODAY())</f>
-        <v>71</v>
-      </c>
-      <c r="O423" s="9">
-        <v>46266</v>
+        <v/>
+      </c>
+      <c t="str" r="M423" s="11">
+        <f ca="1">IF(AND(TRIM($A423)="Finalized",$K423&lt;&gt;""),"",IF($C423="","",$C423+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N423" s="11">
+        <f ca="1">IF(AND(TRIM($A423)="Finalized",$K423&lt;&gt;""),"",IF($C423="","",$C423+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O423" s="9">
+        <f>IF(AND(TRIM($A423)="Finalized",$K423&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P423" s="8" t="s">
         <v>208</v>
@@ -62556,20 +62936,21 @@
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D424,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D424,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46284</v>
       </c>
-      <c r="L424" s="11">
+      <c t="str" r="L424" s="11">
         <f ca="1">IF($O424="","",$O424-TODAY())</f>
-        <v>-38</v>
-      </c>
-      <c r="M424" s="11">
-        <f ca="1">IF($C424="","",$C424+180-TODAY())</f>
-        <v>149</v>
-      </c>
-      <c r="N424" s="11">
-        <f ca="1">IF($C424="","",$C424+365-TODAY())</f>
-        <v>334</v>
-      </c>
-      <c r="O424" s="9">
-        <v>46266</v>
+        <v/>
+      </c>
+      <c t="str" r="M424" s="11">
+        <f ca="1">IF(AND(TRIM($A424)="Finalized",$K424&lt;&gt;""),"",IF($C424="","",$C424+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N424" s="11">
+        <f ca="1">IF(AND(TRIM($A424)="Finalized",$K424&lt;&gt;""),"",IF($C424="","",$C424+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O424" s="9">
+        <f>IF(AND(TRIM($A424)="Finalized",$K424&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P424" s="8" t="s">
         <v>86</v>
@@ -62678,20 +63059,21 @@
         <f>IFERROR(IF(INDEX([5]US!$K$2:$K$19,MATCH($D425,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$K$2:$K$19,MATCH($D425,[5]US!$D$2:$D$19,0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="L425" s="11">
+      <c t="str" r="L425" s="11">
         <f ca="1">IF($O425="","",$O425-TODAY())</f>
-        <v>-37</v>
-      </c>
-      <c r="M425" s="11">
-        <f ca="1">IF($C425="","",$C425+180-TODAY())</f>
-        <v>61</v>
-      </c>
-      <c r="N425" s="11">
-        <f ca="1">IF($C425="","",$C425+180-TODAY())</f>
-        <v>61</v>
-      </c>
-      <c r="O425" s="9">
-        <v>46267</v>
+        <v/>
+      </c>
+      <c t="str" r="M425" s="11">
+        <f ca="1">IF(AND(TRIM($A425)="Finalized",$K425&lt;&gt;""),"",IF($C425="","",$C425+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N425" s="11">
+        <f ca="1">IF(AND(TRIM($A425)="Finalized",$K425&lt;&gt;""),"",IF($C425="","",$C425+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O425" s="9">
+        <f>IF(AND(TRIM($A425)="Finalized",$K425&lt;&gt;""),"",DATE(2026,9,2))</f>
+        <v/>
       </c>
       <c r="P425" s="8" t="s">
         <v>208</v>
@@ -62796,20 +63178,21 @@
         <f>IFERROR(IF(INDEX([6]BH!$K$2:$K$82,MATCH($D426,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$K$2:$K$82,MATCH($D426,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>46284</v>
       </c>
-      <c r="L426" s="11">
+      <c t="str" r="L426" s="11">
         <f ca="1">IF($O426="","",$O426-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="M426" s="11">
-        <f ca="1">IF($F426="","",$F426+90-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="N426" s="11">
-        <f ca="1">IF($C426="","",$C426+540-TODAY())</f>
-        <v>461</v>
-      </c>
-      <c r="O426" s="9">
-        <v>46268</v>
+        <v/>
+      </c>
+      <c t="str" r="M426" s="11">
+        <f ca="1">IF(AND(TRIM($A426)="Finalized",$K426&lt;&gt;""),"",IF($F426="","",$F426+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N426" s="11">
+        <f ca="1">IF(AND(TRIM($A426)="Finalized",$K426&lt;&gt;""),"",IF($C426="","",$C426+540-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O426" s="9">
+        <f>IF(AND(TRIM($A426)="Finalized",$K426&lt;&gt;""),"",DATE(2026,9,3))</f>
+        <v/>
       </c>
       <c r="P426" s="8" t="s">
         <v>86</v>
@@ -62916,20 +63299,21 @@
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D427,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D427,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46288</v>
       </c>
-      <c r="L427" s="11">
+      <c t="str" r="L427" s="11">
         <f ca="1">IF($O427="","",$O427-TODAY())</f>
-        <v>-32</v>
-      </c>
-      <c r="M427" s="11">
-        <f ca="1">IF($C427="","",$C427+365-TODAY())</f>
-        <v>339</v>
-      </c>
-      <c r="N427" s="11">
-        <f ca="1">IF($C427="","",$C427+365-TODAY())</f>
-        <v>339</v>
-      </c>
-      <c r="O427" s="9">
-        <v>46272</v>
+        <v/>
+      </c>
+      <c t="str" r="M427" s="11">
+        <f ca="1">IF(AND(TRIM($A427)="Finalized",$K427&lt;&gt;""),"",IF($C427="","",$C427+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N427" s="11">
+        <f ca="1">IF(AND(TRIM($A427)="Finalized",$K427&lt;&gt;""),"",IF($C427="","",$C427+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O427" s="9">
+        <f>IF(AND(TRIM($A427)="Finalized",$K427&lt;&gt;""),"",DATE(2026,9,7))</f>
+        <v/>
       </c>
       <c r="P427" s="8" t="s">
         <v>86</v>
@@ -63034,20 +63418,21 @@
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D428,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D428,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>46250</v>
       </c>
-      <c r="L428" s="11">
+      <c t="str" r="L428" s="11">
         <f ca="1">IF($O428="","",$O428-TODAY())</f>
-        <v>-31</v>
-      </c>
-      <c r="M428" s="11">
-        <f ca="1">IF($C428="","",$C428+180-TODAY())</f>
-        <v>40</v>
-      </c>
-      <c r="N428" s="11">
-        <f ca="1">IF($C428="","",$C428+180-TODAY())</f>
-        <v>40</v>
-      </c>
-      <c r="O428" s="9">
-        <v>46273</v>
+        <v/>
+      </c>
+      <c t="str" r="M428" s="11">
+        <f ca="1">IF(AND(TRIM($A428)="Finalized",$K428&lt;&gt;""),"",IF($C428="","",$C428+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N428" s="11">
+        <f ca="1">IF(AND(TRIM($A428)="Finalized",$K428&lt;&gt;""),"",IF($C428="","",$C428+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O428" s="9">
+        <f>IF(AND(TRIM($A428)="Finalized",$K428&lt;&gt;""),"",DATE(2026,9,8))</f>
+        <v/>
       </c>
       <c r="P428" s="8" t="s">
         <v>208</v>
@@ -63160,20 +63545,21 @@
         <f>IFERROR(IF(INDEX([6]ORTHO!$K$2:$K$39,MATCH($D429,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$K$2:$K$39,MATCH($D429,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>46271</v>
       </c>
-      <c r="L429" s="11">
+      <c t="str" r="L429" s="11">
         <f ca="1">IF($O429="","",$O429-TODAY())</f>
-        <v>-30</v>
-      </c>
-      <c r="M429" s="11">
-        <f ca="1">IF($F429="","",$F429+90-TODAY())</f>
-        <v>-30</v>
-      </c>
-      <c r="N429" s="11">
-        <f ca="1">IF($C429="","",$C429+365-TODAY())</f>
-        <v>257</v>
-      </c>
-      <c r="O429" s="9">
-        <v>46274</v>
+        <v/>
+      </c>
+      <c t="str" r="M429" s="11">
+        <f ca="1">IF(AND(TRIM($A429)="Finalized",$K429&lt;&gt;""),"",IF($F429="","",$F429+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N429" s="11">
+        <f ca="1">IF(AND(TRIM($A429)="Finalized",$K429&lt;&gt;""),"",IF($C429="","",$C429+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O429" s="9">
+        <f>IF(AND(TRIM($A429)="Finalized",$K429&lt;&gt;""),"",DATE(2026,9,9))</f>
+        <v/>
       </c>
       <c r="P429" s="8" t="s">
         <v>86</v>
@@ -63282,20 +63668,21 @@
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D430,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D430,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>46250</v>
       </c>
-      <c r="L430" s="11">
+      <c t="str" r="L430" s="11">
         <f ca="1">IF($O430="","",$O430-TODAY())</f>
-        <v>-28</v>
-      </c>
-      <c r="M430" s="11">
-        <f ca="1">IF($C430="","",$C430+180-TODAY())</f>
-        <v>47</v>
-      </c>
-      <c r="N430" s="11">
-        <f ca="1">IF($C430="","",$C430+180-TODAY())</f>
-        <v>47</v>
-      </c>
-      <c r="O430" s="9">
-        <v>46276</v>
+        <v/>
+      </c>
+      <c t="str" r="M430" s="11">
+        <f ca="1">IF(AND(TRIM($A430)="Finalized",$K430&lt;&gt;""),"",IF($C430="","",$C430+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N430" s="11">
+        <f ca="1">IF(AND(TRIM($A430)="Finalized",$K430&lt;&gt;""),"",IF($C430="","",$C430+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O430" s="9">
+        <f>IF(AND(TRIM($A430)="Finalized",$K430&lt;&gt;""),"",DATE(2026,9,11))</f>
+        <v/>
       </c>
       <c r="P430" s="8" t="s">
         <v>208</v>
@@ -63400,20 +63787,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D431,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D431,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46245</v>
       </c>
-      <c r="L431" s="11">
+      <c t="str" r="L431" s="11">
         <f ca="1">IF($O431="","",$O431-TODAY())</f>
-        <v>-26</v>
-      </c>
-      <c r="M431" s="11">
-        <f ca="1">IF($F431="","",$F431+180-TODAY())</f>
-        <v>-26</v>
-      </c>
-      <c r="N431" s="11">
-        <f ca="1">IF($C431="","",$C431+180-TODAY())</f>
-        <v>2</v>
-      </c>
-      <c r="O431" s="9">
-        <v>46278</v>
+        <v/>
+      </c>
+      <c t="str" r="M431" s="11">
+        <f ca="1">IF(AND(TRIM($A431)="Finalized",$K431&lt;&gt;""),"",IF($F431="","",$F431+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N431" s="11">
+        <f ca="1">IF(AND(TRIM($A431)="Finalized",$K431&lt;&gt;""),"",IF($C431="","",$C431+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O431" s="9">
+        <f>IF(AND(TRIM($A431)="Finalized",$K431&lt;&gt;""),"",DATE(2026,9,13))</f>
+        <v/>
       </c>
       <c r="P431" s="8" t="s">
         <v>117</v>
@@ -63518,20 +63906,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D432,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D432,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46272</v>
       </c>
-      <c r="L432" s="11">
+      <c t="str" r="L432" s="11">
         <f ca="1">IF($O432="","",$O432-TODAY())</f>
-        <v>-25</v>
-      </c>
-      <c r="M432" s="11">
-        <f ca="1">IF($C432="","",$C432+180-TODAY())</f>
-        <v>78</v>
-      </c>
-      <c r="N432" s="11">
-        <f ca="1">IF($C432="","",$C432+365-TODAY())</f>
-        <v>263</v>
-      </c>
-      <c r="O432" s="9">
-        <v>46279</v>
+        <v/>
+      </c>
+      <c t="str" r="M432" s="11">
+        <f ca="1">IF(AND(TRIM($A432)="Finalized",$K432&lt;&gt;""),"",IF($C432="","",$C432+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N432" s="11">
+        <f ca="1">IF(AND(TRIM($A432)="Finalized",$K432&lt;&gt;""),"",IF($C432="","",$C432+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O432" s="9">
+        <f>IF(AND(TRIM($A432)="Finalized",$K432&lt;&gt;""),"",DATE(2026,9,14))</f>
+        <v/>
       </c>
       <c r="P432" s="8" t="s">
         <v>86</v>
@@ -63638,20 +64027,21 @@
         <f>IFERROR(IF(INDEX([6]BH!$K$2:$K$82,MATCH($D433,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$K$2:$K$82,MATCH($D433,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>46293</v>
       </c>
-      <c r="L433" s="11">
+      <c t="str" r="L433" s="11">
         <f ca="1">IF($O433="","",$O433-TODAY())</f>
-        <v>-24</v>
-      </c>
-      <c r="M433" s="11">
-        <f ca="1">IF($C433="","",$C433+365-TODAY())</f>
-        <v>343</v>
-      </c>
-      <c r="N433" s="11">
-        <f ca="1">IF($C433="","",$C433+365-TODAY())</f>
-        <v>343</v>
-      </c>
-      <c r="O433" s="9">
-        <v>46280</v>
+        <v/>
+      </c>
+      <c t="str" r="M433" s="11">
+        <f ca="1">IF(AND(TRIM($A433)="Finalized",$K433&lt;&gt;""),"",IF($C433="","",$C433+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N433" s="11">
+        <f ca="1">IF(AND(TRIM($A433)="Finalized",$K433&lt;&gt;""),"",IF($C433="","",$C433+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O433" s="9">
+        <f>IF(AND(TRIM($A433)="Finalized",$K433&lt;&gt;""),"",DATE(2026,9,15))</f>
+        <v/>
       </c>
       <c r="P433" s="8" t="s">
         <v>86</v>
@@ -63756,20 +64146,21 @@
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D434,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D434,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46282</v>
       </c>
-      <c r="L434" s="11">
+      <c t="str" r="L434" s="11">
         <f ca="1">IF($O434="","",$O434-TODAY())</f>
-        <v>-24</v>
-      </c>
-      <c r="M434" s="11">
-        <f ca="1">IF($F434="","",$F434+90-TODAY())</f>
-        <v>-24</v>
-      </c>
-      <c r="N434" s="11">
-        <f ca="1">IF($C434="","",$C434+180-TODAY())</f>
-        <v>78</v>
-      </c>
-      <c r="O434" s="9">
-        <v>46280</v>
+        <v/>
+      </c>
+      <c t="str" r="M434" s="11">
+        <f ca="1">IF(AND(TRIM($A434)="Finalized",$K434&lt;&gt;""),"",IF($F434="","",$F434+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N434" s="11">
+        <f ca="1">IF(AND(TRIM($A434)="Finalized",$K434&lt;&gt;""),"",IF($C434="","",$C434+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O434" s="9">
+        <f>IF(AND(TRIM($A434)="Finalized",$K434&lt;&gt;""),"",DATE(2026,9,15))</f>
+        <v/>
       </c>
       <c r="P434" s="8" t="s">
         <v>86</v>
@@ -63876,20 +64267,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D435,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D435,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46282</v>
       </c>
-      <c r="L435" s="11">
+      <c t="str" r="L435" s="11">
         <f ca="1">IF($O435="","",$O435-TODAY())</f>
-        <v>-23</v>
-      </c>
-      <c r="M435" s="11">
-        <f ca="1">IF($F435="","",$F435+90-TODAY())</f>
-        <v>-23</v>
-      </c>
-      <c r="N435" s="11">
-        <f ca="1">IF($C435="","",$C435+365-TODAY())</f>
-        <v>264</v>
-      </c>
-      <c r="O435" s="9">
-        <v>46281</v>
+        <v/>
+      </c>
+      <c t="str" r="M435" s="11">
+        <f ca="1">IF(AND(TRIM($A435)="Finalized",$K435&lt;&gt;""),"",IF($F435="","",$F435+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N435" s="11">
+        <f ca="1">IF(AND(TRIM($A435)="Finalized",$K435&lt;&gt;""),"",IF($C435="","",$C435+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O435" s="9">
+        <f>IF(AND(TRIM($A435)="Finalized",$K435&lt;&gt;""),"",DATE(2026,9,16))</f>
+        <v/>
       </c>
       <c r="P435" s="8" t="s">
         <v>86</v>
@@ -63994,20 +64386,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D436,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D436,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46282</v>
       </c>
-      <c r="L436" s="11">
+      <c t="str" r="L436" s="11">
         <f ca="1">IF($O436="","",$O436-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M436" s="11">
-        <f ca="1">IF($C436="","",$C436+180-TODAY())</f>
-        <v>80</v>
-      </c>
-      <c r="N436" s="11">
-        <f ca="1">IF($C436="","",$C436+365-TODAY())</f>
-        <v>265</v>
-      </c>
-      <c r="O436" s="9">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M436" s="11">
+        <f ca="1">IF(AND(TRIM($A436)="Finalized",$K436&lt;&gt;""),"",IF($C436="","",$C436+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N436" s="11">
+        <f ca="1">IF(AND(TRIM($A436)="Finalized",$K436&lt;&gt;""),"",IF($C436="","",$C436+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O436" s="9">
+        <f>IF(AND(TRIM($A436)="Finalized",$K436&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P436" s="8" t="s">
         <v>86</v>
@@ -64116,20 +64509,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D437,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D437,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46282</v>
       </c>
-      <c r="L437" s="11">
+      <c t="str" r="L437" s="11">
         <f ca="1">IF($O437="","",$O437-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M437" s="11">
-        <f ca="1">IF($C437="","",$C437+365-TODAY())</f>
-        <v>283</v>
-      </c>
-      <c r="N437" s="11">
-        <f ca="1">IF($C437="","",$C437+365-TODAY())</f>
-        <v>283</v>
-      </c>
-      <c r="O437" s="9">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M437" s="11">
+        <f ca="1">IF(AND(TRIM($A437)="Finalized",$K437&lt;&gt;""),"",IF($C437="","",$C437+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N437" s="11">
+        <f ca="1">IF(AND(TRIM($A437)="Finalized",$K437&lt;&gt;""),"",IF($C437="","",$C437+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O437" s="9">
+        <f>IF(AND(TRIM($A437)="Finalized",$K437&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P437" s="8" t="s">
         <v>86</v>
@@ -64238,20 +64632,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D438,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D438,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46282</v>
       </c>
-      <c r="L438" s="11">
+      <c t="str" r="L438" s="11">
         <f ca="1">IF($O438="","",$O438-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M438" s="11">
-        <f ca="1">IF($F438="","",$F438+90-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="N438" s="11">
-        <f ca="1">IF($C438="","",$C438+365-TODAY())</f>
-        <v>271</v>
-      </c>
-      <c r="O438" s="9">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M438" s="11">
+        <f ca="1">IF(AND(TRIM($A438)="Finalized",$K438&lt;&gt;""),"",IF($F438="","",$F438+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N438" s="11">
+        <f ca="1">IF(AND(TRIM($A438)="Finalized",$K438&lt;&gt;""),"",IF($C438="","",$C438+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O438" s="9">
+        <f>IF(AND(TRIM($A438)="Finalized",$K438&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P438" s="8" t="s">
         <v>86</v>
@@ -64358,20 +64753,21 @@
         <f>IFERROR(IF(INDEX([6]BH!$K$2:$K$82,MATCH($D439,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$K$2:$K$82,MATCH($D439,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>46283</v>
       </c>
-      <c r="L439" s="11">
+      <c t="str" r="L439" s="11">
         <f ca="1">IF($O439="","",$O439-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M439" s="11">
-        <f ca="1">IF($F439="","",$F439+90-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="N439" s="11">
-        <f ca="1">IF($C439="","",$C439+365-TODAY())</f>
-        <v>299</v>
-      </c>
-      <c r="O439" s="9">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M439" s="11">
+        <f ca="1">IF(AND(TRIM($A439)="Finalized",$K439&lt;&gt;""),"",IF($F439="","",$F439+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N439" s="11">
+        <f ca="1">IF(AND(TRIM($A439)="Finalized",$K439&lt;&gt;""),"",IF($C439="","",$C439+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O439" s="9">
+        <f>IF(AND(TRIM($A439)="Finalized",$K439&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P439" s="8" t="s">
         <v>86</v>
@@ -64476,20 +64872,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D440,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D440,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46243</v>
       </c>
-      <c r="L440" s="11">
+      <c t="str" r="L440" s="11">
         <f ca="1">IF($O440="","",$O440-TODAY())</f>
-        <v>-16</v>
-      </c>
-      <c r="M440" s="11">
-        <f ca="1">IF($F440="","",$F440+90-TODAY())</f>
-        <v>-16</v>
-      </c>
-      <c r="N440" s="11">
-        <f ca="1">IF($C440="","",$C440+365-TODAY())</f>
-        <v>304</v>
-      </c>
-      <c r="O440" s="9">
-        <v>46288</v>
+        <v/>
+      </c>
+      <c t="str" r="M440" s="11">
+        <f ca="1">IF(AND(TRIM($A440)="Finalized",$K440&lt;&gt;""),"",IF($F440="","",$F440+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N440" s="11">
+        <f ca="1">IF(AND(TRIM($A440)="Finalized",$K440&lt;&gt;""),"",IF($C440="","",$C440+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O440" s="9">
+        <f>IF(AND(TRIM($A440)="Finalized",$K440&lt;&gt;""),"",DATE(2026,9,23))</f>
+        <v/>
       </c>
       <c r="P440" s="8" t="s">
         <v>86</v>
@@ -64596,20 +64993,21 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D441,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D441,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46276</v>
       </c>
-      <c r="L441" s="11">
+      <c t="str" r="L441" s="11">
         <f ca="1">IF($O441="","",$O441-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M441" s="11">
-        <f ca="1">IF($C441="","",$C441+180-TODAY())</f>
-        <v>128</v>
-      </c>
-      <c r="N441" s="11">
-        <f ca="1">IF($C441="","",$C441+180-TODAY())</f>
-        <v>128</v>
-      </c>
-      <c r="O441" s="9">
-        <v>46289</v>
+        <v/>
+      </c>
+      <c t="str" r="M441" s="11">
+        <f ca="1">IF(AND(TRIM($A441)="Finalized",$K441&lt;&gt;""),"",IF($C441="","",$C441+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N441" s="11">
+        <f ca="1">IF(AND(TRIM($A441)="Finalized",$K441&lt;&gt;""),"",IF($C441="","",$C441+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O441" s="9">
+        <f>IF(AND(TRIM($A441)="Finalized",$K441&lt;&gt;""),"",DATE(2026,9,24))</f>
+        <v/>
       </c>
       <c r="P441" s="8" t="s">
         <v>208</v>
@@ -64720,20 +65118,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D442,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D442,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46283</v>
       </c>
-      <c r="L442" s="11">
+      <c t="str" r="L442" s="11">
         <f ca="1">IF($O442="","",$O442-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="M442" s="11">
-        <f ca="1">IF($C442="","",$C442+180-TODAY())</f>
-        <v>86</v>
-      </c>
-      <c r="N442" s="11">
-        <f ca="1">IF($C442="","",$C442+365-TODAY())</f>
-        <v>271</v>
-      </c>
-      <c r="O442" s="9">
-        <v>46292</v>
+        <v/>
+      </c>
+      <c t="str" r="M442" s="11">
+        <f ca="1">IF(AND(TRIM($A442)="Finalized",$K442&lt;&gt;""),"",IF($C442="","",$C442+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N442" s="11">
+        <f ca="1">IF(AND(TRIM($A442)="Finalized",$K442&lt;&gt;""),"",IF($C442="","",$C442+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O442" s="9">
+        <f>IF(AND(TRIM($A442)="Finalized",$K442&lt;&gt;""),"",DATE(2026,9,27))</f>
+        <v/>
       </c>
       <c r="P442" s="8" t="s">
         <v>86</v>
@@ -64838,20 +65237,21 @@
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$51,MATCH($D443,[6]DME!$D$2:$D$51,0))="","",INDEX([6]DME!$K$2:$K$51,MATCH($D443,[6]DME!$D$2:$D$51,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L443" s="11">
+      <c t="str" r="L443" s="11">
         <f ca="1">IF($O443="","",$O443-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="M443" s="11">
-        <f ca="1">IF($C443="","",$C443+180-TODAY())</f>
-        <v>165</v>
-      </c>
-      <c r="N443" s="11">
-        <f ca="1">IF($C443="","",$C443+365-TODAY())</f>
-        <v>350</v>
-      </c>
-      <c r="O443" s="9">
-        <v>46292</v>
+        <v/>
+      </c>
+      <c t="str" r="M443" s="11">
+        <f ca="1">IF(AND(TRIM($A443)="Finalized",$K443&lt;&gt;""),"",IF($C443="","",$C443+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N443" s="11">
+        <f ca="1">IF(AND(TRIM($A443)="Finalized",$K443&lt;&gt;""),"",IF($C443="","",$C443+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O443" s="9">
+        <f>IF(AND(TRIM($A443)="Finalized",$K443&lt;&gt;""),"",DATE(2026,9,27))</f>
+        <v/>
       </c>
       <c r="P443" s="8" t="s">
         <v>86</v>
@@ -64956,20 +65356,21 @@
         <f>IFERROR(IF(INDEX([6]BH!$K$2:$K$82,MATCH($D444,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$K$2:$K$82,MATCH($D444,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L444" s="11">
+      <c t="str" r="L444" s="11">
         <f ca="1">IF($O444="","",$O444-TODAY())</f>
-        <v>-8</v>
-      </c>
-      <c r="M444" s="11">
-        <f ca="1">IF($C444="","",$C444+365-TODAY())</f>
-        <v>326</v>
-      </c>
-      <c r="N444" s="11">
-        <f ca="1">IF($C444="","",$C444+90-TODAY())</f>
-        <v>51</v>
-      </c>
-      <c r="O444" s="9">
-        <v>46296</v>
+        <v/>
+      </c>
+      <c t="str" r="M444" s="11">
+        <f ca="1">IF(AND(TRIM($A444)="Finalized",$K444&lt;&gt;""),"",IF($C444="","",$C444+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N444" s="11">
+        <f ca="1">IF(AND(TRIM($A444)="Finalized",$K444&lt;&gt;""),"",IF($C444="","",$C444+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O444" s="9">
+        <f>IF(AND(TRIM($A444)="Finalized",$K444&lt;&gt;""),"",DATE(2026,10,1))</f>
+        <v/>
       </c>
       <c r="P444" s="8" t="s">
         <v>208</v>
@@ -65072,20 +65473,21 @@
         <f>IFERROR(IF(INDEX([6]GAE!$K$2:$K$23,MATCH($D445,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$K$2:$K$23,MATCH($D445,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L445" s="11">
+      <c t="str" r="L445" s="11">
         <f ca="1">IF($O445="","",$O445-TODAY())</f>
-        <v>-3</v>
-      </c>
-      <c r="M445" s="11">
-        <f ca="1">IF($C445="","",$C445+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="N445" s="11">
-        <f ca="1">IF($C445="","",$C445+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="O445" s="9">
-        <v>46301</v>
+        <v/>
+      </c>
+      <c t="str" r="M445" s="11">
+        <f ca="1">IF(AND(TRIM($A445)="Finalized",$K445&lt;&gt;""),"",IF($C445="","",$C445+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N445" s="11">
+        <f ca="1">IF(AND(TRIM($A445)="Finalized",$K445&lt;&gt;""),"",IF($C445="","",$C445+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O445" s="9">
+        <f>IF(AND(TRIM($A445)="Finalized",$K445&lt;&gt;""),"",DATE(2026,10,6))</f>
+        <v/>
       </c>
       <c r="P445" s="8" t="s">
         <v>208</v>
@@ -65198,20 +65600,21 @@
         <f>IFERROR(IF(INDEX([6]GAE!$K$2:$K$23,MATCH($D446,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$K$2:$K$23,MATCH($D446,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L446" s="11">
+      <c t="str" r="L446" s="11">
         <f ca="1">IF($O446="","",$O446-TODAY())</f>
-        <v>4</v>
-      </c>
-      <c r="M446" s="11">
-        <f ca="1">IF($C446="","",$C446+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="N446" s="11">
-        <f ca="1">IF($C446="","",$C446+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="O446" s="9">
-        <v>46308</v>
+        <v/>
+      </c>
+      <c t="str" r="M446" s="11">
+        <f ca="1">IF(AND(TRIM($A446)="Finalized",$K446&lt;&gt;""),"",IF($C446="","",$C446+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N446" s="11">
+        <f ca="1">IF(AND(TRIM($A446)="Finalized",$K446&lt;&gt;""),"",IF($C446="","",$C446+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O446" s="9">
+        <f>IF(AND(TRIM($A446)="Finalized",$K446&lt;&gt;""),"",DATE(2026,10,13))</f>
+        <v/>
       </c>
       <c r="P446" s="8" t="s">
         <v>208</v>
@@ -65324,20 +65727,21 @@
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D447,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D447,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L447" s="11">
+      <c t="str" r="L447" s="11">
         <f ca="1">IF($O447="","",$O447-TODAY())</f>
-        <v>6</v>
-      </c>
-      <c r="M447" s="11">
-        <f ca="1">IF($C447="","",$C447+180-TODAY())</f>
-        <v>103</v>
-      </c>
-      <c r="N447" s="11">
-        <f ca="1">IF($C447="","",$C447+180-TODAY())</f>
-        <v>103</v>
-      </c>
-      <c r="O447" s="9">
-        <v>46310</v>
+        <v/>
+      </c>
+      <c t="str" r="M447" s="11">
+        <f ca="1">IF(AND(TRIM($A447)="Finalized",$K447&lt;&gt;""),"",IF($C447="","",$C447+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N447" s="11">
+        <f ca="1">IF(AND(TRIM($A447)="Finalized",$K447&lt;&gt;""),"",IF($C447="","",$C447+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O447" s="9">
+        <f>IF(AND(TRIM($A447)="Finalized",$K447&lt;&gt;""),"",DATE(2026,10,15))</f>
+        <v/>
       </c>
       <c r="P447" s="8" t="s">
         <v>208</v>
@@ -65442,20 +65846,21 @@
         <f>IFERROR(IF(INDEX([4]GAE!$K$2:$K$8,MATCH($D448,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$K$2:$K$8,MATCH($D448,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>46278</v>
       </c>
-      <c r="L448" s="11">
+      <c t="str" r="L448" s="11">
         <f ca="1">IF($O448="","",$O448-TODAY())</f>
-        <v>8</v>
-      </c>
-      <c r="M448" s="11">
-        <f ca="1">IF($F448="","",$F448+365-TODAY())</f>
-        <v>193</v>
-      </c>
-      <c r="N448" s="11">
-        <f ca="1">IF($F448="","",$F448+365-TODAY())</f>
-        <v>193</v>
-      </c>
-      <c r="O448" s="9">
-        <v>46312</v>
+        <v/>
+      </c>
+      <c t="str" r="M448" s="11">
+        <f ca="1">IF(AND(TRIM($A448)="Finalized",$K448&lt;&gt;""),"",IF($F448="","",$F448+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N448" s="11">
+        <f ca="1">IF(AND(TRIM($A448)="Finalized",$K448&lt;&gt;""),"",IF($F448="","",$F448+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O448" s="9">
+        <f>IF(AND(TRIM($A448)="Finalized",$K448&lt;&gt;""),"",DATE(2026,10,17))</f>
+        <v/>
       </c>
       <c r="P448" s="8" t="s">
         <v>117</v>
@@ -65570,20 +65975,21 @@
         <f>IFERROR(IF(INDEX([6]ORTHO!$K$2:$K$39,MATCH($D449,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$K$2:$K$39,MATCH($D449,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L449" s="11">
+      <c t="str" r="L449" s="11">
         <f ca="1">IF($O449="","",$O449-TODAY())</f>
-        <v>9</v>
-      </c>
-      <c r="M449" s="11">
-        <f ca="1">IF($C449="","",$C449+180-TODAY())</f>
-        <v>93</v>
-      </c>
-      <c r="N449" s="11">
-        <f ca="1">IF($C449="","",$C449+180-TODAY())</f>
-        <v>93</v>
-      </c>
-      <c r="O449" s="9">
-        <v>46313</v>
+        <v/>
+      </c>
+      <c t="str" r="M449" s="11">
+        <f ca="1">IF(AND(TRIM($A449)="Finalized",$K449&lt;&gt;""),"",IF($C449="","",$C449+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N449" s="11">
+        <f ca="1">IF(AND(TRIM($A449)="Finalized",$K449&lt;&gt;""),"",IF($C449="","",$C449+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O449" s="9">
+        <f>IF(AND(TRIM($A449)="Finalized",$K449&lt;&gt;""),"",DATE(2026,10,18))</f>
+        <v/>
       </c>
       <c r="P449" s="8" t="s">
         <v>208</v>
@@ -65690,20 +66096,21 @@
         <f>IFERROR(IF(INDEX([6]GAE!$K$2:$K$23,MATCH($D450,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$K$2:$K$23,MATCH($D450,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L450" s="11">
+      <c t="str" r="L450" s="11">
         <f ca="1">IF($O450="","",$O450-TODAY())</f>
-        <v>18</v>
-      </c>
-      <c r="M450" s="11">
-        <f ca="1">IF($C450="","",$C450+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="N450" s="11">
-        <f ca="1">IF($C450="","",$C450+180-TODAY())</f>
-        <v>114</v>
-      </c>
-      <c r="O450" s="9">
-        <v>46322</v>
+        <v/>
+      </c>
+      <c t="str" r="M450" s="11">
+        <f ca="1">IF(AND(TRIM($A450)="Finalized",$K450&lt;&gt;""),"",IF($C450="","",$C450+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N450" s="11">
+        <f ca="1">IF(AND(TRIM($A450)="Finalized",$K450&lt;&gt;""),"",IF($C450="","",$C450+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O450" s="9">
+        <f>IF(AND(TRIM($A450)="Finalized",$K450&lt;&gt;""),"",DATE(2026,10,27))</f>
+        <v/>
       </c>
       <c r="P450" s="8" t="s">
         <v>208</v>
@@ -65816,20 +66223,21 @@
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D451,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D451,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="L451" s="11">
+      <c t="str" r="L451" s="11">
         <f ca="1">IF($O451="","",$O451-TODAY())</f>
-        <v>32</v>
-      </c>
-      <c r="M451" s="11">
-        <f ca="1">IF($F451="","",$F451+180-TODAY())</f>
-        <v>32</v>
-      </c>
-      <c r="N451" s="11">
-        <f ca="1">IF($C451="","",$C451+180-TODAY())</f>
-        <v>46</v>
-      </c>
-      <c r="O451" s="9">
-        <v>46336</v>
+        <v/>
+      </c>
+      <c t="str" r="M451" s="11">
+        <f ca="1">IF(AND(TRIM($A451)="Finalized",$K451&lt;&gt;""),"",IF($F451="","",$F451+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N451" s="11">
+        <f ca="1">IF(AND(TRIM($A451)="Finalized",$K451&lt;&gt;""),"",IF($C451="","",$C451+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O451" s="9">
+        <f>IF(AND(TRIM($A451)="Finalized",$K451&lt;&gt;""),"",DATE(2026,11,10))</f>
+        <v/>
       </c>
       <c r="P451" s="8" t="s">
         <v>117</v>
@@ -65934,20 +66342,21 @@
         <f>IFERROR(IF(INDEX([1]DME!$K$2:$K$8,MATCH($D452,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$K$2:$K$8,MATCH($D452,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>46261</v>
       </c>
-      <c r="L452" s="11">
+      <c t="str" r="L452" s="11">
         <f ca="1">IF($O452="","",$O452-TODAY())</f>
-        <v>92</v>
-      </c>
-      <c r="M452" s="11">
-        <f ca="1">IF($C452="","",$C452+365-TODAY())</f>
-        <v>221</v>
-      </c>
-      <c r="N452" s="11">
-        <f ca="1">IF($C452="","",$C452+120-TODAY())</f>
-        <v>-24</v>
-      </c>
-      <c r="O452" s="9">
-        <v>46396</v>
+        <v/>
+      </c>
+      <c t="str" r="M452" s="11">
+        <f ca="1">IF(AND(TRIM($A452)="Finalized",$K452&lt;&gt;""),"",IF($C452="","",$C452+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N452" s="11">
+        <f ca="1">IF(AND(TRIM($A452)="Finalized",$K452&lt;&gt;""),"",IF($C452="","",$C452+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O452" s="9">
+        <f>IF(AND(TRIM($A452)="Finalized",$K452&lt;&gt;""),"",DATE(2027,1,9))</f>
+        <v/>
       </c>
       <c r="P452" s="8" t="s">
         <v>73</v>
@@ -66054,20 +66463,21 @@
         <f>IFERROR(IF(INDEX([1]DME!$K$2:$K$8,MATCH($D453,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$K$2:$K$8,MATCH($D453,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>46261</v>
       </c>
-      <c r="L453" s="11">
+      <c t="str" r="L453" s="11">
         <f ca="1">IF($O453="","",$O453-TODAY())</f>
-        <v>102</v>
-      </c>
-      <c r="M453" s="11">
-        <f ca="1">IF($C453="","",$C453+365-TODAY())</f>
-        <v>147</v>
-      </c>
-      <c r="N453" s="11">
-        <f ca="1">IF($C453="","",$C453+120-TODAY())</f>
-        <v>-98</v>
-      </c>
-      <c r="O453" s="9">
-        <v>46406</v>
+        <v/>
+      </c>
+      <c t="str" r="M453" s="11">
+        <f ca="1">IF(AND(TRIM($A453)="Finalized",$K453&lt;&gt;""),"",IF($C453="","",$C453+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N453" s="11">
+        <f ca="1">IF(AND(TRIM($A453)="Finalized",$K453&lt;&gt;""),"",IF($C453="","",$C453+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O453" s="9">
+        <f>IF(AND(TRIM($A453)="Finalized",$K453&lt;&gt;""),"",DATE(2027,1,19))</f>
+        <v/>
       </c>
       <c r="P453" s="8" t="s">
         <v>73</v>
@@ -66176,20 +66586,21 @@
         <f>IFERROR(IF(INDEX([1]DME!$K$2:$K$8,MATCH($D454,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$K$2:$K$8,MATCH($D454,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>46261</v>
       </c>
-      <c r="L454" s="11">
+      <c t="str" r="L454" s="11">
         <f ca="1">IF($O454="","",$O454-TODAY())</f>
-        <v>102</v>
-      </c>
-      <c r="M454" s="11">
-        <f ca="1">IF($C454="","",$C454+365-TODAY())</f>
-        <v>132</v>
-      </c>
-      <c r="N454" s="11">
-        <f ca="1">IF($C454="","",$C454+120-TODAY())</f>
-        <v>-113</v>
-      </c>
-      <c r="O454" s="9">
-        <v>46406</v>
+        <v/>
+      </c>
+      <c t="str" r="M454" s="11">
+        <f ca="1">IF(AND(TRIM($A454)="Finalized",$K454&lt;&gt;""),"",IF($C454="","",$C454+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N454" s="11">
+        <f ca="1">IF(AND(TRIM($A454)="Finalized",$K454&lt;&gt;""),"",IF($C454="","",$C454+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O454" s="9">
+        <f>IF(AND(TRIM($A454)="Finalized",$K454&lt;&gt;""),"",DATE(2027,1,19))</f>
+        <v/>
       </c>
       <c r="P454" s="8" t="s">
         <v>73</v>
@@ -66298,20 +66709,21 @@
         <f>IFERROR(IF(INDEX([2]DME!$K$2:$K$12,MATCH($D455,[2]DME!$D$2:$D$12,0))="","",INDEX([2]DME!$K$2:$K$12,MATCH($D455,[2]DME!$D$2:$D$12,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L455" s="11">
+      <c t="str" r="L455" s="11">
         <f ca="1">IF($O455="","",$O455-TODAY())</f>
-        <v>124</v>
-      </c>
-      <c r="M455" s="11">
-        <f ca="1">IF($C455="","",$C455+365-TODAY())</f>
-        <v>194</v>
-      </c>
-      <c r="N455" s="11">
-        <f ca="1">IF($C455="","",$C455+120-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="O455" s="9">
-        <v>46428</v>
+        <v/>
+      </c>
+      <c t="str" r="M455" s="11">
+        <f ca="1">IF(AND(TRIM($A455)="Finalized",$K455&lt;&gt;""),"",IF($C455="","",$C455+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N455" s="11">
+        <f ca="1">IF(AND(TRIM($A455)="Finalized",$K455&lt;&gt;""),"",IF($C455="","",$C455+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O455" s="9">
+        <f>IF(AND(TRIM($A455)="Finalized",$K455&lt;&gt;""),"",DATE(2027,2,10))</f>
+        <v/>
       </c>
       <c r="P455" s="8" t="s">
         <v>73</v>
@@ -66418,20 +66830,21 @@
         <f>IFERROR(IF(INDEX([2]DME!$K$2:$K$12,MATCH($D456,[2]DME!$D$2:$D$12,0))="","",INDEX([2]DME!$K$2:$K$12,MATCH($D456,[2]DME!$D$2:$D$12,0))),"")</f>
         <v>46246</v>
       </c>
-      <c r="L456" s="11">
+      <c t="str" r="L456" s="11">
         <f ca="1">IF($O456="","",$O456-TODAY())</f>
-        <v>130</v>
-      </c>
-      <c r="M456" s="11">
-        <f ca="1">IF($C456="","",$C456+365-TODAY())</f>
-        <v>182</v>
-      </c>
-      <c r="N456" s="11">
-        <f ca="1">IF($C456="","",$C456+120-TODAY())</f>
-        <v>-63</v>
-      </c>
-      <c r="O456" s="9">
-        <v>46434</v>
+        <v/>
+      </c>
+      <c t="str" r="M456" s="11">
+        <f ca="1">IF(AND(TRIM($A456)="Finalized",$K456&lt;&gt;""),"",IF($C456="","",$C456+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N456" s="11">
+        <f ca="1">IF(AND(TRIM($A456)="Finalized",$K456&lt;&gt;""),"",IF($C456="","",$C456+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O456" s="9">
+        <f>IF(AND(TRIM($A456)="Finalized",$K456&lt;&gt;""),"",DATE(2027,2,16))</f>
+        <v/>
       </c>
       <c r="P456" s="8" t="s">
         <v>73</v>
@@ -66542,20 +66955,21 @@
         <f>IFERROR(IF(INDEX([2]DME!$K$2:$K$12,MATCH($D457,[2]DME!$D$2:$D$12,0))="","",INDEX([2]DME!$K$2:$K$12,MATCH($D457,[2]DME!$D$2:$D$12,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L457" s="11">
+      <c t="str" r="L457" s="11">
         <f ca="1">IF($O457="","",$O457-TODAY())</f>
-        <v>132</v>
-      </c>
-      <c r="M457" s="11">
-        <f ca="1">IF($C457="","",$C457+365-TODAY())</f>
-        <v>162</v>
-      </c>
-      <c r="N457" s="11">
-        <f ca="1">IF($C457="","",$C457+120-TODAY())</f>
-        <v>-83</v>
-      </c>
-      <c r="O457" s="9">
-        <v>46436</v>
+        <v/>
+      </c>
+      <c t="str" r="M457" s="11">
+        <f ca="1">IF(AND(TRIM($A457)="Finalized",$K457&lt;&gt;""),"",IF($C457="","",$C457+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N457" s="11">
+        <f ca="1">IF(AND(TRIM($A457)="Finalized",$K457&lt;&gt;""),"",IF($C457="","",$C457+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O457" s="9">
+        <f>IF(AND(TRIM($A457)="Finalized",$K457&lt;&gt;""),"",DATE(2027,2,18))</f>
+        <v/>
       </c>
       <c r="P457" s="8" t="s">
         <v>73</v>
@@ -66662,20 +67076,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D458,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D458,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46268</v>
       </c>
-      <c r="L458" s="11">
+      <c t="str" r="L458" s="11">
         <f ca="1">IF($O458="","",$O458-TODAY())</f>
-        <v>144</v>
-      </c>
-      <c r="M458" s="11">
-        <f ca="1">IF($C458="","",$C458+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="N458" s="11">
-        <f ca="1">IF($C458="","",$C458+120-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="O458" s="9">
-        <v>46448</v>
+        <v/>
+      </c>
+      <c t="str" r="M458" s="11">
+        <f ca="1">IF(AND(TRIM($A458)="Finalized",$K458&lt;&gt;""),"",IF($C458="","",$C458+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N458" s="11">
+        <f ca="1">IF(AND(TRIM($A458)="Finalized",$K458&lt;&gt;""),"",IF($C458="","",$C458+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O458" s="9">
+        <f>IF(AND(TRIM($A458)="Finalized",$K458&lt;&gt;""),"",DATE(2027,3,2))</f>
+        <v/>
       </c>
       <c r="P458" s="8" t="s">
         <v>73</v>
@@ -66782,20 +67197,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D459,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D459,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L459" s="11">
+      <c t="str" r="L459" s="11">
         <f ca="1">IF($O459="","",$O459-TODAY())</f>
-        <v>146</v>
-      </c>
-      <c r="M459" s="11">
-        <f ca="1">IF($C459="","",$C459+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="N459" s="11">
-        <f ca="1">IF($C459="","",$C459+120-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="O459" s="9">
-        <v>46450</v>
+        <v/>
+      </c>
+      <c t="str" r="M459" s="11">
+        <f ca="1">IF(AND(TRIM($A459)="Finalized",$K459&lt;&gt;""),"",IF($C459="","",$C459+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N459" s="11">
+        <f ca="1">IF(AND(TRIM($A459)="Finalized",$K459&lt;&gt;""),"",IF($C459="","",$C459+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O459" s="9">
+        <f>IF(AND(TRIM($A459)="Finalized",$K459&lt;&gt;""),"",DATE(2027,3,4))</f>
+        <v/>
       </c>
       <c r="P459" s="8" t="s">
         <v>73</v>
@@ -66902,20 +67318,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D460,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D460,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46268</v>
       </c>
-      <c r="L460" s="11">
+      <c t="str" r="L460" s="11">
         <f ca="1">IF($O460="","",$O460-TODAY())</f>
-        <v>153</v>
-      </c>
-      <c r="M460" s="11">
-        <f ca="1">IF($C460="","",$C460+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="N460" s="11">
-        <f ca="1">IF($C460="","",$C460+120-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="O460" s="9">
-        <v>46457</v>
+        <v/>
+      </c>
+      <c t="str" r="M460" s="11">
+        <f ca="1">IF(AND(TRIM($A460)="Finalized",$K460&lt;&gt;""),"",IF($C460="","",$C460+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N460" s="11">
+        <f ca="1">IF(AND(TRIM($A460)="Finalized",$K460&lt;&gt;""),"",IF($C460="","",$C460+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O460" s="9">
+        <f>IF(AND(TRIM($A460)="Finalized",$K460&lt;&gt;""),"",DATE(2027,3,11))</f>
+        <v/>
       </c>
       <c r="P460" s="8" t="s">
         <v>73</v>
@@ -67022,20 +67439,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D461,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D461,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46268</v>
       </c>
-      <c r="L461" s="11">
+      <c t="str" r="L461" s="11">
         <f ca="1">IF($O461="","",$O461-TODAY())</f>
-        <v>155</v>
-      </c>
-      <c r="M461" s="11">
-        <f ca="1">IF($C461="","",$C461+365-TODAY())</f>
-        <v>202</v>
-      </c>
-      <c r="N461" s="11">
-        <f ca="1">IF($C461="","",$C461+120-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="O461" s="9">
-        <v>46459</v>
+        <v/>
+      </c>
+      <c t="str" r="M461" s="11">
+        <f ca="1">IF(AND(TRIM($A461)="Finalized",$K461&lt;&gt;""),"",IF($C461="","",$C461+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N461" s="11">
+        <f ca="1">IF(AND(TRIM($A461)="Finalized",$K461&lt;&gt;""),"",IF($C461="","",$C461+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O461" s="9">
+        <f>IF(AND(TRIM($A461)="Finalized",$K461&lt;&gt;""),"",DATE(2027,3,13))</f>
+        <v/>
       </c>
       <c r="P461" s="8" t="s">
         <v>73</v>
@@ -67142,20 +67560,21 @@
         <f>IFERROR(IF(INDEX([3]BH!$K$2:$K$32,MATCH($D462,[3]BH!$D$2:$D$32,0))="","",INDEX([3]BH!$K$2:$K$32,MATCH($D462,[3]BH!$D$2:$D$32,0))),"")</f>
         <v>46268</v>
       </c>
-      <c r="L462" s="11">
+      <c t="str" r="L462" s="11">
         <f ca="1">IF($O462="","",$O462-TODAY())</f>
-        <v>155</v>
-      </c>
-      <c r="M462" s="11">
-        <f ca="1">IF($C462="","",$C462+365-TODAY())</f>
-        <v>271</v>
-      </c>
-      <c r="N462" s="11">
-        <f ca="1">IF($C462="","",$C462+120-TODAY())</f>
-        <v>26</v>
-      </c>
-      <c r="O462" s="9">
-        <v>46459</v>
+        <v/>
+      </c>
+      <c t="str" r="M462" s="11">
+        <f ca="1">IF(AND(TRIM($A462)="Finalized",$K462&lt;&gt;""),"",IF($C462="","",$C462+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N462" s="11">
+        <f ca="1">IF(AND(TRIM($A462)="Finalized",$K462&lt;&gt;""),"",IF($C462="","",$C462+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O462" s="9">
+        <f>IF(AND(TRIM($A462)="Finalized",$K462&lt;&gt;""),"",DATE(2027,3,13))</f>
+        <v/>
       </c>
       <c r="P462" s="8" t="s">
         <v>73</v>
@@ -67262,20 +67681,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D463,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D463,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L463" s="11">
+      <c t="str" r="L463" s="11">
         <f ca="1">IF($O463="","",$O463-TODAY())</f>
-        <v>158</v>
-      </c>
-      <c r="M463" s="11">
-        <f ca="1">IF($C463="","",$C463+365-TODAY())</f>
-        <v>182</v>
-      </c>
-      <c r="N463" s="11">
-        <f ca="1">IF($C463="","",$C463+120-TODAY())</f>
-        <v>-63</v>
-      </c>
-      <c r="O463" s="9">
-        <v>46462</v>
+        <v/>
+      </c>
+      <c t="str" r="M463" s="11">
+        <f ca="1">IF(AND(TRIM($A463)="Finalized",$K463&lt;&gt;""),"",IF($C463="","",$C463+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N463" s="11">
+        <f ca="1">IF(AND(TRIM($A463)="Finalized",$K463&lt;&gt;""),"",IF($C463="","",$C463+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O463" s="9">
+        <f>IF(AND(TRIM($A463)="Finalized",$K463&lt;&gt;""),"",DATE(2027,3,16))</f>
+        <v/>
       </c>
       <c r="P463" s="8" t="s">
         <v>73</v>
@@ -67384,20 +67804,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D464,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D464,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L464" s="11">
+      <c t="str" r="L464" s="11">
         <f ca="1">IF($O464="","",$O464-TODAY())</f>
-        <v>165</v>
-      </c>
-      <c r="M464" s="11">
-        <f ca="1">IF($C464="","",$C464+365-TODAY())</f>
-        <v>217</v>
-      </c>
-      <c r="N464" s="11">
-        <f ca="1">IF($C464="","",$C464+120-TODAY())</f>
-        <v>-28</v>
-      </c>
-      <c r="O464" s="9">
-        <v>46469</v>
+        <v/>
+      </c>
+      <c t="str" r="M464" s="11">
+        <f ca="1">IF(AND(TRIM($A464)="Finalized",$K464&lt;&gt;""),"",IF($C464="","",$C464+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N464" s="11">
+        <f ca="1">IF(AND(TRIM($A464)="Finalized",$K464&lt;&gt;""),"",IF($C464="","",$C464+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O464" s="9">
+        <f>IF(AND(TRIM($A464)="Finalized",$K464&lt;&gt;""),"",DATE(2027,3,23))</f>
+        <v/>
       </c>
       <c r="P464" s="8" t="s">
         <v>73</v>
@@ -67506,20 +67927,21 @@
         <f>IFERROR(IF(INDEX([3]DME!$K$2:$K$11,MATCH($D465,[3]DME!$D$2:$D$11,0))="","",INDEX([3]DME!$K$2:$K$11,MATCH($D465,[3]DME!$D$2:$D$11,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L465" s="11">
+      <c t="str" r="L465" s="11">
         <f ca="1">IF($O465="","",$O465-TODAY())</f>
-        <v>173</v>
-      </c>
-      <c r="M465" s="11">
-        <f ca="1">IF($C465="","",$C465+365-TODAY())</f>
-        <v>182</v>
-      </c>
-      <c r="N465" s="11">
-        <f ca="1">IF($C465="","",$C465+120-TODAY())</f>
-        <v>-63</v>
-      </c>
-      <c r="O465" s="9">
-        <v>46477</v>
+        <v/>
+      </c>
+      <c t="str" r="M465" s="11">
+        <f ca="1">IF(AND(TRIM($A465)="Finalized",$K465&lt;&gt;""),"",IF($C465="","",$C465+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N465" s="11">
+        <f ca="1">IF(AND(TRIM($A465)="Finalized",$K465&lt;&gt;""),"",IF($C465="","",$C465+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O465" s="9">
+        <f>IF(AND(TRIM($A465)="Finalized",$K465&lt;&gt;""),"",DATE(2027,3,31))</f>
+        <v/>
       </c>
       <c r="P465" s="8" t="s">
         <v>73</v>
@@ -67630,20 +68052,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D466,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D466,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46283</v>
       </c>
-      <c r="L466" s="11">
+      <c t="str" r="L466" s="11">
         <f ca="1">IF($O466="","",$O466-TODAY())</f>
-        <v>182</v>
-      </c>
-      <c r="M466" s="11">
-        <f ca="1">IF($C466="","",$C466+365-TODAY())</f>
-        <v>310</v>
-      </c>
-      <c r="N466" s="11">
-        <f ca="1">IF($C466="","",$C466+120-TODAY())</f>
-        <v>65</v>
-      </c>
-      <c r="O466" s="9">
-        <v>46486</v>
+        <v/>
+      </c>
+      <c t="str" r="M466" s="11">
+        <f ca="1">IF(AND(TRIM($A466)="Finalized",$K466&lt;&gt;""),"",IF($C466="","",$C466+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N466" s="11">
+        <f ca="1">IF(AND(TRIM($A466)="Finalized",$K466&lt;&gt;""),"",IF($C466="","",$C466+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O466" s="9">
+        <f>IF(AND(TRIM($A466)="Finalized",$K466&lt;&gt;""),"",DATE(2027,4,9))</f>
+        <v/>
       </c>
       <c r="P466" s="8" t="s">
         <v>73</v>
@@ -67748,20 +68171,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D467,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D467,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46283</v>
       </c>
-      <c r="L467" s="11">
+      <c t="str" r="L467" s="11">
         <f ca="1">IF($O467="","",$O467-TODAY())</f>
-        <v>186</v>
-      </c>
-      <c r="M467" s="11">
-        <f ca="1">IF($C467="","",$C467+365-TODAY())</f>
-        <v>200</v>
-      </c>
-      <c r="N467" s="11">
-        <f ca="1">IF($C467="","",$C467+120-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="O467" s="9">
-        <v>46490</v>
+        <v/>
+      </c>
+      <c t="str" r="M467" s="11">
+        <f ca="1">IF(AND(TRIM($A467)="Finalized",$K467&lt;&gt;""),"",IF($C467="","",$C467+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N467" s="11">
+        <f ca="1">IF(AND(TRIM($A467)="Finalized",$K467&lt;&gt;""),"",IF($C467="","",$C467+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O467" s="9">
+        <f>IF(AND(TRIM($A467)="Finalized",$K467&lt;&gt;""),"",DATE(2027,4,13))</f>
+        <v/>
       </c>
       <c r="P467" s="8" t="s">
         <v>73</v>
@@ -67868,20 +68292,21 @@
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D468,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D468,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>46300</v>
       </c>
-      <c r="L468" s="11">
+      <c t="str" r="L468" s="11">
         <f ca="1">IF($O468="","",$O468-TODAY())</f>
-        <v>187</v>
-      </c>
-      <c r="M468" s="11">
-        <f ca="1">IF($C468="","",$C468+365-TODAY())</f>
-        <v>209</v>
-      </c>
-      <c r="N468" s="11">
-        <f ca="1">IF($C468="","",$C468+120-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="O468" s="9">
-        <v>46491</v>
+        <v/>
+      </c>
+      <c t="str" r="M468" s="11">
+        <f ca="1">IF(AND(TRIM($A468)="Finalized",$K468&lt;&gt;""),"",IF($C468="","",$C468+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N468" s="11">
+        <f ca="1">IF(AND(TRIM($A468)="Finalized",$K468&lt;&gt;""),"",IF($C468="","",$C468+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O468" s="9">
+        <f>IF(AND(TRIM($A468)="Finalized",$K468&lt;&gt;""),"",DATE(2027,4,14))</f>
+        <v/>
       </c>
       <c r="P468" s="8" t="s">
         <v>73</v>
@@ -67988,20 +68413,21 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D469,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D469,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46276</v>
       </c>
-      <c r="L469" s="11">
+      <c t="str" r="L469" s="11">
         <f ca="1">IF($O469="","",$O469-TODAY())</f>
-        <v>204</v>
-      </c>
-      <c r="M469" s="11">
-        <f ca="1">IF($C469="","",$C469+365-TODAY())</f>
-        <v>327</v>
-      </c>
-      <c r="N469" s="11">
-        <f ca="1">IF($C469="","",$C469+120-TODAY())</f>
-        <v>82</v>
-      </c>
-      <c r="O469" s="9">
-        <v>46508</v>
+        <v/>
+      </c>
+      <c t="str" r="M469" s="11">
+        <f ca="1">IF(AND(TRIM($A469)="Finalized",$K469&lt;&gt;""),"",IF($C469="","",$C469+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N469" s="11">
+        <f ca="1">IF(AND(TRIM($A469)="Finalized",$K469&lt;&gt;""),"",IF($C469="","",$C469+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O469" s="9">
+        <f>IF(AND(TRIM($A469)="Finalized",$K469&lt;&gt;""),"",DATE(2027,5,1))</f>
+        <v/>
       </c>
       <c r="P469" s="8" t="s">
         <v>73</v>
@@ -68104,20 +68530,21 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D470,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D470,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="L470" s="11">
+      <c t="str" r="L470" s="11">
         <f ca="1">IF($O470="","",$O470-TODAY())</f>
-        <v>210</v>
-      </c>
-      <c r="M470" s="11">
-        <f ca="1">IF($C470="","",$C470+365-TODAY())</f>
-        <v>257</v>
-      </c>
-      <c r="N470" s="11">
-        <f ca="1">IF($C470="","",$C470+120-TODAY())</f>
-        <v>12</v>
-      </c>
-      <c r="O470" s="9">
-        <v>46514</v>
+        <v/>
+      </c>
+      <c t="str" r="M470" s="11">
+        <f ca="1">IF(AND(TRIM($A470)="Finalized",$K470&lt;&gt;""),"",IF($C470="","",$C470+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N470" s="11">
+        <f ca="1">IF(AND(TRIM($A470)="Finalized",$K470&lt;&gt;""),"",IF($C470="","",$C470+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O470" s="9">
+        <f>IF(AND(TRIM($A470)="Finalized",$K470&lt;&gt;""),"",DATE(2027,5,7))</f>
+        <v/>
       </c>
       <c r="P470" s="8" t="s">
         <v>73</v>
@@ -68224,20 +68651,21 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D471,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D471,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="L471" s="11">
+      <c t="str" r="L471" s="11">
         <f ca="1">IF($O471="","",$O471-TODAY())</f>
-        <v>211</v>
-      </c>
-      <c r="M471" s="11">
-        <f ca="1">IF($C471="","",$C471+365-TODAY())</f>
-        <v>257</v>
-      </c>
-      <c r="N471" s="11">
-        <f ca="1">IF($C471="","",$C471+120-TODAY())</f>
-        <v>12</v>
-      </c>
-      <c r="O471" s="9">
-        <v>46515</v>
+        <v/>
+      </c>
+      <c t="str" r="M471" s="11">
+        <f ca="1">IF(AND(TRIM($A471)="Finalized",$K471&lt;&gt;""),"",IF($C471="","",$C471+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N471" s="11">
+        <f ca="1">IF(AND(TRIM($A471)="Finalized",$K471&lt;&gt;""),"",IF($C471="","",$C471+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O471" s="9">
+        <f>IF(AND(TRIM($A471)="Finalized",$K471&lt;&gt;""),"",DATE(2027,5,8))</f>
+        <v/>
       </c>
       <c r="P471" s="8" t="s">
         <v>73</v>
@@ -68344,20 +68772,21 @@
         <f>IFERROR(IF(INDEX([5]US!$K$2:$K$19,MATCH($D472,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$K$2:$K$19,MATCH($D472,[5]US!$D$2:$D$19,0))),"")</f>
         <v>46258</v>
       </c>
-      <c r="L472" s="11">
+      <c t="str" r="L472" s="11">
         <f ca="1">IF($O472="","",$O472-TODAY())</f>
-        <v>216</v>
-      </c>
-      <c r="M472" s="11">
-        <f ca="1">IF($C472="","",$C472+365-TODAY())</f>
-        <v>306</v>
-      </c>
-      <c r="N472" s="11">
-        <f ca="1">IF($C472="","",$C472+120-TODAY())</f>
-        <v>61</v>
-      </c>
-      <c r="O472" s="9">
-        <v>46520</v>
+        <v/>
+      </c>
+      <c t="str" r="M472" s="11">
+        <f ca="1">IF(AND(TRIM($A472)="Finalized",$K472&lt;&gt;""),"",IF($C472="","",$C472+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N472" s="11">
+        <f ca="1">IF(AND(TRIM($A472)="Finalized",$K472&lt;&gt;""),"",IF($C472="","",$C472+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O472" s="9">
+        <f>IF(AND(TRIM($A472)="Finalized",$K472&lt;&gt;""),"",DATE(2027,5,13))</f>
+        <v/>
       </c>
       <c r="P472" s="8" t="s">
         <v>73</v>
@@ -68464,20 +68893,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D473,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D473,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46254</v>
       </c>
-      <c r="L473" s="11">
+      <c t="str" r="L473" s="11">
         <f ca="1">IF($O473="","",$O473-TODAY())</f>
-        <v>217</v>
-      </c>
-      <c r="M473" s="11">
-        <f ca="1">IF($C473="","",$C473+365-TODAY())</f>
-        <v>308</v>
-      </c>
-      <c r="N473" s="11">
-        <f ca="1">IF($C473="","",$C473+120-TODAY())</f>
-        <v>63</v>
-      </c>
-      <c r="O473" s="9">
-        <v>46521</v>
+        <v/>
+      </c>
+      <c t="str" r="M473" s="11">
+        <f ca="1">IF(AND(TRIM($A473)="Finalized",$K473&lt;&gt;""),"",IF($C473="","",$C473+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N473" s="11">
+        <f ca="1">IF(AND(TRIM($A473)="Finalized",$K473&lt;&gt;""),"",IF($C473="","",$C473+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O473" s="9">
+        <f>IF(AND(TRIM($A473)="Finalized",$K473&lt;&gt;""),"",DATE(2027,5,14))</f>
+        <v/>
       </c>
       <c r="P473" s="8" t="s">
         <v>73</v>
@@ -68586,20 +69016,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D474,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D474,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46255</v>
       </c>
-      <c r="L474" s="11">
+      <c t="str" r="L474" s="11">
         <f ca="1">IF($O474="","",$O474-TODAY())</f>
-        <v>221</v>
-      </c>
-      <c r="M474" s="11">
-        <f ca="1">IF($C474="","",$C474+365-TODAY())</f>
-        <v>280</v>
-      </c>
-      <c r="N474" s="11">
-        <f ca="1">IF($C474="","",$C474+120-TODAY())</f>
-        <v>35</v>
-      </c>
-      <c r="O474" s="9">
-        <v>46525</v>
+        <v/>
+      </c>
+      <c t="str" r="M474" s="11">
+        <f ca="1">IF(AND(TRIM($A474)="Finalized",$K474&lt;&gt;""),"",IF($C474="","",$C474+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N474" s="11">
+        <f ca="1">IF(AND(TRIM($A474)="Finalized",$K474&lt;&gt;""),"",IF($C474="","",$C474+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O474" s="9">
+        <f>IF(AND(TRIM($A474)="Finalized",$K474&lt;&gt;""),"",DATE(2027,5,18))</f>
+        <v/>
       </c>
       <c r="P474" s="8" t="s">
         <v>73</v>
@@ -68706,20 +69137,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D475,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D475,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46255</v>
       </c>
-      <c r="L475" s="11">
+      <c t="str" r="L475" s="11">
         <f ca="1">IF($O475="","",$O475-TODAY())</f>
-        <v>222</v>
-      </c>
-      <c r="M475" s="11">
-        <f ca="1">IF($C475="","",$C475+365-TODAY())</f>
-        <v>307</v>
-      </c>
-      <c r="N475" s="11">
-        <f ca="1">IF($C475="","",$C475+120-TODAY())</f>
-        <v>62</v>
-      </c>
-      <c r="O475" s="9">
-        <v>46526</v>
+        <v/>
+      </c>
+      <c t="str" r="M475" s="11">
+        <f ca="1">IF(AND(TRIM($A475)="Finalized",$K475&lt;&gt;""),"",IF($C475="","",$C475+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N475" s="11">
+        <f ca="1">IF(AND(TRIM($A475)="Finalized",$K475&lt;&gt;""),"",IF($C475="","",$C475+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O475" s="9">
+        <f>IF(AND(TRIM($A475)="Finalized",$K475&lt;&gt;""),"",DATE(2027,5,19))</f>
+        <v/>
       </c>
       <c r="P475" s="8" t="s">
         <v>73</v>
@@ -68828,20 +69260,21 @@
         <f>IFERROR(IF(INDEX([5]DME!$K$2:$K$35,MATCH($D476,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$K$2:$K$35,MATCH($D476,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>46276</v>
       </c>
-      <c r="L476" s="11">
+      <c t="str" r="L476" s="11">
         <f ca="1">IF($O476="","",$O476-TODAY())</f>
-        <v>232</v>
-      </c>
-      <c r="M476" s="11">
-        <f ca="1">IF($C476="","",$C476+365-TODAY())</f>
-        <v>329</v>
-      </c>
-      <c r="N476" s="11">
-        <f ca="1">IF($C476="","",$C476+120-TODAY())</f>
-        <v>84</v>
-      </c>
-      <c r="O476" s="9">
-        <v>46536</v>
+        <v/>
+      </c>
+      <c t="str" r="M476" s="11">
+        <f ca="1">IF(AND(TRIM($A476)="Finalized",$K476&lt;&gt;""),"",IF($C476="","",$C476+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N476" s="11">
+        <f ca="1">IF(AND(TRIM($A476)="Finalized",$K476&lt;&gt;""),"",IF($C476="","",$C476+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O476" s="9">
+        <f>IF(AND(TRIM($A476)="Finalized",$K476&lt;&gt;""),"",DATE(2027,5,29))</f>
+        <v/>
       </c>
       <c r="P476" s="8" t="s">
         <v>73</v>
@@ -68952,7 +69385,7 @@
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D477,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D477,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>46262</v>
       </c>
-      <c r="L477" s="11" t="str">
+      <c t="str" r="L477" s="11">
         <f ca="1">IF($O477="","",$O477-TODAY())</f>
         <v/>
       </c>
@@ -69014,83 +69447,88 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO477" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="16" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L477 O2:O477">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="4">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M477">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N477">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="4" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="12">
+    <cfRule type="expression" dxfId="3" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="13">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="1" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AO1000">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="23" priority="25">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="22" priority="24">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
